--- a/Note/测试.xlsx
+++ b/Note/测试.xlsx
@@ -49,114 +49,276 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
-  <si>
-    <t>如果问n个关键字能组成几种结构的x树### ###</t>
-  </si>
-  <si>
-    <t>那么指的不是用这n个关键字从无到有的建x树，而是已经存在的x树含仅含这n个关键字，有几种可能</t>
-  </si>
-  <si>
-    <t>比如B树，可以采用树高从1遍历可能性</t>
-  </si>
-  <si>
-    <t>数据类型转换的规律### ###</t>
-  </si>
-  <si>
-    <t>不看目的数据类型，根据原数据类型选择扩展方式</t>
-  </si>
-  <si>
-    <t>原有符号数扩展均采用符号扩展，原无符号数扩展均采用0扩展</t>
-  </si>
-  <si>
-    <t>大小端（高低位）### ###地址增长时先碰到高位就是大端，先碰到低位就是小端</t>
-  </si>
-  <si>
-    <t>C语言的易错点### ###</t>
-  </si>
-  <si>
-    <t>字符数组在内存中按固定大小分配，并直接存储字符数据；而 char* 是一个指针，可以指向动态分配的字符内存或字符数组，其本身仅保存内存地址</t>
-  </si>
-  <si>
-    <t>除了 ASCII，还有其它的单字节编码，char[] 可以存储单字节编码和变长编码（例如 UTF-8）。对于某些 Unicode 编码（如 UTF-16 或 UTF-32），可以使用 wchar_t 或其他适当的字符类型存储</t>
-  </si>
-  <si>
-    <t>边界对齐的大小=###min(系统默认的对齐大小,进程使用的最大基本数据类型大小）###</t>
-  </si>
-  <si>
-    <t>系统默认对齐大小由CPU位数和编译器决定</t>
-  </si>
-  <si>
-    <t>进程使用的最大基本数据类型，比如int是4字节</t>
-  </si>
-  <si>
-    <t>数组的情况下，只看元素的数据类型大小，比如char数组就是1字节</t>
-  </si>
-  <si>
-    <t>总线工作频率≠总线时钟频率### ###</t>
-  </si>
-  <si>
-    <t>纠错码的纠错/检错能力：</t>
-  </si>
-  <si>
-    <t>n个编码，算出两两汉明距，取其中最小的d</t>
-  </si>
-  <si>
-    <t>汉明距：两个二进制串对应位不同的个数</t>
-  </si>
-  <si>
-    <t>检错能力：检出e位，d&gt;=e+1</t>
-  </si>
-  <si>
-    <t>纠错能力：纠正t位，d&gt;=2t+1</t>
-  </si>
-  <si>
-    <t>检错率：能检出的错误情况/所有可能的错误情况</t>
-  </si>
-  <si>
-    <t>所有的错误情况：这n个编码的位数k，用(2^k)-n，即不合法的都错</t>
-  </si>
-  <si>
-    <t>能检出的错误情况：这n个编码，每个挑e位取反的所有可能</t>
-  </si>
-  <si>
-    <t>如果d&gt;=2e+1，那么任意两个合法码取e位取反不会重复，可以直接用组合数C(n,e)*n来算能检出的错误情况</t>
-  </si>
-  <si>
-    <t>如果d&lt;2e+1，那么任意两个合法码取e位取反可能重复，需要手动枚举</t>
-  </si>
-  <si>
-    <t>类比：两个圆如果半径e太长，圆心距离d又不够大，就有可能重叠</t>
-  </si>
-  <si>
-    <t>注意：e属于检错范围内的位数，因此，不可能有合法码通过取e位取反（错误码）变为其它合法码（无法检出）</t>
-  </si>
-  <si>
-    <t>总线周期和总线时钟周期### ###</t>
-  </si>
-  <si>
-    <t>总线周期：完成一次总线操作的总时长</t>
-  </si>
-  <si>
-    <t>总线时钟周期：总线时钟的周期，是衡量总线操作时长的基本单位，一个总线操作一般需要耗费多个总线时钟周期</t>
-  </si>
-  <si>
-    <t>同步总线才有时钟的概念，同步总线的时钟可能是独立的，也可能复用CPU时钟</t>
-  </si>
-  <si>
-    <t>408默认情况下，同步总线使用独立的时钟，除非条件有明写，否则不会复用CPU的时钟</t>
-  </si>
-  <si>
-    <t>TCP拥塞控制中的无效ACK：没有确认任何新数据，仅重复确认已确认过的旧数据### ###</t>
-  </si>
-  <si>
-    <t>第一种情况：重复确认最新的数据，三次后触发快重传</t>
-  </si>
-  <si>
-    <t>第二种情况：先重复了后面的数据，再确认前面的（旧的）数据</t>
-  </si>
-  <si>
-    <t>简化逻辑：当前ACK_SEQ&lt;=之前的最大ACK_SEQ，这种就是无效的</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="90">
+  <si>
+    <t>无论是齐次还是非齐次线性方程组，只要系数阵满秩，那么解的情况就是唯一的。### ###</t>
+  </si>
+  <si>
+    <t>自由变量没了，解就被限定住了</t>
+  </si>
+  <si>
+    <t>对齐次来说就只有0解</t>
+  </si>
+  <si>
+    <t>对非齐次来说就失去了齐次通解的部分，只有唯一一个特解</t>
+  </si>
+  <si>
+    <t>自由变量的个数是固定的，但是选取是不固定的### ###</t>
+  </si>
+  <si>
+    <t>系数阵m*n，也就是m行n列，列对应变量，看作实际的维度### ###</t>
+  </si>
+  <si>
+    <t>秩等于n，也就是说，哪怕行m大于n，实际有效的也就只有其中n行</t>
+  </si>
+  <si>
+    <t>秩大于n是不可能的，因为秩小于等于行列数中较小的那一个</t>
+  </si>
+  <si>
+    <t>唯一解方程暗示r(A)=n，克拉默使用条件满足，如果只求解坐标的其中一个分量，那就一定是克拉默### ###</t>
+  </si>
+  <si>
+    <t>当###A和B不是方阵###时，AB也许可逆，但是A和B不可逆</t>
+  </si>
+  <si>
+    <t>乘积矩阵的维度若大于两个矩阵的秩，必非满秩</t>
+  </si>
+  <si>
+    <t>如果高矩阵*宽矩阵，那么必非满秩</t>
+  </si>
+  <si>
+    <t>如果宽矩阵*高矩阵，那么可能满秩</t>
+  </si>
+  <si>
+    <t>幂零矩阵的要求：存在正整数k使得A^k=零矩阵### ###</t>
+  </si>
+  <si>
+    <t>如果次数n小于k，A^n为非零矩阵</t>
+  </si>
+  <si>
+    <t>只有次数n大于k，A^n为零矩阵</t>
+  </si>
+  <si>
+    <t>r(X)+r(Y)&gt;=r(X+Y)### ###</t>
+  </si>
+  <si>
+    <t>商品生产者的劳动的社会性质是社会分工决定的### ###</t>
+  </si>
+  <si>
+    <t>社会主义改造基本完成后的外交策略### ###</t>
+  </si>
+  <si>
+    <t>时间是1950s-1970s</t>
+  </si>
+  <si>
+    <t>50-60年代中期，毛泽东提出两个中间地带战略</t>
+  </si>
+  <si>
+    <t>亚洲、非洲、拉丁美洲广大经济落后的国家</t>
+  </si>
+  <si>
+    <t>欧洲、北美、大洋洲等发达资本主义国家，及部分东欧国家</t>
+  </si>
+  <si>
+    <t>中国不属于这两个，但是依靠第一个，争取第二个</t>
+  </si>
+  <si>
+    <t>70年代前期，毛泽东提出“三个世界”划分</t>
+  </si>
+  <si>
+    <t>美苏</t>
+  </si>
+  <si>
+    <t>美苏间的发达国家，欧洲、日本、加拿大、澳大利亚</t>
+  </si>
+  <si>
+    <t>亚洲（除日本）、非洲、拉丁美洲和其它地区，包括中国</t>
+  </si>
+  <si>
+    <t>中国经济长期稳定发展的强大引擎是### ###</t>
+  </si>
+  <si>
+    <t>超大规模市场</t>
+  </si>
+  <si>
+    <t>创新驱动发展</t>
+  </si>
+  <si>
+    <t>相互促进、良性循环</t>
+  </si>
+  <si>
+    <t>建设高质量教育体系，办好人民满意的教育，根本在于### ###</t>
+  </si>
+  <si>
+    <t>深化教育综合改革</t>
+  </si>
+  <si>
+    <t>洋务派优先集中发展军事工业，官办企业是辅助的### ###</t>
+  </si>
+  <si>
+    <t>为军事工业提供配套支持和资金支持</t>
+  </si>
+  <si>
+    <t>《中共抗日救国十大纲领》、《中共中央关于目前形势与党的任务的决定》### ###</t>
+  </si>
+  <si>
+    <t>洛川会议，1937年8月</t>
+  </si>
+  <si>
+    <t>标志着党的全面抗战路线的正式形成</t>
+  </si>
+  <si>
+    <t>二战胜利成果的集中体现是以联合国为核心的国际体系### ###</t>
+  </si>
+  <si>
+    <t>认识发展的动力### ###</t>
+  </si>
+  <si>
+    <t>根本动力：实践</t>
+  </si>
+  <si>
+    <t>强大动力：认识工具</t>
+  </si>
+  <si>
+    <t>事物的固有联系是不会被技术手段改变的，技术手段只是发现和利用固有联系### ###</t>
+  </si>
+  <si>
+    <t>价值评价的反映内容：客体对主体有什么用？### ###</t>
+  </si>
+  <si>
+    <t>离我而去的人，与死者何异？</t>
+  </si>
+  <si>
+    <t>国家资本所有制的特点### ###</t>
+  </si>
+  <si>
+    <t>所有权与出资主体是国家</t>
+  </si>
+  <si>
+    <t>经营管理采用委托代理制</t>
+  </si>
+  <si>
+    <t>根本目的：维护资本主义制度和垄断资本利益</t>
+  </si>
+  <si>
+    <t>主要存在于经济命脉、公共利益或战略利益的领域</t>
+  </si>
+  <si>
+    <t>不赚钱但是必须有人做的事</t>
+  </si>
+  <si>
+    <t>不是资本主义所有制的主体</t>
+  </si>
+  <si>
+    <t>主体是法人资本所有制</t>
+  </si>
+  <si>
+    <t>稳定经济、保障公共利益、支持战略产业</t>
+  </si>
+  <si>
+    <t>维护垄断、加重财政负担、无法解决根本矛盾</t>
+  </si>
+  <si>
+    <t>体现总资本家剥削雇佣劳动者的关系</t>
+  </si>
+  <si>
+    <t>科学社会主义的理论基石的是唯物史观和剩余价值学说### ###</t>
+  </si>
+  <si>
+    <t>古田会议### ###</t>
+  </si>
+  <si>
+    <t>确立党对军队绝对领导</t>
+  </si>
+  <si>
+    <t>纠正红军错误思想</t>
+  </si>
+  <si>
+    <t>制定红军建设的各项纲领</t>
+  </si>
+  <si>
+    <t>确立思想建党、政治建军原则</t>
+  </si>
+  <si>
+    <t>规定红军是一个执行革命的政治任务的武装集团</t>
+  </si>
+  <si>
+    <t>加强党的思想建设的极端重要性### ###</t>
+  </si>
+  <si>
+    <t>出自六届六中全会的《论新阶段》</t>
+  </si>
+  <si>
+    <t>构建新发展格局加快推动高质量发展### ###</t>
+  </si>
+  <si>
+    <t>扩大内需</t>
+  </si>
+  <si>
+    <t>高水平开放</t>
+  </si>
+  <si>
+    <t>安全保障</t>
+  </si>
+  <si>
+    <t>内卷为何削弱行业整体竞争力### ###</t>
+  </si>
+  <si>
+    <t>资源错配（资源向低价倾销倾斜，质量降低）</t>
+  </si>
+  <si>
+    <t>创新动力枯竭（创新的风险性太大）</t>
+  </si>
+  <si>
+    <t>利润空间压缩（加重企业经济负担，缺乏资金，就无法提供优质的产品）</t>
+  </si>
+  <si>
+    <t>行业生态恶化（透支消费者信任，A家造假，也怕B家）</t>
+  </si>
+  <si>
+    <t>中国特色社会主义文化建设的根本方向是### ###</t>
+  </si>
+  <si>
+    <t>坚持马克思主义指导</t>
+  </si>
+  <si>
+    <t>坚持为人民服务、为社会主义服务</t>
+  </si>
+  <si>
+    <t>抗战胜利是中华民族从近代以来陷入深重危机走向伟大复兴的历史转折点### ###</t>
+  </si>
+  <si>
+    <t>新民主主义社会：1949-1956### ###</t>
+  </si>
+  <si>
+    <t>三大改造完成前</t>
+  </si>
+  <si>
+    <t>长征的胜利是中国革命转危为安的关键### ###</t>
+  </si>
+  <si>
+    <t>没有信念的理想不叫作理想，而叫作空想（可行）或幻想（不可行）### ###</t>
+  </si>
+  <si>
+    <t>即使盲信，不具备可行性的想法不是理想，而是“有信念的幻想”</t>
+  </si>
+  <si>
+    <t>因此，理想和信念总是相互依存</t>
+  </si>
+  <si>
+    <t>信仰和信念的区别：前者具体，后者抽象，前者细微，后者宏大，前者零散，后者系统### ###</t>
+  </si>
+  <si>
+    <t>坚持依法治国和以德治国相结合，需要### ###</t>
+  </si>
+  <si>
+    <t>运用法治手段解决道德领域突出问题</t>
+  </si>
+  <si>
+    <t>强化道德对法治的支撑作用</t>
+  </si>
+  <si>
+    <t>在立法、执法、司法中都体现社会主义道德要求</t>
   </si>
 </sst>
 </file>
@@ -1094,7 +1256,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H92"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="9.66666666666667" style="1"/>
@@ -1104,23 +1266,23 @@
     <row r="1" s="1" customFormat="1" spans="1:8">
       <c r="A1" s="2">
         <f>SUM(B1:AZ1)</f>
-        <v>12.55</v>
+        <v>34.5</v>
       </c>
       <c r="B1" s="2">
-        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2078)/COLUMN()</f>
-        <v>4.5</v>
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2128)/COLUMN()</f>
+        <v>15</v>
       </c>
       <c r="C1" s="2">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D1" s="2">
         <f t="shared" si="0"/>
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="E1" s="2">
         <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="F1" s="2">
         <f t="shared" si="0"/>
@@ -1155,168 +1317,443 @@
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:8">
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:8">
-      <c r="C6" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:8">
-      <c r="C7" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:8">
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:8">
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:8">
-      <c r="C10" s="1" t="s">
+      <c r="B10" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:8">
-      <c r="C11" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:8">
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:8">
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:8">
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:8">
-      <c r="D15" s="1" t="s">
+      <c r="B15" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:8">
-      <c r="B16" s="1" t="s">
+      <c r="C16" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" spans="2:5">
-      <c r="B17" s="1" t="s">
+    <row r="17" s="1" customFormat="1" spans="2:4">
+      <c r="C17" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" spans="2:5">
-      <c r="C18" s="1" t="s">
+    <row r="18" s="1" customFormat="1" spans="2:4">
+      <c r="B18" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" spans="2:5">
-      <c r="D19" s="1" t="s">
+    <row r="19" s="1" customFormat="1" spans="2:4">
+      <c r="B19" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" spans="2:5">
-      <c r="C20" s="1" t="s">
+    <row r="20" s="1" customFormat="1" spans="2:4">
+      <c r="B20" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" spans="2:5">
+    <row r="21" s="1" customFormat="1" spans="2:4">
       <c r="C21" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" spans="2:5">
+    <row r="22" s="1" customFormat="1" spans="2:4">
       <c r="C22" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" spans="2:5">
+    <row r="23" s="1" customFormat="1" spans="2:4">
       <c r="D23" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" spans="2:5">
+    <row r="24" s="1" customFormat="1" spans="2:4">
       <c r="D24" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" spans="2:5">
-      <c r="E25" s="1" t="s">
+    <row r="25" s="1" customFormat="1" spans="2:4">
+      <c r="D25" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" spans="2:5">
-      <c r="E26" s="1" t="s">
+    <row r="26" s="1" customFormat="1" spans="2:4">
+      <c r="C26" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" spans="2:5">
-      <c r="E27" s="1" t="s">
+    <row r="27" s="1" customFormat="1" spans="2:4">
+      <c r="D27" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" spans="2:5">
-      <c r="E28" s="1" t="s">
+    <row r="28" s="1" customFormat="1" spans="2:4">
+      <c r="D28" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" spans="2:5">
-      <c r="B29" s="1" t="s">
+    <row r="29" s="1" customFormat="1" spans="2:4">
+      <c r="D29" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" spans="2:5">
-      <c r="C30" s="1" t="s">
+    <row r="30" s="1" customFormat="1" spans="2:4">
+      <c r="B30" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" spans="2:5">
+    <row r="31" s="1" customFormat="1" spans="2:4">
       <c r="C31" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="32" s="1" customFormat="1" spans="2:5">
+    <row r="32" s="1" customFormat="1" spans="2:4">
       <c r="C32" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="33" s="1" customFormat="1" spans="2:4">
-      <c r="D33" s="1" t="s">
+    <row r="33" s="1" customFormat="1" spans="2:3">
+      <c r="C33" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" spans="2:4">
+    <row r="34" s="1" customFormat="1" spans="2:3">
       <c r="B34" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" spans="2:4">
+    <row r="35" s="1" customFormat="1" spans="2:3">
       <c r="C35" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="36" s="1" customFormat="1" spans="2:4">
-      <c r="C36" s="1" t="s">
+    <row r="36" s="1" customFormat="1" spans="2:3">
+      <c r="B36" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="37" s="1" customFormat="1" spans="2:4">
+    <row r="37" s="1" customFormat="1" spans="2:3">
       <c r="C37" s="1" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" spans="2:3">
+      <c r="B38" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" s="1" customFormat="1" spans="2:3">
+      <c r="C39" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" s="1" customFormat="1" spans="2:3">
+      <c r="C40" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" s="1" customFormat="1" spans="2:3">
+      <c r="B41" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" s="1" customFormat="1" spans="2:3">
+      <c r="B42" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" s="1" customFormat="1" spans="2:3">
+      <c r="C43" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44" s="1" customFormat="1" spans="2:3">
+      <c r="C44" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" s="1" customFormat="1" spans="2:3">
+      <c r="B45" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" s="1" customFormat="1" spans="2:3">
+      <c r="B46" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" s="1" customFormat="1" spans="2:3">
+      <c r="C47" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" s="1" customFormat="1" spans="2:3">
+      <c r="B48" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" s="1" customFormat="1" spans="2:4">
+      <c r="C49" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" s="1" customFormat="1" spans="2:4">
+      <c r="C50" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51" s="1" customFormat="1" spans="2:4">
+      <c r="C51" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" s="1" customFormat="1" spans="2:4">
+      <c r="C52" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" s="1" customFormat="1" spans="2:4">
+      <c r="D53" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54" s="1" customFormat="1" spans="2:4">
+      <c r="C54" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="55" s="1" customFormat="1" spans="2:4">
+      <c r="D55" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="56" s="1" customFormat="1" spans="2:4">
+      <c r="C56" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="57" s="1" customFormat="1" spans="2:4">
+      <c r="C57" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" s="1" customFormat="1" spans="2:4">
+      <c r="C58" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="59" s="1" customFormat="1" spans="2:4">
+      <c r="B59" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="60" s="1" customFormat="1" spans="2:4">
+      <c r="B60" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="61" s="1" customFormat="1" spans="2:4">
+      <c r="C61" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="62" s="1" customFormat="1" spans="2:4">
+      <c r="C62" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="63" s="1" customFormat="1" spans="2:4">
+      <c r="C63" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64" s="1" customFormat="1" spans="2:4">
+      <c r="C64" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="65" s="1" customFormat="1" spans="2:3">
+      <c r="C65" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="66" s="1" customFormat="1" spans="2:3">
+      <c r="B66" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="67" s="1" customFormat="1" spans="2:3">
+      <c r="C67" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="68" s="1" customFormat="1" spans="2:3">
+      <c r="B68" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="69" s="1" customFormat="1" spans="2:3">
+      <c r="C69" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="70" s="1" customFormat="1" spans="2:3">
+      <c r="C70" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="71" s="1" customFormat="1" spans="2:3">
+      <c r="C71" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="72" s="1" customFormat="1" spans="2:3">
+      <c r="C72" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="73" s="1" customFormat="1" spans="2:3">
+      <c r="B73" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="74" s="1" customFormat="1" spans="2:3">
+      <c r="C74" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="75" s="1" customFormat="1" spans="2:3">
+      <c r="C75" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="76" s="1" customFormat="1" spans="2:3">
+      <c r="C76" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="77" s="1" customFormat="1" spans="2:3">
+      <c r="C77" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="78" s="1" customFormat="1" spans="2:3">
+      <c r="B78" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="79" s="1" customFormat="1" spans="2:3">
+      <c r="C79" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="80" s="1" customFormat="1" spans="2:3">
+      <c r="C80" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="81" s="1" customFormat="1" spans="2:3">
+      <c r="B81" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="82" s="1" customFormat="1" spans="2:3">
+      <c r="B82" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="83" s="1" customFormat="1" spans="2:3">
+      <c r="C83" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="84" s="1" customFormat="1" spans="2:3">
+      <c r="B84" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="85" s="1" customFormat="1" spans="2:3">
+      <c r="B85" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="86" s="1" customFormat="1" spans="2:3">
+      <c r="C86" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="87" s="1" customFormat="1" spans="2:3">
+      <c r="C87" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="88" s="1" customFormat="1" spans="2:3">
+      <c r="B88" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="89" s="1" customFormat="1" spans="2:3">
+      <c r="B89" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="90" s="1" customFormat="1" spans="2:3">
+      <c r="C90" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="91" s="1" customFormat="1" spans="2:3">
+      <c r="C91" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="92" s="1" customFormat="1" spans="2:3">
+      <c r="C92" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/Note/测试.xlsx
+++ b/Note/测试.xlsx
@@ -49,276 +49,192 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="90">
-  <si>
-    <t>无论是齐次还是非齐次线性方程组，只要系数阵满秩，那么解的情况就是唯一的。### ###</t>
-  </si>
-  <si>
-    <t>自由变量没了，解就被限定住了</t>
-  </si>
-  <si>
-    <t>对齐次来说就只有0解</t>
-  </si>
-  <si>
-    <t>对非齐次来说就失去了齐次通解的部分，只有唯一一个特解</t>
-  </si>
-  <si>
-    <t>自由变量的个数是固定的，但是选取是不固定的### ###</t>
-  </si>
-  <si>
-    <t>系数阵m*n，也就是m行n列，列对应变量，看作实际的维度### ###</t>
-  </si>
-  <si>
-    <t>秩等于n，也就是说，哪怕行m大于n，实际有效的也就只有其中n行</t>
-  </si>
-  <si>
-    <t>秩大于n是不可能的，因为秩小于等于行列数中较小的那一个</t>
-  </si>
-  <si>
-    <t>唯一解方程暗示r(A)=n，克拉默使用条件满足，如果只求解坐标的其中一个分量，那就一定是克拉默### ###</t>
-  </si>
-  <si>
-    <t>当###A和B不是方阵###时，AB也许可逆，但是A和B不可逆</t>
-  </si>
-  <si>
-    <t>乘积矩阵的维度若大于两个矩阵的秩，必非满秩</t>
-  </si>
-  <si>
-    <t>如果高矩阵*宽矩阵，那么必非满秩</t>
-  </si>
-  <si>
-    <t>如果宽矩阵*高矩阵，那么可能满秩</t>
-  </si>
-  <si>
-    <t>幂零矩阵的要求：存在正整数k使得A^k=零矩阵### ###</t>
-  </si>
-  <si>
-    <t>如果次数n小于k，A^n为非零矩阵</t>
-  </si>
-  <si>
-    <t>只有次数n大于k，A^n为零矩阵</t>
-  </si>
-  <si>
-    <t>r(X)+r(Y)&gt;=r(X+Y)### ###</t>
-  </si>
-  <si>
-    <t>商品生产者的劳动的社会性质是社会分工决定的### ###</t>
-  </si>
-  <si>
-    <t>社会主义改造基本完成后的外交策略### ###</t>
-  </si>
-  <si>
-    <t>时间是1950s-1970s</t>
-  </si>
-  <si>
-    <t>50-60年代中期，毛泽东提出两个中间地带战略</t>
-  </si>
-  <si>
-    <t>亚洲、非洲、拉丁美洲广大经济落后的国家</t>
-  </si>
-  <si>
-    <t>欧洲、北美、大洋洲等发达资本主义国家，及部分东欧国家</t>
-  </si>
-  <si>
-    <t>中国不属于这两个，但是依靠第一个，争取第二个</t>
-  </si>
-  <si>
-    <t>70年代前期，毛泽东提出“三个世界”划分</t>
-  </si>
-  <si>
-    <t>美苏</t>
-  </si>
-  <si>
-    <t>美苏间的发达国家，欧洲、日本、加拿大、澳大利亚</t>
-  </si>
-  <si>
-    <t>亚洲（除日本）、非洲、拉丁美洲和其它地区，包括中国</t>
-  </si>
-  <si>
-    <t>中国经济长期稳定发展的强大引擎是### ###</t>
-  </si>
-  <si>
-    <t>超大规模市场</t>
-  </si>
-  <si>
-    <t>创新驱动发展</t>
-  </si>
-  <si>
-    <t>相互促进、良性循环</t>
-  </si>
-  <si>
-    <t>建设高质量教育体系，办好人民满意的教育，根本在于### ###</t>
-  </si>
-  <si>
-    <t>深化教育综合改革</t>
-  </si>
-  <si>
-    <t>洋务派优先集中发展军事工业，官办企业是辅助的### ###</t>
-  </si>
-  <si>
-    <t>为军事工业提供配套支持和资金支持</t>
-  </si>
-  <si>
-    <t>《中共抗日救国十大纲领》、《中共中央关于目前形势与党的任务的决定》### ###</t>
-  </si>
-  <si>
-    <t>洛川会议，1937年8月</t>
-  </si>
-  <si>
-    <t>标志着党的全面抗战路线的正式形成</t>
-  </si>
-  <si>
-    <t>二战胜利成果的集中体现是以联合国为核心的国际体系### ###</t>
-  </si>
-  <si>
-    <t>认识发展的动力### ###</t>
-  </si>
-  <si>
-    <t>根本动力：实践</t>
-  </si>
-  <si>
-    <t>强大动力：认识工具</t>
-  </si>
-  <si>
-    <t>事物的固有联系是不会被技术手段改变的，技术手段只是发现和利用固有联系### ###</t>
-  </si>
-  <si>
-    <t>价值评价的反映内容：客体对主体有什么用？### ###</t>
-  </si>
-  <si>
-    <t>离我而去的人，与死者何异？</t>
-  </si>
-  <si>
-    <t>国家资本所有制的特点### ###</t>
-  </si>
-  <si>
-    <t>所有权与出资主体是国家</t>
-  </si>
-  <si>
-    <t>经营管理采用委托代理制</t>
-  </si>
-  <si>
-    <t>根本目的：维护资本主义制度和垄断资本利益</t>
-  </si>
-  <si>
-    <t>主要存在于经济命脉、公共利益或战略利益的领域</t>
-  </si>
-  <si>
-    <t>不赚钱但是必须有人做的事</t>
-  </si>
-  <si>
-    <t>不是资本主义所有制的主体</t>
-  </si>
-  <si>
-    <t>主体是法人资本所有制</t>
-  </si>
-  <si>
-    <t>稳定经济、保障公共利益、支持战略产业</t>
-  </si>
-  <si>
-    <t>维护垄断、加重财政负担、无法解决根本矛盾</t>
-  </si>
-  <si>
-    <t>体现总资本家剥削雇佣劳动者的关系</t>
-  </si>
-  <si>
-    <t>科学社会主义的理论基石的是唯物史观和剩余价值学说### ###</t>
-  </si>
-  <si>
-    <t>古田会议### ###</t>
-  </si>
-  <si>
-    <t>确立党对军队绝对领导</t>
-  </si>
-  <si>
-    <t>纠正红军错误思想</t>
-  </si>
-  <si>
-    <t>制定红军建设的各项纲领</t>
-  </si>
-  <si>
-    <t>确立思想建党、政治建军原则</t>
-  </si>
-  <si>
-    <t>规定红军是一个执行革命的政治任务的武装集团</t>
-  </si>
-  <si>
-    <t>加强党的思想建设的极端重要性### ###</t>
-  </si>
-  <si>
-    <t>出自六届六中全会的《论新阶段》</t>
-  </si>
-  <si>
-    <t>构建新发展格局加快推动高质量发展### ###</t>
-  </si>
-  <si>
-    <t>扩大内需</t>
-  </si>
-  <si>
-    <t>高水平开放</t>
-  </si>
-  <si>
-    <t>安全保障</t>
-  </si>
-  <si>
-    <t>内卷为何削弱行业整体竞争力### ###</t>
-  </si>
-  <si>
-    <t>资源错配（资源向低价倾销倾斜，质量降低）</t>
-  </si>
-  <si>
-    <t>创新动力枯竭（创新的风险性太大）</t>
-  </si>
-  <si>
-    <t>利润空间压缩（加重企业经济负担，缺乏资金，就无法提供优质的产品）</t>
-  </si>
-  <si>
-    <t>行业生态恶化（透支消费者信任，A家造假，也怕B家）</t>
-  </si>
-  <si>
-    <t>中国特色社会主义文化建设的根本方向是### ###</t>
-  </si>
-  <si>
-    <t>坚持马克思主义指导</t>
-  </si>
-  <si>
-    <t>坚持为人民服务、为社会主义服务</t>
-  </si>
-  <si>
-    <t>抗战胜利是中华民族从近代以来陷入深重危机走向伟大复兴的历史转折点### ###</t>
-  </si>
-  <si>
-    <t>新民主主义社会：1949-1956### ###</t>
-  </si>
-  <si>
-    <t>三大改造完成前</t>
-  </si>
-  <si>
-    <t>长征的胜利是中国革命转危为安的关键### ###</t>
-  </si>
-  <si>
-    <t>没有信念的理想不叫作理想，而叫作空想（可行）或幻想（不可行）### ###</t>
-  </si>
-  <si>
-    <t>即使盲信，不具备可行性的想法不是理想，而是“有信念的幻想”</t>
-  </si>
-  <si>
-    <t>因此，理想和信念总是相互依存</t>
-  </si>
-  <si>
-    <t>信仰和信念的区别：前者具体，后者抽象，前者细微，后者宏大，前者零散，后者系统### ###</t>
-  </si>
-  <si>
-    <t>坚持依法治国和以德治国相结合，需要### ###</t>
-  </si>
-  <si>
-    <t>运用法治手段解决道德领域突出问题</t>
-  </si>
-  <si>
-    <t>强化道德对法治的支撑作用</t>
-  </si>
-  <si>
-    <t>在立法、执法、司法中都体现社会主义道德要求</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+  <si>
+    <t>统筹好有为政府与有效市场的关系是破除内卷是竞争的关键### ###</t>
+  </si>
+  <si>
+    <t>汇率政策不能完全市场化，亚洲金融危机有前车之鉴### ###</t>
+  </si>
+  <si>
+    <t>两新两重### ###</t>
+  </si>
+  <si>
+    <t>设备更新和消费品以旧换新</t>
+  </si>
+  <si>
+    <t>重大战略实施和重点领域安全能力建设</t>
+  </si>
+  <si>
+    <t>财产性收入### ###</t>
+  </si>
+  <si>
+    <t>居民依托“动产”、“不动产”的所有权，赚到的钱（租金）</t>
+  </si>
+  <si>
+    <t>分类：金融资产收益、不动产收益、知识产权、财产增值</t>
+  </si>
+  <si>
+    <t>按要素分配中的资本要素分配，属于此次分配领域</t>
+  </si>
+  <si>
+    <t>核心特征：非劳动性</t>
+  </si>
+  <si>
+    <t>我国现阶段的分配方式### ###</t>
+  </si>
+  <si>
+    <t>核心：按劳分配为主体，多重分配方式并存</t>
+  </si>
+  <si>
+    <t>三次分配体系</t>
+  </si>
+  <si>
+    <t>初次分配：生产领域中按生产要素分配，直接与效率挂钩</t>
+  </si>
+  <si>
+    <t>按劳分配、按要素分配、经营性收入</t>
+  </si>
+  <si>
+    <t>按劳分配仅限公有制经济</t>
+  </si>
+  <si>
+    <t>按要素分配的要素：劳动、资本、土地、技术、管理、数据</t>
+  </si>
+  <si>
+    <t>再分配：征服宏观调控控制收入差距，侧重公平</t>
+  </si>
+  <si>
+    <t>税收、转移支付（社保、医保、养老金、补贴）</t>
+  </si>
+  <si>
+    <t>第三次分配：基于道德自愿的慈善捐赠、公益帮扶，是前两次分配的补充</t>
+  </si>
+  <si>
+    <t>乡村全面振兴的底线任务### ###</t>
+  </si>
+  <si>
+    <t>持续增强粮食等重要农产品的攻击保障能力（一号文件第一位，20251123）</t>
+  </si>
+  <si>
+    <t>持续巩固拓展脱贫攻坚成果</t>
+  </si>
+  <si>
+    <t>巩固和完善农村基本经营制度并不要求在土地承包到期后打乱重分### ###</t>
+  </si>
+  <si>
+    <t>底线三条：土地公有、耕地红线、农民利益不受损</t>
+  </si>
+  <si>
+    <t>乡村全面振兴的重点（三个水平）是### ###</t>
+  </si>
+  <si>
+    <t>提升乡村产业发展水平</t>
+  </si>
+  <si>
+    <t>提升乡村建设水平</t>
+  </si>
+  <si>
+    <t>提升乡村治理水平</t>
+  </si>
+  <si>
+    <t>三农工作的底线任务是确保国家粮食安全和不发生规模性返贫致贫### ###</t>
+  </si>
+  <si>
+    <t>抓产业创新要### ###</t>
+  </si>
+  <si>
+    <t>守牢实体经济这个根基</t>
+  </si>
+  <si>
+    <t>坚持推动传统产业改造升级和开辟战略性新兴产业、未来产业新赛道并重</t>
+  </si>
+  <si>
+    <t>中国特色现代企业制度的基础是### ###</t>
+  </si>
+  <si>
+    <t>产权清晰</t>
+  </si>
+  <si>
+    <t>权责明确</t>
+  </si>
+  <si>
+    <t>政企分开</t>
+  </si>
+  <si>
+    <t>管理科学</t>
+  </si>
+  <si>
+    <t>完善企业制度与社会治理无关### ###</t>
+  </si>
+  <si>
+    <t>人大代表不是由选民直接选举产生### ###</t>
+  </si>
+  <si>
+    <t>县乡两级人大代表直接选举</t>
+  </si>
+  <si>
+    <t>县级以上人大由下级人大代表间接选举产生</t>
+  </si>
+  <si>
+    <t>变通执行权### ###</t>
+  </si>
+  <si>
+    <t>特定地方国家机关（如民族自治地方、经济特区等）</t>
+  </si>
+  <si>
+    <t>在不违背宪法、法律、行政法规基本原则的前提下</t>
+  </si>
+  <si>
+    <t>针对本地区特殊情况</t>
+  </si>
+  <si>
+    <t>对上级制定的政策、法律、法规作出灵活调整并执行的权力</t>
+  </si>
+  <si>
+    <t>引领发展的第一动力是创新### ###</t>
+  </si>
+  <si>
+    <t>《新时代的中国国家安全》### ###</t>
+  </si>
+  <si>
+    <t>捍卫国家利益的坚定力量</t>
+  </si>
+  <si>
+    <t>维护世界和平稳定的正义力量</t>
+  </si>
+  <si>
+    <t>维护国际公平正义的进步力量</t>
+  </si>
+  <si>
+    <t>促进全球共同发展的建设力量</t>
+  </si>
+  <si>
+    <t>总体国家安全观是当代中国对世界的重要思想理论贡献### ###</t>
+  </si>
+  <si>
+    <t>KMP算法（怎么算）### ###</t>
+  </si>
+  <si>
+    <t>主串指针不动，模式串指针动（不一定从头，具体动多少？↓），主串指针不需要回到移动后的起点</t>
+  </si>
+  <si>
+    <t>模式串的next[j]数组记录失配后模式串指针跳转到模式串的哪个元素，j是失配指针前一个元素的下标</t>
+  </si>
+  <si>
+    <t>next[j]的生成</t>
+  </si>
+  <si>
+    <t>取最后一个字符是模式串下标j-1字符的模式子串</t>
+  </si>
+  <si>
+    <t>求出这个模式子串的前后缀</t>
+  </si>
+  <si>
+    <t>注意，前后缀不包括模式子串本身，不然长度必然是模式子串的长度</t>
+  </si>
+  <si>
+    <t>前缀和后缀的交集中选择最长的那个，取它的长度作为next[j]的元素</t>
   </si>
 </sst>
 </file>
@@ -1256,7 +1172,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H92"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="9.66666666666667" style="1"/>
@@ -1266,27 +1182,27 @@
     <row r="1" s="1" customFormat="1" spans="1:8">
       <c r="A1" s="2">
         <f>SUM(B1:AZ1)</f>
-        <v>34.5</v>
+        <v>22.4333333333333</v>
       </c>
       <c r="B1" s="2">
-        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2128)/COLUMN()</f>
-        <v>15</v>
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2192)/COLUMN()</f>
+        <v>9</v>
       </c>
       <c r="C1" s="2">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D1" s="2">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="E1" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="F1" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="G1" s="2">
         <f t="shared" si="0"/>
@@ -1307,12 +1223,12 @@
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:8">
-      <c r="C3" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:8">
-      <c r="C4" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1322,7 +1238,7 @@
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:8">
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1342,117 +1258,117 @@
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:8">
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:8">
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:8">
-      <c r="C12" s="1" t="s">
+      <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:8">
-      <c r="D13" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:8">
-      <c r="D14" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:8">
-      <c r="B15" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:8">
-      <c r="C16" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" spans="2:4">
-      <c r="C17" s="1" t="s">
+    <row r="17" s="1" customFormat="1" spans="2:6">
+      <c r="F17" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" spans="2:4">
-      <c r="B18" s="1" t="s">
+    <row r="18" s="1" customFormat="1" spans="2:6">
+      <c r="F18" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" spans="2:4">
-      <c r="B19" s="1" t="s">
+    <row r="19" s="1" customFormat="1" spans="2:6">
+      <c r="D19" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" spans="2:4">
-      <c r="B20" s="1" t="s">
+    <row r="20" s="1" customFormat="1" spans="2:6">
+      <c r="E20" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" spans="2:4">
-      <c r="C21" s="1" t="s">
+    <row r="21" s="1" customFormat="1" spans="2:6">
+      <c r="D21" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" spans="2:4">
-      <c r="C22" s="1" t="s">
+    <row r="22" s="1" customFormat="1" spans="2:6">
+      <c r="B22" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" spans="2:4">
-      <c r="D23" s="1" t="s">
+    <row r="23" s="1" customFormat="1" spans="2:6">
+      <c r="C23" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" spans="2:4">
-      <c r="D24" s="1" t="s">
+    <row r="24" s="1" customFormat="1" spans="2:6">
+      <c r="C24" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" spans="2:4">
-      <c r="D25" s="1" t="s">
+    <row r="25" s="1" customFormat="1" spans="2:6">
+      <c r="B25" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" spans="2:4">
+    <row r="26" s="1" customFormat="1" spans="2:6">
       <c r="C26" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" spans="2:4">
-      <c r="D27" s="1" t="s">
+    <row r="27" s="1" customFormat="1" spans="2:6">
+      <c r="B27" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" spans="2:4">
-      <c r="D28" s="1" t="s">
+    <row r="28" s="1" customFormat="1" spans="2:6">
+      <c r="C28" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" spans="2:4">
-      <c r="D29" s="1" t="s">
+    <row r="29" s="1" customFormat="1" spans="2:6">
+      <c r="C29" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" spans="2:4">
-      <c r="B30" s="1" t="s">
+    <row r="30" s="1" customFormat="1" spans="2:6">
+      <c r="C30" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" spans="2:4">
-      <c r="C31" s="1" t="s">
+    <row r="31" s="1" customFormat="1" spans="2:6">
+      <c r="B31" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="32" s="1" customFormat="1" spans="2:4">
-      <c r="C32" s="1" t="s">
+    <row r="32" s="1" customFormat="1" spans="2:6">
+      <c r="B32" s="1" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1462,17 +1378,17 @@
       </c>
     </row>
     <row r="34" s="1" customFormat="1" spans="2:3">
-      <c r="B34" s="1" t="s">
+      <c r="C34" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" spans="2:3">
-      <c r="C35" s="1" t="s">
+      <c r="B35" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" spans="2:3">
-      <c r="B36" s="1" t="s">
+      <c r="C36" s="1" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1482,7 +1398,7 @@
       </c>
     </row>
     <row r="38" s="1" customFormat="1" spans="2:3">
-      <c r="B38" s="1" t="s">
+      <c r="C38" s="1" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1492,7 +1408,7 @@
       </c>
     </row>
     <row r="40" s="1" customFormat="1" spans="2:3">
-      <c r="C40" s="1" t="s">
+      <c r="B40" s="1" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1502,7 +1418,7 @@
       </c>
     </row>
     <row r="42" s="1" customFormat="1" spans="2:3">
-      <c r="B42" s="1" t="s">
+      <c r="C42" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1512,17 +1428,17 @@
       </c>
     </row>
     <row r="44" s="1" customFormat="1" spans="2:3">
-      <c r="C44" s="1" t="s">
+      <c r="B44" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" spans="2:3">
-      <c r="B45" s="1" t="s">
+      <c r="C45" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" spans="2:3">
-      <c r="B46" s="1" t="s">
+      <c r="C46" s="1" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1532,228 +1448,83 @@
       </c>
     </row>
     <row r="48" s="1" customFormat="1" spans="2:3">
-      <c r="B48" s="1" t="s">
+      <c r="C48" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="49" s="1" customFormat="1" spans="2:4">
-      <c r="C49" s="1" t="s">
+    <row r="49" s="1" customFormat="1" spans="2:5">
+      <c r="B49" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="50" s="1" customFormat="1" spans="2:4">
-      <c r="C50" s="1" t="s">
+    <row r="50" s="1" customFormat="1" spans="2:5">
+      <c r="B50" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="51" s="1" customFormat="1" spans="2:4">
+    <row r="51" s="1" customFormat="1" spans="2:5">
       <c r="C51" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="52" s="1" customFormat="1" spans="2:4">
+    <row r="52" s="1" customFormat="1" spans="2:5">
       <c r="C52" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="53" s="1" customFormat="1" spans="2:4">
-      <c r="D53" s="1" t="s">
+    <row r="53" s="1" customFormat="1" spans="2:5">
+      <c r="C53" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="54" s="1" customFormat="1" spans="2:4">
+    <row r="54" s="1" customFormat="1" spans="2:5">
       <c r="C54" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="55" s="1" customFormat="1" spans="2:4">
-      <c r="D55" s="1" t="s">
+    <row r="55" s="1" customFormat="1" spans="2:5">
+      <c r="B55" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="56" s="1" customFormat="1" spans="2:4">
-      <c r="C56" s="1" t="s">
+    <row r="56" s="1" customFormat="1" spans="2:5">
+      <c r="B56" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="57" s="1" customFormat="1" spans="2:4">
+    <row r="57" s="1" customFormat="1" spans="2:5">
       <c r="C57" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="58" s="1" customFormat="1" spans="2:4">
+    <row r="58" s="1" customFormat="1" spans="2:5">
       <c r="C58" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="59" s="1" customFormat="1" spans="2:4">
-      <c r="B59" s="1" t="s">
+    <row r="59" s="1" customFormat="1" spans="2:5">
+      <c r="C59" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="60" s="1" customFormat="1" spans="2:4">
-      <c r="B60" s="1" t="s">
+    <row r="60" s="1" customFormat="1" spans="2:5">
+      <c r="D60" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="61" s="1" customFormat="1" spans="2:4">
-      <c r="C61" s="1" t="s">
+    <row r="61" s="1" customFormat="1" spans="2:5">
+      <c r="D61" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="62" s="1" customFormat="1" spans="2:4">
-      <c r="C62" s="1" t="s">
+    <row r="62" s="1" customFormat="1" spans="2:5">
+      <c r="E62" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="63" s="1" customFormat="1" spans="2:4">
-      <c r="C63" s="1" t="s">
+    <row r="63" s="1" customFormat="1" spans="2:5">
+      <c r="D63" s="1" t="s">
         <v>61</v>
-      </c>
-    </row>
-    <row r="64" s="1" customFormat="1" spans="2:4">
-      <c r="C64" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="65" s="1" customFormat="1" spans="2:3">
-      <c r="C65" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="66" s="1" customFormat="1" spans="2:3">
-      <c r="B66" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="67" s="1" customFormat="1" spans="2:3">
-      <c r="C67" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="68" s="1" customFormat="1" spans="2:3">
-      <c r="B68" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="69" s="1" customFormat="1" spans="2:3">
-      <c r="C69" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="70" s="1" customFormat="1" spans="2:3">
-      <c r="C70" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="71" s="1" customFormat="1" spans="2:3">
-      <c r="C71" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="72" s="1" customFormat="1" spans="2:3">
-      <c r="C72" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="73" s="1" customFormat="1" spans="2:3">
-      <c r="B73" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="74" s="1" customFormat="1" spans="2:3">
-      <c r="C74" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="75" s="1" customFormat="1" spans="2:3">
-      <c r="C75" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="76" s="1" customFormat="1" spans="2:3">
-      <c r="C76" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="77" s="1" customFormat="1" spans="2:3">
-      <c r="C77" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="78" s="1" customFormat="1" spans="2:3">
-      <c r="B78" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="79" s="1" customFormat="1" spans="2:3">
-      <c r="C79" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="80" s="1" customFormat="1" spans="2:3">
-      <c r="C80" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="81" s="1" customFormat="1" spans="2:3">
-      <c r="B81" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="82" s="1" customFormat="1" spans="2:3">
-      <c r="B82" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="83" s="1" customFormat="1" spans="2:3">
-      <c r="C83" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="84" s="1" customFormat="1" spans="2:3">
-      <c r="B84" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="85" s="1" customFormat="1" spans="2:3">
-      <c r="B85" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="86" s="1" customFormat="1" spans="2:3">
-      <c r="C86" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="87" s="1" customFormat="1" spans="2:3">
-      <c r="C87" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="88" s="1" customFormat="1" spans="2:3">
-      <c r="B88" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="89" s="1" customFormat="1" spans="2:3">
-      <c r="B89" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="90" s="1" customFormat="1" spans="2:3">
-      <c r="C90" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="91" s="1" customFormat="1" spans="2:3">
-      <c r="C91" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="92" s="1" customFormat="1" spans="2:3">
-      <c r="C92" s="1" t="s">
-        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/Note/测试.xlsx
+++ b/Note/测试.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180"/>
+    <workbookView windowWidth="23040" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="待处理" sheetId="1" r:id="rId1"/>
@@ -49,192 +49,294 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
-  <si>
-    <t>统筹好有为政府与有效市场的关系是破除内卷是竞争的关键### ###</t>
-  </si>
-  <si>
-    <t>汇率政策不能完全市场化，亚洲金融危机有前车之鉴### ###</t>
-  </si>
-  <si>
-    <t>两新两重### ###</t>
-  </si>
-  <si>
-    <t>设备更新和消费品以旧换新</t>
-  </si>
-  <si>
-    <t>重大战略实施和重点领域安全能力建设</t>
-  </si>
-  <si>
-    <t>财产性收入### ###</t>
-  </si>
-  <si>
-    <t>居民依托“动产”、“不动产”的所有权，赚到的钱（租金）</t>
-  </si>
-  <si>
-    <t>分类：金融资产收益、不动产收益、知识产权、财产增值</t>
-  </si>
-  <si>
-    <t>按要素分配中的资本要素分配，属于此次分配领域</t>
-  </si>
-  <si>
-    <t>核心特征：非劳动性</t>
-  </si>
-  <si>
-    <t>我国现阶段的分配方式### ###</t>
-  </si>
-  <si>
-    <t>核心：按劳分配为主体，多重分配方式并存</t>
-  </si>
-  <si>
-    <t>三次分配体系</t>
-  </si>
-  <si>
-    <t>初次分配：生产领域中按生产要素分配，直接与效率挂钩</t>
-  </si>
-  <si>
-    <t>按劳分配、按要素分配、经营性收入</t>
-  </si>
-  <si>
-    <t>按劳分配仅限公有制经济</t>
-  </si>
-  <si>
-    <t>按要素分配的要素：劳动、资本、土地、技术、管理、数据</t>
-  </si>
-  <si>
-    <t>再分配：征服宏观调控控制收入差距，侧重公平</t>
-  </si>
-  <si>
-    <t>税收、转移支付（社保、医保、养老金、补贴）</t>
-  </si>
-  <si>
-    <t>第三次分配：基于道德自愿的慈善捐赠、公益帮扶，是前两次分配的补充</t>
-  </si>
-  <si>
-    <t>乡村全面振兴的底线任务### ###</t>
-  </si>
-  <si>
-    <t>持续增强粮食等重要农产品的攻击保障能力（一号文件第一位，20251123）</t>
-  </si>
-  <si>
-    <t>持续巩固拓展脱贫攻坚成果</t>
-  </si>
-  <si>
-    <t>巩固和完善农村基本经营制度并不要求在土地承包到期后打乱重分### ###</t>
-  </si>
-  <si>
-    <t>底线三条：土地公有、耕地红线、农民利益不受损</t>
-  </si>
-  <si>
-    <t>乡村全面振兴的重点（三个水平）是### ###</t>
-  </si>
-  <si>
-    <t>提升乡村产业发展水平</t>
-  </si>
-  <si>
-    <t>提升乡村建设水平</t>
-  </si>
-  <si>
-    <t>提升乡村治理水平</t>
-  </si>
-  <si>
-    <t>三农工作的底线任务是确保国家粮食安全和不发生规模性返贫致贫### ###</t>
-  </si>
-  <si>
-    <t>抓产业创新要### ###</t>
-  </si>
-  <si>
-    <t>守牢实体经济这个根基</t>
-  </si>
-  <si>
-    <t>坚持推动传统产业改造升级和开辟战略性新兴产业、未来产业新赛道并重</t>
-  </si>
-  <si>
-    <t>中国特色现代企业制度的基础是### ###</t>
-  </si>
-  <si>
-    <t>产权清晰</t>
-  </si>
-  <si>
-    <t>权责明确</t>
-  </si>
-  <si>
-    <t>政企分开</t>
-  </si>
-  <si>
-    <t>管理科学</t>
-  </si>
-  <si>
-    <t>完善企业制度与社会治理无关### ###</t>
-  </si>
-  <si>
-    <t>人大代表不是由选民直接选举产生### ###</t>
-  </si>
-  <si>
-    <t>县乡两级人大代表直接选举</t>
-  </si>
-  <si>
-    <t>县级以上人大由下级人大代表间接选举产生</t>
-  </si>
-  <si>
-    <t>变通执行权### ###</t>
-  </si>
-  <si>
-    <t>特定地方国家机关（如民族自治地方、经济特区等）</t>
-  </si>
-  <si>
-    <t>在不违背宪法、法律、行政法规基本原则的前提下</t>
-  </si>
-  <si>
-    <t>针对本地区特殊情况</t>
-  </si>
-  <si>
-    <t>对上级制定的政策、法律、法规作出灵活调整并执行的权力</t>
-  </si>
-  <si>
-    <t>引领发展的第一动力是创新### ###</t>
-  </si>
-  <si>
-    <t>《新时代的中国国家安全》### ###</t>
-  </si>
-  <si>
-    <t>捍卫国家利益的坚定力量</t>
-  </si>
-  <si>
-    <t>维护世界和平稳定的正义力量</t>
-  </si>
-  <si>
-    <t>维护国际公平正义的进步力量</t>
-  </si>
-  <si>
-    <t>促进全球共同发展的建设力量</t>
-  </si>
-  <si>
-    <t>总体国家安全观是当代中国对世界的重要思想理论贡献### ###</t>
-  </si>
-  <si>
-    <t>KMP算法（怎么算）### ###</t>
-  </si>
-  <si>
-    <t>主串指针不动，模式串指针动（不一定从头，具体动多少？↓），主串指针不需要回到移动后的起点</t>
-  </si>
-  <si>
-    <t>模式串的next[j]数组记录失配后模式串指针跳转到模式串的哪个元素，j是失配指针前一个元素的下标</t>
-  </si>
-  <si>
-    <t>next[j]的生成</t>
-  </si>
-  <si>
-    <t>取最后一个字符是模式串下标j-1字符的模式子串</t>
-  </si>
-  <si>
-    <t>求出这个模式子串的前后缀</t>
-  </si>
-  <si>
-    <t>注意，前后缀不包括模式子串本身，不然长度必然是模式子串的长度</t>
-  </si>
-  <si>
-    <t>前缀和后缀的交集中选择最长的那个，取它的长度作为next[j]的元素</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
+  <si>
+    <t>抗日对世界发展的意义### ###</t>
+  </si>
+  <si>
+    <t>第一：揭开世界反法西斯战争序幕</t>
+  </si>
+  <si>
+    <t>第二：构成东方主战场</t>
+  </si>
+  <si>
+    <t>以巨大民族牺牲支撑起世界反法西斯战争的东方主战场</t>
+  </si>
+  <si>
+    <t>第三：凝聚全球正义力量</t>
+  </si>
+  <si>
+    <t>团结并汇集了国际反对法西斯侵略的正义力量</t>
+  </si>
+  <si>
+    <t>第四：推动国际秩序重建</t>
+  </si>
+  <si>
+    <t>第五：促进民族解放运动</t>
+  </si>
+  <si>
+    <t>鼓舞并加速了世界范围内民族解放运动的兴起</t>
+  </si>
+  <si>
+    <t>个人奋斗与国家前途命运### ###</t>
+  </si>
+  <si>
+    <t>本质是个人理想与社会理想的结合</t>
+  </si>
+  <si>
+    <t>个人目标与国家、民族目标的统一</t>
+  </si>
+  <si>
+    <t>在实现社会理想中完成个人理想</t>
+  </si>
+  <si>
+    <t>第一：个人理想以社会理想为指引</t>
+  </si>
+  <si>
+    <t>社会理想是最根本的，个人理想从属于社会理想</t>
+  </si>
+  <si>
+    <t>个人理想只有与国家前途、民族命运相结合，与社会需要和人民利益相一致，才可能实现</t>
+  </si>
+  <si>
+    <t>第二：社会理想是个人理想的汇聚与升华</t>
+  </si>
+  <si>
+    <t>社会理想的实现依靠全体社会成员的共同努力</t>
+  </si>
+  <si>
+    <t>并体现在每个人实现个人理想的实践中</t>
+  </si>
+  <si>
+    <t>第三：在伟大事业中成就个人理想</t>
+  </si>
+  <si>
+    <t>个人只有将人生理想融入国家和民族事业，才能最终成就事业</t>
+  </si>
+  <si>
+    <t>当代青年的追求不能脱离社会现实，应在实现社会理想的过程中努力实现个人理想</t>
+  </si>
+  <si>
+    <t>如何在推进中国式现代化中发挥个人作用### ###</t>
+  </si>
+  <si>
+    <t>第一，怀爱国之心</t>
+  </si>
+  <si>
+    <t>爱国是最深层持久的情感，是立德之源、立功之本</t>
+  </si>
+  <si>
+    <t>作为民族心魂，爱国是每个中国人的本分与职责，是心之所系、情之所归</t>
+  </si>
+  <si>
+    <t>第二，立报国之志</t>
+  </si>
+  <si>
+    <t>以国家富强、人民幸福为念，将个人小我融入国家大我</t>
+  </si>
+  <si>
+    <t>在为国尽责、为民服务中实现个人价值、展现人生风采</t>
+  </si>
+  <si>
+    <t>第三，增强国之能</t>
+  </si>
+  <si>
+    <t>爱国需落到实处，顺应时代要求，学习新知识、掌握新技能、练就真本领</t>
+  </si>
+  <si>
+    <t>努力成为岗位能手、行家里手，以实干能力践行爱国之志</t>
+  </si>
+  <si>
+    <t>中国式现代化是和平发展的现代化### ###</t>
+  </si>
+  <si>
+    <t>二战的历史教训</t>
+  </si>
+  <si>
+    <t>战火遍及全球，伤亡超一亿人</t>
+  </si>
+  <si>
+    <t>弱肉强食、穷兵黩武、赢者通吃皆非人类共存、和平与发展之道</t>
+  </si>
+  <si>
+    <t>和平需共同维护</t>
+  </si>
+  <si>
+    <t>和平是人类共同事业，需各方共同争取与维护</t>
+  </si>
+  <si>
+    <t>人人珍爱和平、铭记战争教训，和平才有希望</t>
+  </si>
+  <si>
+    <t>面对动荡变革期</t>
+  </si>
+  <si>
+    <t>应不忘《联合国宪章》初心</t>
+  </si>
+  <si>
+    <t>牢记守护和平使命</t>
+  </si>
+  <si>
+    <t>中国的和平发展道路</t>
+  </si>
+  <si>
+    <t>中国式现代化是走和平发展道路的现代化</t>
+  </si>
+  <si>
+    <t>中国始终是世界和平、稳定与进步的力量</t>
+  </si>
+  <si>
+    <t>国际调解院### ###</t>
+  </si>
+  <si>
+    <t>国际法治的创新之举</t>
+  </si>
+  <si>
+    <t>具有重要历史意义</t>
+  </si>
+  <si>
+    <t>践行《联合国宪章》宗旨</t>
+  </si>
+  <si>
+    <t>填补国际调解机制空白</t>
+  </si>
+  <si>
+    <t>是完善全球治理的法治公共产品</t>
+  </si>
+  <si>
+    <t>蕴含和合共生的文明智慧</t>
+  </si>
+  <si>
+    <t>有助于超越零和思维</t>
+  </si>
+  <si>
+    <t>促进国际争议的友好解决</t>
+  </si>
+  <si>
+    <t>彰显兼容并蓄的法治文明</t>
+  </si>
+  <si>
+    <t>尊重当事方意愿</t>
+  </si>
+  <si>
+    <t>具有灵活、经济、便捷、高效的优势</t>
+  </si>
+  <si>
+    <t>与诉讼、仲裁等现有机制互补协同</t>
+  </si>
+  <si>
+    <t>与全球治理倡议高度契合</t>
+  </si>
+  <si>
+    <t>奉行和解合作和谐</t>
+  </si>
+  <si>
+    <t>坚持公平公正公道</t>
+  </si>
+  <si>
+    <t>秉持共商共建共享</t>
+  </si>
+  <si>
+    <t>以人为本，务实导向</t>
+  </si>
+  <si>
+    <t>为构建人类命运共同体注入法治正能量</t>
+  </si>
+  <si>
+    <t>为什么要科技创新与产业创新融合### ###</t>
+  </si>
+  <si>
+    <t>实践是认识的目的</t>
+  </si>
+  <si>
+    <t>认识的获得并非出于猎奇或雅兴</t>
+  </si>
+  <si>
+    <t>最终目的是为实践服务</t>
+  </si>
+  <si>
+    <t>指导实践以满足生活与生产需要</t>
+  </si>
+  <si>
+    <t>认识世界的根本目的在于改造世界</t>
+  </si>
+  <si>
+    <t>科技成果必须从“书架”走向“货架”，转化为实际应用</t>
+  </si>
+  <si>
+    <t>方能实现更美好的生活</t>
+  </si>
+  <si>
+    <t>认识活动中的非理性因素### ###</t>
+  </si>
+  <si>
+    <t>非理性因素的定义与作用</t>
+  </si>
+  <si>
+    <t>主要包括主体的情感与意志</t>
+  </si>
+  <si>
+    <t>广义上也含联想、想象、直觉、灵感等</t>
+  </si>
+  <si>
+    <t>对人的认识能力与活动具有激活与驱动作用</t>
+  </si>
+  <si>
+    <t>科学创新需要两者的结合</t>
+  </si>
+  <si>
+    <t>既需严密的逻辑思维</t>
+  </si>
+  <si>
+    <t>也需发挥灵感、直觉、想象力等非逻辑形式的重要作用</t>
+  </si>
+  <si>
+    <t>继续吸引外资### ###</t>
+  </si>
+  <si>
+    <t>改革开放中利用外资的作用与意义</t>
+  </si>
+  <si>
+    <t>积极利用外资是中国快速融入世界、赶上时代的关键。</t>
+  </si>
+  <si>
+    <t>外资企业是中国现代化、改革开放、创新创造及联通全球的重要参与者。</t>
+  </si>
+  <si>
+    <t>当前继续加大吸引和利用外资力度仍具有重大深远意义。</t>
+  </si>
+  <si>
+    <t>第一，推动经济高质量发展的必然选择</t>
+  </si>
+  <si>
+    <t>有利于引进先进技术与科技人才</t>
+  </si>
+  <si>
+    <t>增强国家创新力与竞争力。</t>
+  </si>
+  <si>
+    <t>第二，扩大高水平对外开放的内在要求</t>
+  </si>
+  <si>
+    <t>有利于对接国际高标准经贸规则</t>
+  </si>
+  <si>
+    <t>扩大自主开放</t>
+  </si>
+  <si>
+    <t>塑造更高水平开放型经济新优势</t>
+  </si>
+  <si>
+    <t>第三，引领经济全球化正确方向的重要动力</t>
+  </si>
+  <si>
+    <t>有利于促进国际投资自由化便利化</t>
+  </si>
+  <si>
+    <t>深化产业链供应链国际合作</t>
+  </si>
+  <si>
+    <t>维护多元稳定的国际经济格局</t>
   </si>
 </sst>
 </file>
@@ -1172,7 +1274,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H97"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="9.66666666666667" style="1"/>
@@ -1182,27 +1284,27 @@
     <row r="1" s="1" customFormat="1" spans="1:8">
       <c r="A1" s="2">
         <f>SUM(B1:AZ1)</f>
-        <v>22.4333333333333</v>
+        <v>28.3166666666667</v>
       </c>
       <c r="B1" s="2">
-        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2192)/COLUMN()</f>
-        <v>9</v>
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B1698)/COLUMN()</f>
+        <v>4</v>
       </c>
       <c r="C1" s="2">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>9.66666666666667</v>
       </c>
       <c r="D1" s="2">
         <f t="shared" si="0"/>
-        <v>1.5</v>
+        <v>14.25</v>
       </c>
       <c r="E1" s="2">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="F1" s="2">
         <f t="shared" si="0"/>
-        <v>0.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="G1" s="2">
         <f t="shared" si="0"/>
@@ -1223,17 +1325,17 @@
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:8">
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:8">
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:8">
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1243,7 +1345,7 @@
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:8">
-      <c r="B7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1258,17 +1360,17 @@
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:8">
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:8">
-      <c r="C11" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:8">
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="1" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1283,248 +1385,418 @@
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:8">
-      <c r="D15" s="1" t="s">
+      <c r="C15" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:8">
-      <c r="E16" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" spans="2:6">
-      <c r="F17" s="1" t="s">
+    <row r="17" s="1" customFormat="1" spans="2:4">
+      <c r="D17" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" spans="2:6">
-      <c r="F18" s="1" t="s">
+    <row r="18" s="1" customFormat="1" spans="2:4">
+      <c r="C18" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" spans="2:6">
+    <row r="19" s="1" customFormat="1" spans="2:4">
       <c r="D19" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" spans="2:6">
-      <c r="E20" s="1" t="s">
+    <row r="20" s="1" customFormat="1" spans="2:4">
+      <c r="D20" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" spans="2:6">
-      <c r="D21" s="1" t="s">
+    <row r="21" s="1" customFormat="1" spans="2:4">
+      <c r="C21" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" spans="2:6">
-      <c r="B22" s="1" t="s">
+    <row r="22" s="1" customFormat="1" spans="2:4">
+      <c r="D22" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" spans="2:6">
-      <c r="C23" s="1" t="s">
+    <row r="23" s="1" customFormat="1" spans="2:4">
+      <c r="D23" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" spans="2:6">
-      <c r="C24" s="1" t="s">
+    <row r="24" s="1" customFormat="1" spans="2:4">
+      <c r="B24" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" spans="2:6">
-      <c r="B25" s="1" t="s">
+    <row r="25" s="1" customFormat="1" spans="2:4">
+      <c r="C25" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" spans="2:6">
-      <c r="C26" s="1" t="s">
+    <row r="26" s="1" customFormat="1" spans="2:4">
+      <c r="D26" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" spans="2:6">
-      <c r="B27" s="1" t="s">
+    <row r="27" s="1" customFormat="1" spans="2:4">
+      <c r="D27" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" spans="2:6">
+    <row r="28" spans="2:4">
       <c r="C28" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" spans="2:6">
-      <c r="C29" s="1" t="s">
+    <row r="29" spans="2:4">
+      <c r="D29" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" spans="2:6">
-      <c r="C30" s="1" t="s">
+    <row r="30" spans="2:4">
+      <c r="D30" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" spans="2:6">
-      <c r="B31" s="1" t="s">
+    <row r="31" spans="2:4">
+      <c r="C31" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="32" s="1" customFormat="1" spans="2:6">
-      <c r="B32" s="1" t="s">
+    <row r="32" spans="2:4">
+      <c r="D32" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="33" s="1" customFormat="1" spans="2:3">
-      <c r="C33" s="1" t="s">
+    <row r="33" spans="2:5">
+      <c r="D33" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" spans="2:3">
-      <c r="C34" s="1" t="s">
+    <row r="34" spans="2:5">
+      <c r="B34" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" spans="2:3">
-      <c r="B35" s="1" t="s">
+    <row r="35" spans="2:5">
+      <c r="C35" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="36" s="1" customFormat="1" spans="2:3">
-      <c r="C36" s="1" t="s">
+    <row r="36" spans="2:5">
+      <c r="D36" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="37" s="1" customFormat="1" spans="2:3">
-      <c r="C37" s="1" t="s">
+    <row r="37" spans="2:5">
+      <c r="D37" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1" spans="2:3">
+    <row r="38" spans="2:5">
       <c r="C38" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="39" s="1" customFormat="1" spans="2:3">
-      <c r="C39" s="1" t="s">
+    <row r="39" spans="2:5">
+      <c r="D39" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="40" s="1" customFormat="1" spans="2:3">
-      <c r="B40" s="1" t="s">
+    <row r="40" spans="2:5">
+      <c r="D40" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="41" s="1" customFormat="1" spans="2:3">
-      <c r="B41" s="1" t="s">
+    <row r="41" spans="2:5">
+      <c r="D41" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="42" s="1" customFormat="1" spans="2:3">
-      <c r="C42" s="1" t="s">
+    <row r="42" spans="2:5">
+      <c r="E42" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="43" s="1" customFormat="1" spans="2:3">
-      <c r="C43" s="1" t="s">
+    <row r="43" spans="2:5">
+      <c r="E43" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="44" s="1" customFormat="1" spans="2:3">
-      <c r="B44" s="1" t="s">
+    <row r="44" spans="2:5">
+      <c r="C44" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="45" s="1" customFormat="1" spans="2:3">
-      <c r="C45" s="1" t="s">
+    <row r="45" spans="2:5">
+      <c r="D45" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="46" s="1" customFormat="1" spans="2:3">
-      <c r="C46" s="1" t="s">
+    <row r="46" spans="2:5">
+      <c r="D46" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="47" s="1" customFormat="1" spans="2:3">
-      <c r="C47" s="1" t="s">
+    <row r="47" spans="2:5">
+      <c r="B47" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="48" s="1" customFormat="1" spans="2:3">
+    <row r="48" spans="2:5">
       <c r="C48" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="49" s="1" customFormat="1" spans="2:5">
-      <c r="B49" s="1" t="s">
+    <row r="49" spans="3:4">
+      <c r="D49" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="50" s="1" customFormat="1" spans="2:5">
-      <c r="B50" s="1" t="s">
+    <row r="50" spans="3:4">
+      <c r="D50" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="51" s="1" customFormat="1" spans="2:5">
-      <c r="C51" s="1" t="s">
+    <row r="51" spans="3:4">
+      <c r="D51" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="52" s="1" customFormat="1" spans="2:5">
-      <c r="C52" s="1" t="s">
+    <row r="52" spans="3:4">
+      <c r="D52" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="53" s="1" customFormat="1" spans="2:5">
+    <row r="53" spans="3:4">
       <c r="C53" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="54" s="1" customFormat="1" spans="2:5">
-      <c r="C54" s="1" t="s">
+    <row r="54" spans="3:4">
+      <c r="D54" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="55" s="1" customFormat="1" spans="2:5">
-      <c r="B55" s="1" t="s">
+    <row r="55" spans="3:4">
+      <c r="D55" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="56" s="1" customFormat="1" spans="2:5">
-      <c r="B56" s="1" t="s">
+    <row r="56" spans="3:4">
+      <c r="C56" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="57" s="1" customFormat="1" spans="2:5">
-      <c r="C57" s="1" t="s">
+    <row r="57" spans="3:4">
+      <c r="D57" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="58" s="1" customFormat="1" spans="2:5">
-      <c r="C58" s="1" t="s">
+    <row r="58" spans="3:4">
+      <c r="D58" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="59" s="1" customFormat="1" spans="2:5">
-      <c r="C59" s="1" t="s">
+    <row r="59" spans="3:4">
+      <c r="D59" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="60" s="1" customFormat="1" spans="2:5">
-      <c r="D60" s="1" t="s">
+    <row r="60" spans="3:4">
+      <c r="C60" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="61" s="1" customFormat="1" spans="2:5">
+    <row r="61" spans="3:4">
       <c r="D61" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="62" s="1" customFormat="1" spans="2:5">
-      <c r="E62" s="1" t="s">
+    <row r="62" spans="3:4">
+      <c r="D62" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="63" s="1" customFormat="1" spans="2:5">
+    <row r="63" spans="3:4">
       <c r="D63" s="1" t="s">
         <v>61</v>
+      </c>
+    </row>
+    <row r="64" spans="3:4">
+      <c r="D64" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4">
+      <c r="D65" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4">
+      <c r="B66" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4">
+      <c r="C67" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4">
+      <c r="D68" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4">
+      <c r="D69" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4">
+      <c r="D70" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4">
+      <c r="C71" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4">
+      <c r="D72" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="73" spans="2:4">
+      <c r="D73" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="74" spans="2:4">
+      <c r="B74" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="75" spans="2:4">
+      <c r="C75" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="76" spans="2:4">
+      <c r="D76" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="77" spans="2:4">
+      <c r="D77" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="78" spans="2:4">
+      <c r="D78" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="79" spans="2:4">
+      <c r="C79" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="80" spans="2:4">
+      <c r="D80" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="81" spans="2:4">
+      <c r="D81" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4">
+      <c r="B82" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="83" spans="2:4">
+      <c r="C83" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="84" spans="2:4">
+      <c r="D84" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="85" spans="2:4">
+      <c r="D85" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="86" spans="2:4">
+      <c r="D86" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="87" spans="2:4">
+      <c r="C87" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="88" spans="2:4">
+      <c r="D88" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="89" spans="2:4">
+      <c r="D89" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="90" spans="2:4">
+      <c r="C90" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="91" spans="2:4">
+      <c r="D91" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="92" spans="2:4">
+      <c r="D92" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="93" spans="2:4">
+      <c r="D93" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="94" spans="2:4">
+      <c r="C94" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="95" spans="2:4">
+      <c r="D95" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="96" spans="2:4">
+      <c r="D96" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="97" spans="4:4">
+      <c r="D97" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/Note/测试.xlsx
+++ b/Note/测试.xlsx
@@ -49,294 +49,297 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
-  <si>
-    <t>抗日对世界发展的意义### ###</t>
-  </si>
-  <si>
-    <t>第一：揭开世界反法西斯战争序幕</t>
-  </si>
-  <si>
-    <t>第二：构成东方主战场</t>
-  </si>
-  <si>
-    <t>以巨大民族牺牲支撑起世界反法西斯战争的东方主战场</t>
-  </si>
-  <si>
-    <t>第三：凝聚全球正义力量</t>
-  </si>
-  <si>
-    <t>团结并汇集了国际反对法西斯侵略的正义力量</t>
-  </si>
-  <si>
-    <t>第四：推动国际秩序重建</t>
-  </si>
-  <si>
-    <t>第五：促进民族解放运动</t>
-  </si>
-  <si>
-    <t>鼓舞并加速了世界范围内民族解放运动的兴起</t>
-  </si>
-  <si>
-    <t>个人奋斗与国家前途命运### ###</t>
-  </si>
-  <si>
-    <t>本质是个人理想与社会理想的结合</t>
-  </si>
-  <si>
-    <t>个人目标与国家、民族目标的统一</t>
-  </si>
-  <si>
-    <t>在实现社会理想中完成个人理想</t>
-  </si>
-  <si>
-    <t>第一：个人理想以社会理想为指引</t>
-  </si>
-  <si>
-    <t>社会理想是最根本的，个人理想从属于社会理想</t>
-  </si>
-  <si>
-    <t>个人理想只有与国家前途、民族命运相结合，与社会需要和人民利益相一致，才可能实现</t>
-  </si>
-  <si>
-    <t>第二：社会理想是个人理想的汇聚与升华</t>
-  </si>
-  <si>
-    <t>社会理想的实现依靠全体社会成员的共同努力</t>
-  </si>
-  <si>
-    <t>并体现在每个人实现个人理想的实践中</t>
-  </si>
-  <si>
-    <t>第三：在伟大事业中成就个人理想</t>
-  </si>
-  <si>
-    <t>个人只有将人生理想融入国家和民族事业，才能最终成就事业</t>
-  </si>
-  <si>
-    <t>当代青年的追求不能脱离社会现实，应在实现社会理想的过程中努力实现个人理想</t>
-  </si>
-  <si>
-    <t>如何在推进中国式现代化中发挥个人作用### ###</t>
-  </si>
-  <si>
-    <t>第一，怀爱国之心</t>
-  </si>
-  <si>
-    <t>爱国是最深层持久的情感，是立德之源、立功之本</t>
-  </si>
-  <si>
-    <t>作为民族心魂，爱国是每个中国人的本分与职责，是心之所系、情之所归</t>
-  </si>
-  <si>
-    <t>第二，立报国之志</t>
-  </si>
-  <si>
-    <t>以国家富强、人民幸福为念，将个人小我融入国家大我</t>
-  </si>
-  <si>
-    <t>在为国尽责、为民服务中实现个人价值、展现人生风采</t>
-  </si>
-  <si>
-    <t>第三，增强国之能</t>
-  </si>
-  <si>
-    <t>爱国需落到实处，顺应时代要求，学习新知识、掌握新技能、练就真本领</t>
-  </si>
-  <si>
-    <t>努力成为岗位能手、行家里手，以实干能力践行爱国之志</t>
-  </si>
-  <si>
-    <t>中国式现代化是和平发展的现代化### ###</t>
-  </si>
-  <si>
-    <t>二战的历史教训</t>
-  </si>
-  <si>
-    <t>战火遍及全球，伤亡超一亿人</t>
-  </si>
-  <si>
-    <t>弱肉强食、穷兵黩武、赢者通吃皆非人类共存、和平与发展之道</t>
-  </si>
-  <si>
-    <t>和平需共同维护</t>
-  </si>
-  <si>
-    <t>和平是人类共同事业，需各方共同争取与维护</t>
-  </si>
-  <si>
-    <t>人人珍爱和平、铭记战争教训，和平才有希望</t>
-  </si>
-  <si>
-    <t>面对动荡变革期</t>
-  </si>
-  <si>
-    <t>应不忘《联合国宪章》初心</t>
-  </si>
-  <si>
-    <t>牢记守护和平使命</t>
-  </si>
-  <si>
-    <t>中国的和平发展道路</t>
-  </si>
-  <si>
-    <t>中国式现代化是走和平发展道路的现代化</t>
-  </si>
-  <si>
-    <t>中国始终是世界和平、稳定与进步的力量</t>
-  </si>
-  <si>
-    <t>国际调解院### ###</t>
-  </si>
-  <si>
-    <t>国际法治的创新之举</t>
-  </si>
-  <si>
-    <t>具有重要历史意义</t>
-  </si>
-  <si>
-    <t>践行《联合国宪章》宗旨</t>
-  </si>
-  <si>
-    <t>填补国际调解机制空白</t>
-  </si>
-  <si>
-    <t>是完善全球治理的法治公共产品</t>
-  </si>
-  <si>
-    <t>蕴含和合共生的文明智慧</t>
-  </si>
-  <si>
-    <t>有助于超越零和思维</t>
-  </si>
-  <si>
-    <t>促进国际争议的友好解决</t>
-  </si>
-  <si>
-    <t>彰显兼容并蓄的法治文明</t>
-  </si>
-  <si>
-    <t>尊重当事方意愿</t>
-  </si>
-  <si>
-    <t>具有灵活、经济、便捷、高效的优势</t>
-  </si>
-  <si>
-    <t>与诉讼、仲裁等现有机制互补协同</t>
-  </si>
-  <si>
-    <t>与全球治理倡议高度契合</t>
-  </si>
-  <si>
-    <t>奉行和解合作和谐</t>
-  </si>
-  <si>
-    <t>坚持公平公正公道</t>
-  </si>
-  <si>
-    <t>秉持共商共建共享</t>
-  </si>
-  <si>
-    <t>以人为本，务实导向</t>
-  </si>
-  <si>
-    <t>为构建人类命运共同体注入法治正能量</t>
-  </si>
-  <si>
-    <t>为什么要科技创新与产业创新融合### ###</t>
-  </si>
-  <si>
-    <t>实践是认识的目的</t>
-  </si>
-  <si>
-    <t>认识的获得并非出于猎奇或雅兴</t>
-  </si>
-  <si>
-    <t>最终目的是为实践服务</t>
-  </si>
-  <si>
-    <t>指导实践以满足生活与生产需要</t>
-  </si>
-  <si>
-    <t>认识世界的根本目的在于改造世界</t>
-  </si>
-  <si>
-    <t>科技成果必须从“书架”走向“货架”，转化为实际应用</t>
-  </si>
-  <si>
-    <t>方能实现更美好的生活</t>
-  </si>
-  <si>
-    <t>认识活动中的非理性因素### ###</t>
-  </si>
-  <si>
-    <t>非理性因素的定义与作用</t>
-  </si>
-  <si>
-    <t>主要包括主体的情感与意志</t>
-  </si>
-  <si>
-    <t>广义上也含联想、想象、直觉、灵感等</t>
-  </si>
-  <si>
-    <t>对人的认识能力与活动具有激活与驱动作用</t>
-  </si>
-  <si>
-    <t>科学创新需要两者的结合</t>
-  </si>
-  <si>
-    <t>既需严密的逻辑思维</t>
-  </si>
-  <si>
-    <t>也需发挥灵感、直觉、想象力等非逻辑形式的重要作用</t>
-  </si>
-  <si>
-    <t>继续吸引外资### ###</t>
-  </si>
-  <si>
-    <t>改革开放中利用外资的作用与意义</t>
-  </si>
-  <si>
-    <t>积极利用外资是中国快速融入世界、赶上时代的关键。</t>
-  </si>
-  <si>
-    <t>外资企业是中国现代化、改革开放、创新创造及联通全球的重要参与者。</t>
-  </si>
-  <si>
-    <t>当前继续加大吸引和利用外资力度仍具有重大深远意义。</t>
-  </si>
-  <si>
-    <t>第一，推动经济高质量发展的必然选择</t>
-  </si>
-  <si>
-    <t>有利于引进先进技术与科技人才</t>
-  </si>
-  <si>
-    <t>增强国家创新力与竞争力。</t>
-  </si>
-  <si>
-    <t>第二，扩大高水平对外开放的内在要求</t>
-  </si>
-  <si>
-    <t>有利于对接国际高标准经贸规则</t>
-  </si>
-  <si>
-    <t>扩大自主开放</t>
-  </si>
-  <si>
-    <t>塑造更高水平开放型经济新优势</t>
-  </si>
-  <si>
-    <t>第三，引领经济全球化正确方向的重要动力</t>
-  </si>
-  <si>
-    <t>有利于促进国际投资自由化便利化</t>
-  </si>
-  <si>
-    <t>深化产业链供应链国际合作</t>
-  </si>
-  <si>
-    <t>维护多元稳定的国际经济格局</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
+  <si>
+    <t>中国的投资价值### ###</t>
+  </si>
+  <si>
+    <t>第一，坚持高水平对外开放</t>
+  </si>
+  <si>
+    <t>对外开放是基本国策</t>
+  </si>
+  <si>
+    <t>正稳步推进规则、规制等制度型开放</t>
+  </si>
+  <si>
+    <t>利用外资政策长期稳定</t>
+  </si>
+  <si>
+    <t>第二，市场潜力巨大且转型加速</t>
+  </si>
+  <si>
+    <t>作为全球第二大消费市场，拥有最大规模中等收入群体</t>
+  </si>
+  <si>
+    <t>绿色化、数字化、智能化转型加快，产业配套强</t>
+  </si>
+  <si>
+    <t>是科技革命与产业变革的最佳应用场景</t>
+  </si>
+  <si>
+    <t>第三，外资法规政策体系健全</t>
+  </si>
+  <si>
+    <t>已形成较为完备的利用外资法规政策与工作体系</t>
+  </si>
+  <si>
+    <t>第四，社会环境安全稳定</t>
+  </si>
+  <si>
+    <t>长期保持政局稳定与社会安定</t>
+  </si>
+  <si>
+    <t>是国际公认的最安全国家之一</t>
+  </si>
+  <si>
+    <t>抗日是持久战### ###</t>
+  </si>
+  <si>
+    <t>战争性质：是半殖民地中国与帝国主义日本之间的决死战争</t>
+  </si>
+  <si>
+    <t>第一方面：强弱对比决定战争形态</t>
+  </si>
+  <si>
+    <t>日本是强国</t>
+  </si>
+  <si>
+    <t>中国是弱国</t>
+  </si>
+  <si>
+    <t>强弱对比决定了抗日战争只能是持久战</t>
+  </si>
+  <si>
+    <t>第二方面：多因素对比决定最终胜利</t>
+  </si>
+  <si>
+    <t>日本是小国，进行退步、野蛮的侵略战争，在国际上失道寡助</t>
+  </si>
+  <si>
+    <t>中国是大国，进行进步、正义的反侵略战争，在国际上得道多助</t>
+  </si>
+  <si>
+    <t>中国已有政治上成熟的中国共产党及其领导的抗日根据地与人民军队</t>
+  </si>
+  <si>
+    <t>因此，最后胜利必将属于中国。</t>
+  </si>
+  <si>
+    <t>敌后战场的作用### ###</t>
+  </si>
+  <si>
+    <t>决策内容与意义</t>
+  </si>
+  <si>
+    <t>为执行全面抗战路线，作出开辟敌后战场的决策</t>
+  </si>
+  <si>
+    <t>延续农村包围城市、武装夺取政权的道路</t>
+  </si>
+  <si>
+    <t>敌后战场的坚持与发展为抗战胜利作出巨大贡献</t>
+  </si>
+  <si>
+    <t>起到改变战局的战略引领作用</t>
+  </si>
+  <si>
+    <t>敌后战场在各阶段的作用</t>
+  </si>
+  <si>
+    <t>战略防御阶段</t>
+  </si>
+  <si>
+    <t>正面战场为主战场</t>
+  </si>
+  <si>
+    <t>敌后战场是重要力量</t>
+  </si>
+  <si>
+    <t>推动战争转入相持阶段，实现持久抗战</t>
+  </si>
+  <si>
+    <t>战略相持阶段</t>
+  </si>
+  <si>
+    <t>敌后战场逐渐成为主战场</t>
+  </si>
+  <si>
+    <t>极大振奋全国信心</t>
+  </si>
+  <si>
+    <t>展现人民战争的强大威力</t>
+  </si>
+  <si>
+    <t>战略反攻阶段</t>
+  </si>
+  <si>
+    <t>敌后战场成为决胜力量</t>
+  </si>
+  <si>
+    <t>总结</t>
+  </si>
+  <si>
+    <t>中国共产党领导的人民武装在敌后战场发展壮大，由弱变强</t>
+  </si>
+  <si>
+    <t>为夺取最后胜利发挥决定性作用</t>
+  </si>
+  <si>
+    <t>崇尚英雄### ###</t>
+  </si>
+  <si>
+    <t>伟大时代与英雄精神</t>
+  </si>
+  <si>
+    <t>伟大时代呼唤并造就英雄，英雄辈出推动党和人民事业兴旺发达</t>
+  </si>
+  <si>
+    <t>崇尚英雄才能产生英雄，争做英雄方能英雄辈出</t>
+  </si>
+  <si>
+    <t>英雄精神对民族复兴的意义</t>
+  </si>
+  <si>
+    <t>国家强盛与民族复兴既需物质积累，亦需精神文明升华</t>
+  </si>
+  <si>
+    <t>缅怀英烈事迹、传承英烈精神是对价值观的洗礼</t>
+  </si>
+  <si>
+    <t>可转化为爱国情、强国志、报国行的内生动力</t>
+  </si>
+  <si>
+    <t>纪念活动的现实作用</t>
+  </si>
+  <si>
+    <t>在烈士纪念日追思先烈、致敬英雄，有助于增强历史自信、激扬历史主动精神</t>
+  </si>
+  <si>
+    <t>使爱国主义与革命英雄主义成为引领向前、催人奋斗的强大精神动力</t>
+  </si>
+  <si>
+    <t>做堂堂正正光荣自豪的中国人### ###</t>
+  </si>
+  <si>
+    <t>一、‘堂堂正正’的民族气节</t>
+  </si>
+  <si>
+    <t>中华民族在磨难中愈挫愈勇、奋起成长</t>
+  </si>
+  <si>
+    <t>‘堂堂正正’体现为</t>
+  </si>
+  <si>
+    <t>危难中不甘屈辱</t>
+  </si>
+  <si>
+    <t>敢于斗争的精神坚守与担当</t>
+  </si>
+  <si>
+    <t>这种姿态是百年风雨淬炼出的民族气质</t>
+  </si>
+  <si>
+    <t>是亿万中国人的血脉共鸣与心灵选择</t>
+  </si>
+  <si>
+    <t>二、‘光荣自豪’的从容自信</t>
+  </si>
+  <si>
+    <t>体现为</t>
+  </si>
+  <si>
+    <t>面对压力有信心</t>
+  </si>
+  <si>
+    <t>应对挑战有定力</t>
+  </si>
+  <si>
+    <t>面向世界有风采</t>
+  </si>
+  <si>
+    <t>这是一种</t>
+  </si>
+  <si>
+    <t>基于历史与文化自信的</t>
+  </si>
+  <si>
+    <t>从容理性、不卑不亢、开放包容的胸怀</t>
+  </si>
+  <si>
+    <t>根植于</t>
+  </si>
+  <si>
+    <t>文明传统</t>
+  </si>
+  <si>
+    <t>中国特色社会主义实践</t>
+  </si>
+  <si>
+    <t>当代青年作为‘平视世界’的一代</t>
+  </si>
+  <si>
+    <t>应在更广阔舞台上</t>
+  </si>
+  <si>
+    <t>展现昂扬风貌</t>
+  </si>
+  <si>
+    <t>续写时代荣光</t>
+  </si>
+  <si>
+    <t>正确二战史观### ###</t>
+  </si>
+  <si>
+    <t>坚持正确二战史观、捍卫历史正义</t>
+  </si>
+  <si>
+    <t>既是对历史的总结</t>
+  </si>
+  <si>
+    <t>也是对未来的指引</t>
+  </si>
+  <si>
+    <t>第一，汲取历史教训的现实需要</t>
+  </si>
+  <si>
+    <t>历史是教科书与清醒剂</t>
+  </si>
+  <si>
+    <t>坚持正确史观，引导国际社会系统反思二战</t>
+  </si>
+  <si>
+    <t>（对西方）抵制否定成果、歪曲真相的错误思潮</t>
+  </si>
+  <si>
+    <t>（对日本）警惕军国主义，防止悲剧重演</t>
+  </si>
+  <si>
+    <t>第二，凝聚历史共识的现实需要</t>
+  </si>
+  <si>
+    <t>铭记历史是为共同引以为戒</t>
+  </si>
+  <si>
+    <t>形成关于反法西斯战争的正确历史认知与国际共识</t>
+  </si>
+  <si>
+    <t>有助于为建设公正、合理的美好世界奠定思想基础</t>
+  </si>
+  <si>
+    <t>第三，把握发展趋势的现实需要</t>
+  </si>
+  <si>
+    <t>当前国际形势变乱交织</t>
+  </si>
+  <si>
+    <t>需弘扬正确二战史观</t>
+  </si>
+  <si>
+    <t>深刻认识践行真正多边主义、维护国际规则与秩序的重要性</t>
+  </si>
+  <si>
+    <t>把握国际秩序发展前景，推动‘全球倡议’落实</t>
   </si>
 </sst>
 </file>
@@ -1274,7 +1277,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H97"/>
+  <dimension ref="A1:H98"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="9.66666666666667" style="1"/>
@@ -1284,27 +1287,27 @@
     <row r="1" s="1" customFormat="1" spans="1:8">
       <c r="A1" s="2">
         <f>SUM(B1:AZ1)</f>
-        <v>28.3166666666667</v>
+        <v>26.3666666666667</v>
       </c>
       <c r="B1" s="2">
         <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B1698)/COLUMN()</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1" s="2">
         <f t="shared" si="0"/>
-        <v>9.66666666666667</v>
+        <v>7.33333333333333</v>
       </c>
       <c r="D1" s="2">
         <f t="shared" si="0"/>
-        <v>14.25</v>
+        <v>11.5</v>
       </c>
       <c r="E1" s="2">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>4.2</v>
       </c>
       <c r="F1" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="G1" s="2">
         <f t="shared" si="0"/>
@@ -1330,7 +1333,7 @@
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:8">
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1340,22 +1343,22 @@
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:8">
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:8">
-      <c r="D7" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:8">
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:8">
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1365,12 +1368,12 @@
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:8">
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:8">
-      <c r="C12" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1380,147 +1383,147 @@
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:8">
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:8">
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:8">
-      <c r="D16" s="1" t="s">
+      <c r="B16" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" spans="2:4">
-      <c r="D17" s="1" t="s">
+    <row r="17" s="1" customFormat="1" spans="2:5">
+      <c r="C17" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" spans="2:4">
+    <row r="18" s="1" customFormat="1" spans="2:5">
       <c r="C18" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" spans="2:4">
+    <row r="19" s="1" customFormat="1" spans="2:5">
       <c r="D19" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" spans="2:4">
+    <row r="20" s="1" customFormat="1" spans="2:5">
       <c r="D20" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" spans="2:4">
-      <c r="C21" s="1" t="s">
+    <row r="21" s="1" customFormat="1" spans="2:5">
+      <c r="D21" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" spans="2:4">
-      <c r="D22" s="1" t="s">
+    <row r="22" s="1" customFormat="1" spans="2:5">
+      <c r="C22" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" spans="2:4">
+    <row r="23" s="1" customFormat="1" spans="2:5">
       <c r="D23" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" spans="2:4">
-      <c r="B24" s="1" t="s">
+    <row r="24" s="1" customFormat="1" spans="2:5">
+      <c r="D24" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" spans="2:4">
-      <c r="C25" s="1" t="s">
+    <row r="25" s="1" customFormat="1" spans="2:5">
+      <c r="D25" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" spans="2:4">
-      <c r="D26" s="1" t="s">
+    <row r="26" s="1" customFormat="1" spans="2:5">
+      <c r="C26" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" spans="2:4">
-      <c r="D27" s="1" t="s">
+    <row r="27" s="1" customFormat="1" spans="2:5">
+      <c r="B27" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="2:4">
+    <row r="28" spans="2:5">
       <c r="C28" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="2:4">
+    <row r="29" spans="2:5">
       <c r="D29" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="2:4">
-      <c r="D30" s="1" t="s">
+    <row r="30" spans="2:5">
+      <c r="E30" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="2:4">
-      <c r="C31" s="1" t="s">
+    <row r="31" spans="2:5">
+      <c r="D31" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:4">
-      <c r="D32" s="1" t="s">
+    <row r="32" spans="2:5">
+      <c r="E32" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="33" spans="2:5">
-      <c r="D33" s="1" t="s">
+      <c r="C33" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="34" spans="2:5">
-      <c r="B34" s="1" t="s">
+      <c r="D34" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="35" spans="2:5">
-      <c r="C35" s="1" t="s">
+      <c r="E35" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="36" spans="2:5">
-      <c r="D36" s="1" t="s">
+      <c r="E36" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="37" spans="2:5">
-      <c r="D37" s="1" t="s">
+      <c r="E37" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="38" spans="2:5">
-      <c r="C38" s="1" t="s">
+      <c r="D38" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="39" spans="2:5">
-      <c r="D39" s="1" t="s">
+      <c r="E39" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="40" spans="2:5">
-      <c r="D40" s="1" t="s">
+      <c r="E40" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="41" spans="2:5">
-      <c r="D41" s="1" t="s">
+      <c r="E41" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="42" spans="2:5">
-      <c r="E42" s="1" t="s">
+      <c r="D42" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1554,173 +1557,173 @@
         <v>46</v>
       </c>
     </row>
-    <row r="49" spans="3:4">
+    <row r="49" spans="2:5">
       <c r="D49" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="50" spans="3:4">
+    <row r="50" spans="2:5">
       <c r="D50" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="51" spans="3:4">
-      <c r="D51" s="1" t="s">
+    <row r="51" spans="2:5">
+      <c r="C51" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="52" spans="3:4">
+    <row r="52" spans="2:5">
       <c r="D52" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="53" spans="3:4">
-      <c r="C53" s="1" t="s">
+    <row r="53" spans="2:5">
+      <c r="D53" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="54" spans="3:4">
-      <c r="D54" s="1" t="s">
+    <row r="54" spans="2:5">
+      <c r="E54" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="3:4">
-      <c r="D55" s="1" t="s">
+    <row r="55" spans="2:5">
+      <c r="C55" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="56" spans="3:4">
-      <c r="C56" s="1" t="s">
+    <row r="56" spans="2:5">
+      <c r="D56" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="57" spans="3:4">
+    <row r="57" spans="2:5">
       <c r="D57" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="58" spans="3:4">
-      <c r="D58" s="1" t="s">
+    <row r="58" spans="2:5">
+      <c r="B58" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="59" spans="3:4">
-      <c r="D59" s="1" t="s">
+    <row r="59" spans="2:5">
+      <c r="C59" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="60" spans="3:4">
-      <c r="C60" s="1" t="s">
+    <row r="60" spans="2:5">
+      <c r="D60" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="61" spans="3:4">
+    <row r="61" spans="2:5">
       <c r="D61" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="62" spans="3:4">
-      <c r="D62" s="1" t="s">
+    <row r="62" spans="2:5">
+      <c r="E62" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="63" spans="3:4">
-      <c r="D63" s="1" t="s">
+    <row r="63" spans="2:5">
+      <c r="E63" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="3:4">
+    <row r="64" spans="2:5">
       <c r="D64" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="65" spans="2:4">
+    <row r="65" spans="3:6">
       <c r="D65" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="66" spans="2:4">
-      <c r="B66" s="1" t="s">
+    <row r="66" spans="3:6">
+      <c r="C66" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="67" spans="2:4">
-      <c r="C67" s="1" t="s">
+    <row r="67" spans="3:6">
+      <c r="D67" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="68" spans="2:4">
-      <c r="D68" s="1" t="s">
+    <row r="68" spans="3:6">
+      <c r="E68" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="69" spans="2:4">
-      <c r="D69" s="1" t="s">
+    <row r="69" spans="3:6">
+      <c r="E69" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="70" spans="2:4">
-      <c r="D70" s="1" t="s">
+    <row r="70" spans="3:6">
+      <c r="E70" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="71" spans="2:4">
-      <c r="C71" s="1" t="s">
+    <row r="71" spans="3:6">
+      <c r="D71" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="2:4">
-      <c r="D72" s="1" t="s">
+    <row r="72" spans="3:6">
+      <c r="E72" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="73" spans="2:4">
-      <c r="D73" s="1" t="s">
+    <row r="73" spans="3:6">
+      <c r="E73" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="74" spans="2:4">
-      <c r="B74" s="1" t="s">
+    <row r="74" spans="3:6">
+      <c r="E74" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="75" spans="2:4">
-      <c r="C75" s="1" t="s">
+    <row r="75" spans="3:6">
+      <c r="F75" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="76" spans="2:4">
-      <c r="D76" s="1" t="s">
+    <row r="76" spans="3:6">
+      <c r="F76" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="77" spans="2:4">
+    <row r="77" spans="3:6">
       <c r="D77" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="78" spans="2:4">
-      <c r="D78" s="1" t="s">
+    <row r="78" spans="3:6">
+      <c r="E78" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="79" spans="2:4">
-      <c r="C79" s="1" t="s">
+    <row r="79" spans="3:6">
+      <c r="E79" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="80" spans="2:4">
-      <c r="D80" s="1" t="s">
+    <row r="80" spans="3:6">
+      <c r="E80" s="1" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="81" spans="2:4">
-      <c r="D81" s="1" t="s">
+      <c r="B81" s="1" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="82" spans="2:4">
-      <c r="B82" s="1" t="s">
+      <c r="C82" s="1" t="s">
         <v>80</v>
       </c>
     </row>
@@ -1730,12 +1733,12 @@
       </c>
     </row>
     <row r="84" spans="2:4">
-      <c r="D84" s="1" t="s">
+      <c r="C84" s="1" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="85" spans="2:4">
-      <c r="D85" s="1" t="s">
+      <c r="C85" s="1" t="s">
         <v>83</v>
       </c>
     </row>
@@ -1745,7 +1748,7 @@
       </c>
     </row>
     <row r="87" spans="2:4">
-      <c r="C87" s="1" t="s">
+      <c r="D87" s="1" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1797,6 +1800,11 @@
     <row r="97" spans="4:4">
       <c r="D97" s="1" t="s">
         <v>95</v>
+      </c>
+    </row>
+    <row r="98" spans="4:4">
+      <c r="D98" s="1" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/Note/测试.xlsx
+++ b/Note/测试.xlsx
@@ -49,297 +49,172 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
-  <si>
-    <t>中国的投资价值### ###</t>
-  </si>
-  <si>
-    <t>第一，坚持高水平对外开放</t>
-  </si>
-  <si>
-    <t>对外开放是基本国策</t>
-  </si>
-  <si>
-    <t>正稳步推进规则、规制等制度型开放</t>
-  </si>
-  <si>
-    <t>利用外资政策长期稳定</t>
-  </si>
-  <si>
-    <t>第二，市场潜力巨大且转型加速</t>
-  </si>
-  <si>
-    <t>作为全球第二大消费市场，拥有最大规模中等收入群体</t>
-  </si>
-  <si>
-    <t>绿色化、数字化、智能化转型加快，产业配套强</t>
-  </si>
-  <si>
-    <t>是科技革命与产业变革的最佳应用场景</t>
-  </si>
-  <si>
-    <t>第三，外资法规政策体系健全</t>
-  </si>
-  <si>
-    <t>已形成较为完备的利用外资法规政策与工作体系</t>
-  </si>
-  <si>
-    <t>第四，社会环境安全稳定</t>
-  </si>
-  <si>
-    <t>长期保持政局稳定与社会安定</t>
-  </si>
-  <si>
-    <t>是国际公认的最安全国家之一</t>
-  </si>
-  <si>
-    <t>抗日是持久战### ###</t>
-  </si>
-  <si>
-    <t>战争性质：是半殖民地中国与帝国主义日本之间的决死战争</t>
-  </si>
-  <si>
-    <t>第一方面：强弱对比决定战争形态</t>
-  </si>
-  <si>
-    <t>日本是强国</t>
-  </si>
-  <si>
-    <t>中国是弱国</t>
-  </si>
-  <si>
-    <t>强弱对比决定了抗日战争只能是持久战</t>
-  </si>
-  <si>
-    <t>第二方面：多因素对比决定最终胜利</t>
-  </si>
-  <si>
-    <t>日本是小国，进行退步、野蛮的侵略战争，在国际上失道寡助</t>
-  </si>
-  <si>
-    <t>中国是大国，进行进步、正义的反侵略战争，在国际上得道多助</t>
-  </si>
-  <si>
-    <t>中国已有政治上成熟的中国共产党及其领导的抗日根据地与人民军队</t>
-  </si>
-  <si>
-    <t>因此，最后胜利必将属于中国。</t>
-  </si>
-  <si>
-    <t>敌后战场的作用### ###</t>
-  </si>
-  <si>
-    <t>决策内容与意义</t>
-  </si>
-  <si>
-    <t>为执行全面抗战路线，作出开辟敌后战场的决策</t>
-  </si>
-  <si>
-    <t>延续农村包围城市、武装夺取政权的道路</t>
-  </si>
-  <si>
-    <t>敌后战场的坚持与发展为抗战胜利作出巨大贡献</t>
-  </si>
-  <si>
-    <t>起到改变战局的战略引领作用</t>
-  </si>
-  <si>
-    <t>敌后战场在各阶段的作用</t>
-  </si>
-  <si>
-    <t>战略防御阶段</t>
-  </si>
-  <si>
-    <t>正面战场为主战场</t>
-  </si>
-  <si>
-    <t>敌后战场是重要力量</t>
-  </si>
-  <si>
-    <t>推动战争转入相持阶段，实现持久抗战</t>
-  </si>
-  <si>
-    <t>战略相持阶段</t>
-  </si>
-  <si>
-    <t>敌后战场逐渐成为主战场</t>
-  </si>
-  <si>
-    <t>极大振奋全国信心</t>
-  </si>
-  <si>
-    <t>展现人民战争的强大威力</t>
-  </si>
-  <si>
-    <t>战略反攻阶段</t>
-  </si>
-  <si>
-    <t>敌后战场成为决胜力量</t>
-  </si>
-  <si>
-    <t>总结</t>
-  </si>
-  <si>
-    <t>中国共产党领导的人民武装在敌后战场发展壮大，由弱变强</t>
-  </si>
-  <si>
-    <t>为夺取最后胜利发挥决定性作用</t>
-  </si>
-  <si>
-    <t>崇尚英雄### ###</t>
-  </si>
-  <si>
-    <t>伟大时代与英雄精神</t>
-  </si>
-  <si>
-    <t>伟大时代呼唤并造就英雄，英雄辈出推动党和人民事业兴旺发达</t>
-  </si>
-  <si>
-    <t>崇尚英雄才能产生英雄，争做英雄方能英雄辈出</t>
-  </si>
-  <si>
-    <t>英雄精神对民族复兴的意义</t>
-  </si>
-  <si>
-    <t>国家强盛与民族复兴既需物质积累，亦需精神文明升华</t>
-  </si>
-  <si>
-    <t>缅怀英烈事迹、传承英烈精神是对价值观的洗礼</t>
-  </si>
-  <si>
-    <t>可转化为爱国情、强国志、报国行的内生动力</t>
-  </si>
-  <si>
-    <t>纪念活动的现实作用</t>
-  </si>
-  <si>
-    <t>在烈士纪念日追思先烈、致敬英雄，有助于增强历史自信、激扬历史主动精神</t>
-  </si>
-  <si>
-    <t>使爱国主义与革命英雄主义成为引领向前、催人奋斗的强大精神动力</t>
-  </si>
-  <si>
-    <t>做堂堂正正光荣自豪的中国人### ###</t>
-  </si>
-  <si>
-    <t>一、‘堂堂正正’的民族气节</t>
-  </si>
-  <si>
-    <t>中华民族在磨难中愈挫愈勇、奋起成长</t>
-  </si>
-  <si>
-    <t>‘堂堂正正’体现为</t>
-  </si>
-  <si>
-    <t>危难中不甘屈辱</t>
-  </si>
-  <si>
-    <t>敢于斗争的精神坚守与担当</t>
-  </si>
-  <si>
-    <t>这种姿态是百年风雨淬炼出的民族气质</t>
-  </si>
-  <si>
-    <t>是亿万中国人的血脉共鸣与心灵选择</t>
-  </si>
-  <si>
-    <t>二、‘光荣自豪’的从容自信</t>
-  </si>
-  <si>
-    <t>体现为</t>
-  </si>
-  <si>
-    <t>面对压力有信心</t>
-  </si>
-  <si>
-    <t>应对挑战有定力</t>
-  </si>
-  <si>
-    <t>面向世界有风采</t>
-  </si>
-  <si>
-    <t>这是一种</t>
-  </si>
-  <si>
-    <t>基于历史与文化自信的</t>
-  </si>
-  <si>
-    <t>从容理性、不卑不亢、开放包容的胸怀</t>
-  </si>
-  <si>
-    <t>根植于</t>
-  </si>
-  <si>
-    <t>文明传统</t>
-  </si>
-  <si>
-    <t>中国特色社会主义实践</t>
-  </si>
-  <si>
-    <t>当代青年作为‘平视世界’的一代</t>
-  </si>
-  <si>
-    <t>应在更广阔舞台上</t>
-  </si>
-  <si>
-    <t>展现昂扬风貌</t>
-  </si>
-  <si>
-    <t>续写时代荣光</t>
-  </si>
-  <si>
-    <t>正确二战史观### ###</t>
-  </si>
-  <si>
-    <t>坚持正确二战史观、捍卫历史正义</t>
-  </si>
-  <si>
-    <t>既是对历史的总结</t>
-  </si>
-  <si>
-    <t>也是对未来的指引</t>
-  </si>
-  <si>
-    <t>第一，汲取历史教训的现实需要</t>
-  </si>
-  <si>
-    <t>历史是教科书与清醒剂</t>
-  </si>
-  <si>
-    <t>坚持正确史观，引导国际社会系统反思二战</t>
-  </si>
-  <si>
-    <t>（对西方）抵制否定成果、歪曲真相的错误思潮</t>
-  </si>
-  <si>
-    <t>（对日本）警惕军国主义，防止悲剧重演</t>
-  </si>
-  <si>
-    <t>第二，凝聚历史共识的现实需要</t>
-  </si>
-  <si>
-    <t>铭记历史是为共同引以为戒</t>
-  </si>
-  <si>
-    <t>形成关于反法西斯战争的正确历史认知与国际共识</t>
-  </si>
-  <si>
-    <t>有助于为建设公正、合理的美好世界奠定思想基础</t>
-  </si>
-  <si>
-    <t>第三，把握发展趋势的现实需要</t>
-  </si>
-  <si>
-    <t>当前国际形势变乱交织</t>
-  </si>
-  <si>
-    <t>需弘扬正确二战史观</t>
-  </si>
-  <si>
-    <t>深刻认识践行真正多边主义、维护国际规则与秩序的重要性</t>
-  </si>
-  <si>
-    <t>把握国际秩序发展前景，推动‘全球倡议’落实</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+  <si>
+    <t>如何认识关税战、贸易战### ###</t>
+  </si>
+  <si>
+    <t>一、基本论断：贸易战与保护主义的后果</t>
+  </si>
+  <si>
+    <t>总体定性</t>
+  </si>
+  <si>
+    <t>贸易战、关税战没有赢家</t>
+  </si>
+  <si>
+    <t>保护主义没有出路</t>
+  </si>
+  <si>
+    <t>二、对美国关税行为的指控</t>
+  </si>
+  <si>
+    <t>行为概述：美国以各种借口宣布对包括中国在内的所有贸易伙伴滥施关税</t>
+  </si>
+  <si>
+    <t>行为的四重“严重”危害</t>
+  </si>
+  <si>
+    <t>侵犯权益：严重侵犯各国正当权益</t>
+  </si>
+  <si>
+    <t>违反规则：严重违反世界贸易组织规则</t>
+  </si>
+  <si>
+    <t>损害体制：严重损害以规则为基础的多边贸易体制</t>
+  </si>
+  <si>
+    <t>冲击秩序：严重冲击全球经济秩序稳定</t>
+  </si>
+  <si>
+    <t>三、对美国行为本质的分析</t>
+  </si>
+  <si>
+    <t>违背基本规律与原则：美国有关做法违背基本经济规律和市场原则</t>
+  </si>
+  <si>
+    <t>三“无视”的行径特征</t>
+  </si>
+  <si>
+    <t>罔顾平衡：罔顾多边贸易谈判达成的利益平衡结果</t>
+  </si>
+  <si>
+    <t>无视事实：无视美国长期从国际贸易中大量获利的事实</t>
+  </si>
+  <si>
+    <t>滥用工具：将关税作为实施极限施压、谋取私利的武器</t>
+  </si>
+  <si>
+    <t>行为的根本定性：这是典型的单边主义、保护主义和经济霸凌行径</t>
+  </si>
+  <si>
+    <t>旗号与本质的矛盾</t>
+  </si>
+  <si>
+    <t>旗号：美国打着所谓追求“对等”“公平”的旗号</t>
+  </si>
+  <si>
+    <t>实质</t>
+  </si>
+  <si>
+    <t>搞零和博弈：搞零和博弈</t>
+  </si>
+  <si>
+    <t>追求“美国优先”：本质上是追求“美国优先”“美国特殊”</t>
+  </si>
+  <si>
+    <t>四、对全球化趋势的研判与展望</t>
+  </si>
+  <si>
+    <t>当今世界的现实：当今世界是经济全球化塑造的世界</t>
+  </si>
+  <si>
+    <t>共同的职责：维护健康的国际经贸秩序和全球产供链安全稳定，是各方共同的职责</t>
+  </si>
+  <si>
+    <t>保护主义的局限性：保护主义改变不了经济全球化大势</t>
+  </si>
+  <si>
+    <t>未来的必然趋势</t>
+  </si>
+  <si>
+    <t>必由之路：经济全球化始终是人类社会前进的必由之路</t>
+  </si>
+  <si>
+    <t>时代潮流：不可逆转的时代潮流</t>
+  </si>
+  <si>
+    <t>为什么要倡导普惠包容的经济全球化### ###</t>
+  </si>
+  <si>
+    <t>一、普惠的经济全球化</t>
+  </si>
+  <si>
+    <t>核心目标：处理好发展与分配
+：做大并分好经济发展的“蛋糕”</t>
+  </si>
+  <si>
+    <t>确保广泛参与与共享</t>
+  </si>
+  <si>
+    <t>参与主体：让不同国家、不同阶层、不同人群都能参与</t>
+  </si>
+  <si>
+    <t>享有成果：并享有经济社会发展的成果</t>
+  </si>
+  <si>
+    <t>解决关键问题：妥善解决国家间和各国内部发展失衡问题</t>
+  </si>
+  <si>
+    <t>最终愿景：实现共同发展、共同繁荣</t>
+  </si>
+  <si>
+    <t>二、包容的经济全球化</t>
+  </si>
+  <si>
+    <t>尊重发展道路多样性：支持各国走出符合自身国情的发展道路</t>
+  </si>
+  <si>
+    <t>反对单一与排他</t>
+  </si>
+  <si>
+    <t>反对模式单一：不搞发展模式的单一化</t>
+  </si>
+  <si>
+    <t>摒弃错误主义：摒弃损人利己的单边主义、保护主义</t>
+  </si>
+  <si>
+    <t>维护经济系统稳定与活力</t>
+  </si>
+  <si>
+    <t>稳定供应链：维护全球产业链供应链的稳定畅通</t>
+  </si>
+  <si>
+    <t>保持增长动力：保持世界经济增长活力与动力</t>
+  </si>
+  <si>
+    <t>三、普惠包容全球化的性质与中国角色</t>
+  </si>
+  <si>
+    <t>根本定位：普惠包容全球化是人心所向、人间正道</t>
+  </si>
+  <si>
+    <t>中国倡导的现实意义：具有针对性：中国倡导并推动此举，有着现实针对性和战略指导性</t>
+  </si>
+  <si>
+    <t>中国的引领与贡献</t>
+  </si>
+  <si>
+    <t>引领方向：将引领经济全球化正确方向</t>
+  </si>
+  <si>
+    <t>贡献智慧：为解决当今世界面临的一系列重大问题和挑战贡献中国智慧</t>
+  </si>
+  <si>
+    <t>提供依托：为构建人类命运共同体提供坚实依托</t>
+  </si>
+  <si>
+    <t>总体评价：普惠包容全球化具有重要深远意义</t>
   </si>
 </sst>
 </file>
@@ -956,14 +831,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1277,33 +1155,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H98"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <dimension ref="A1:J56"/>
+  <sheetFormatPr defaultColWidth="9.66666666666667" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.66666666666667" style="1"/>
-    <col min="2" max="16384" width="8.88888888888889" style="1"/>
+    <col min="1" max="16384" width="9.66666666666667" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:8">
+    <row r="1" s="1" customFormat="1" spans="1:10">
       <c r="A1" s="2">
         <f>SUM(B1:AZ1)</f>
-        <v>26.3666666666667</v>
+        <v>13.65</v>
       </c>
       <c r="B1" s="2">
-        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B1698)/COLUMN()</f>
-        <v>3</v>
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2220)/COLUMN()</f>
+        <v>1</v>
       </c>
       <c r="C1" s="2">
         <f t="shared" si="0"/>
-        <v>7.33333333333333</v>
+        <v>2.66666666666667</v>
       </c>
       <c r="D1" s="2">
         <f t="shared" si="0"/>
-        <v>11.5</v>
+        <v>5.25</v>
       </c>
       <c r="E1" s="2">
         <f t="shared" si="0"/>
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="F1" s="2">
         <f t="shared" si="0"/>
@@ -1317,494 +1194,429 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:8">
-      <c r="A2" s="1" t="str" cm="1">
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:10">
+      <c r="A2" s="3" t="str" cm="1">
         <f ca="1" t="array" ref="A2">_wpsfn.SHEETSNAME(A1)</f>
         <v>待处理</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:8">
-      <c r="C3" s="1" t="s">
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:10">
+      <c r="A3" s="3"/>
+      <c r="B3"/>
+      <c r="C3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:8">
-      <c r="D4" s="1" t="s">
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+      <c r="H3"/>
+      <c r="I3"/>
+      <c r="J3"/>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:10">
+      <c r="A4" s="3"/>
+      <c r="B4"/>
+      <c r="C4"/>
+      <c r="D4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:8">
-      <c r="D5" s="1" t="s">
+      <c r="E4"/>
+      <c r="F4"/>
+      <c r="G4"/>
+      <c r="H4"/>
+      <c r="I4"/>
+      <c r="J4"/>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:10">
+      <c r="A5" s="3"/>
+      <c r="B5"/>
+      <c r="C5"/>
+      <c r="D5"/>
+      <c r="E5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:8">
-      <c r="D6" s="1" t="s">
+      <c r="F5"/>
+      <c r="G5"/>
+      <c r="H5"/>
+      <c r="I5"/>
+      <c r="J5"/>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:10">
+      <c r="A6" s="3"/>
+      <c r="B6"/>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:8">
-      <c r="C7" s="1" t="s">
+      <c r="F6"/>
+      <c r="G6"/>
+      <c r="H6"/>
+      <c r="I6"/>
+      <c r="J6"/>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:10">
+      <c r="A7" s="3"/>
+      <c r="B7"/>
+      <c r="C7" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:8">
-      <c r="D8" s="1" t="s">
+      <c r="D7"/>
+      <c r="E7"/>
+      <c r="F7"/>
+      <c r="G7"/>
+      <c r="H7"/>
+      <c r="I7"/>
+      <c r="J7"/>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:10">
+      <c r="A8" s="3"/>
+      <c r="B8"/>
+      <c r="C8"/>
+      <c r="D8" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:8">
-      <c r="D9" s="1" t="s">
+      <c r="E8"/>
+      <c r="F8"/>
+      <c r="G8"/>
+      <c r="H8"/>
+      <c r="I8"/>
+      <c r="J8"/>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:10">
+      <c r="A9" s="3"/>
+      <c r="B9"/>
+      <c r="C9"/>
+      <c r="D9" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:8">
-      <c r="D10" s="1" t="s">
+      <c r="E9"/>
+      <c r="F9"/>
+      <c r="G9"/>
+      <c r="H9"/>
+      <c r="I9"/>
+      <c r="J9"/>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:10">
+      <c r="A10" s="3"/>
+      <c r="B10"/>
+      <c r="C10"/>
+      <c r="D10"/>
+      <c r="E10" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:8">
-      <c r="C11" s="1" t="s">
+      <c r="F10"/>
+      <c r="G10"/>
+      <c r="H10"/>
+      <c r="I10"/>
+      <c r="J10"/>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:10">
+      <c r="A11" s="3"/>
+      <c r="B11"/>
+      <c r="C11"/>
+      <c r="D11"/>
+      <c r="E11" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:8">
-      <c r="D12" s="1" t="s">
+      <c r="F11"/>
+      <c r="G11"/>
+      <c r="H11"/>
+      <c r="I11"/>
+      <c r="J11"/>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:10">
+      <c r="A12" s="3"/>
+      <c r="B12"/>
+      <c r="C12"/>
+      <c r="D12"/>
+      <c r="E12" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:8">
-      <c r="C13" s="1" t="s">
+      <c r="F12"/>
+      <c r="G12"/>
+      <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12"/>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:10">
+      <c r="A13" s="3"/>
+      <c r="B13"/>
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="E13" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:8">
-      <c r="D14" s="1" t="s">
+      <c r="F13"/>
+      <c r="G13"/>
+      <c r="H13"/>
+      <c r="I13"/>
+      <c r="J13"/>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:10">
+      <c r="A14" s="3"/>
+      <c r="B14"/>
+      <c r="C14" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:8">
-      <c r="D15" s="1" t="s">
+      <c r="D14"/>
+      <c r="E14"/>
+      <c r="F14"/>
+      <c r="G14"/>
+      <c r="H14"/>
+      <c r="I14"/>
+      <c r="J14"/>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:10">
+      <c r="A15" s="3"/>
+      <c r="B15"/>
+      <c r="C15"/>
+      <c r="D15" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="1:8">
-      <c r="B16" s="1" t="s">
+      <c r="E15"/>
+      <c r="F15"/>
+      <c r="G15"/>
+      <c r="H15"/>
+      <c r="I15"/>
+      <c r="J15"/>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:10">
+      <c r="A16" s="3"/>
+      <c r="B16"/>
+      <c r="C16"/>
+      <c r="D16" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="2:5">
-      <c r="C17" s="1" t="s">
+      <c r="E16"/>
+      <c r="F16"/>
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="J16"/>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:10">
+      <c r="A17" s="3"/>
+      <c r="B17"/>
+      <c r="C17"/>
+      <c r="D17"/>
+      <c r="E17" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="2:5">
-      <c r="C18" s="1" t="s">
+      <c r="F17"/>
+      <c r="G17"/>
+      <c r="H17"/>
+      <c r="I17"/>
+      <c r="J17"/>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:10">
+      <c r="E18" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" spans="2:5">
-      <c r="D19" s="1" t="s">
+    <row r="19" s="1" customFormat="1" spans="1:10">
+      <c r="E19" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" spans="2:5">
+    <row r="20" s="1" customFormat="1" spans="1:10">
       <c r="D20" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" spans="2:5">
+    <row r="21" s="1" customFormat="1" spans="1:10">
       <c r="D21" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" spans="2:5">
-      <c r="C22" s="1" t="s">
+    <row r="22" s="1" customFormat="1" spans="1:10">
+      <c r="E22" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" spans="2:5">
-      <c r="D23" s="1" t="s">
+    <row r="23" s="1" customFormat="1" spans="1:10">
+      <c r="E23" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" spans="2:5">
-      <c r="D24" s="1" t="s">
+    <row r="24" s="1" customFormat="1" spans="1:10">
+      <c r="F24" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" spans="2:5">
-      <c r="D25" s="1" t="s">
+    <row r="25" s="1" customFormat="1" spans="1:10">
+      <c r="F25" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" spans="2:5">
+    <row r="26" s="1" customFormat="1" spans="1:10">
       <c r="C26" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" spans="2:5">
-      <c r="B27" s="1" t="s">
+    <row r="27" s="1" customFormat="1" spans="1:10">
+      <c r="D27" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="2:5">
-      <c r="C28" s="1" t="s">
+    <row r="28" s="1" customFormat="1" spans="1:10">
+      <c r="D28" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="2:5">
+    <row r="29" s="1" customFormat="1" spans="1:10">
       <c r="D29" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="2:5">
-      <c r="E30" s="1" t="s">
+    <row r="30" s="1" customFormat="1" spans="1:10">
+      <c r="D30" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="2:5">
-      <c r="D31" s="1" t="s">
+    <row r="31" s="1" customFormat="1" spans="1:10">
+      <c r="E31" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:5">
+    <row r="32" s="1" customFormat="1" spans="1:10">
       <c r="E32" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="2:5">
-      <c r="C33" s="1" t="s">
+    <row r="33" s="1" customFormat="1" spans="2:5">
+      <c r="B33" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="2:5">
-      <c r="D34" s="1" t="s">
+    <row r="34" s="1" customFormat="1" spans="2:5">
+      <c r="C34" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="2:5">
-      <c r="E35" s="1" t="s">
+    <row r="35" s="1" customFormat="1" spans="2:5">
+      <c r="D35" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="2:5">
-      <c r="E36" s="1" t="s">
+    <row r="36" s="1" customFormat="1" spans="2:5">
+      <c r="D36" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="2:5">
+    <row r="37" s="1" customFormat="1" spans="2:5">
       <c r="E37" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="2:5">
-      <c r="D38" s="1" t="s">
+    <row r="38" s="1" customFormat="1" spans="2:5">
+      <c r="E38" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="39" spans="2:5">
-      <c r="E39" s="1" t="s">
+    <row r="39" s="1" customFormat="1" spans="2:5">
+      <c r="D39" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="40" spans="2:5">
-      <c r="E40" s="1" t="s">
+    <row r="40" s="1" customFormat="1" spans="2:5">
+      <c r="D40" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="41" spans="2:5">
-      <c r="E41" s="1" t="s">
+    <row r="41" s="1" customFormat="1" spans="2:5">
+      <c r="C41" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="42" spans="2:5">
+    <row r="42" s="1" customFormat="1" spans="2:5">
       <c r="D42" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="2:5">
-      <c r="E43" s="1" t="s">
+    <row r="43" s="1" customFormat="1" spans="2:5">
+      <c r="D43" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="2:5">
-      <c r="C44" s="1" t="s">
+    <row r="44" s="1" customFormat="1" spans="2:5">
+      <c r="E44" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="45" spans="2:5">
-      <c r="D45" s="1" t="s">
+    <row r="45" s="1" customFormat="1" spans="2:5">
+      <c r="E45" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="2:5">
+    <row r="46" s="1" customFormat="1" spans="2:5">
       <c r="D46" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="47" spans="2:5">
-      <c r="B47" s="1" t="s">
+    <row r="47" s="1" customFormat="1" spans="2:5">
+      <c r="E47" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="48" spans="2:5">
-      <c r="C48" s="1" t="s">
+    <row r="48" s="1" customFormat="1" spans="2:5">
+      <c r="E48" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="49" spans="2:5">
-      <c r="D49" s="1" t="s">
+    <row r="49" s="1" customFormat="1" spans="3:5">
+      <c r="C49" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="50" spans="2:5">
+    <row r="50" s="1" customFormat="1" spans="3:5">
       <c r="D50" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="51" spans="2:5">
-      <c r="C51" s="1" t="s">
+    <row r="51" s="1" customFormat="1" spans="3:5">
+      <c r="D51" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="52" spans="2:5">
+    <row r="52" s="1" customFormat="1" spans="3:5">
       <c r="D52" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="53" spans="2:5">
-      <c r="D53" s="1" t="s">
+    <row r="53" s="1" customFormat="1" spans="3:5">
+      <c r="E53" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="54" spans="2:5">
+    <row r="54" s="1" customFormat="1" spans="3:5">
       <c r="E54" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="2:5">
-      <c r="C55" s="1" t="s">
+    <row r="55" s="1" customFormat="1" spans="3:5">
+      <c r="E55" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="56" spans="2:5">
-      <c r="D56" s="1" t="s">
+    <row r="56" s="1" customFormat="1" spans="3:5">
+      <c r="C56" s="1" t="s">
         <v>54</v>
-      </c>
-    </row>
-    <row r="57" spans="2:5">
-      <c r="D57" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="58" spans="2:5">
-      <c r="B58" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="59" spans="2:5">
-      <c r="C59" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="60" spans="2:5">
-      <c r="D60" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="61" spans="2:5">
-      <c r="D61" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="62" spans="2:5">
-      <c r="E62" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="63" spans="2:5">
-      <c r="E63" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="64" spans="2:5">
-      <c r="D64" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="65" spans="3:6">
-      <c r="D65" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="66" spans="3:6">
-      <c r="C66" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="67" spans="3:6">
-      <c r="D67" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="68" spans="3:6">
-      <c r="E68" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="69" spans="3:6">
-      <c r="E69" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="70" spans="3:6">
-      <c r="E70" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="71" spans="3:6">
-      <c r="D71" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="72" spans="3:6">
-      <c r="E72" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="73" spans="3:6">
-      <c r="E73" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="74" spans="3:6">
-      <c r="E74" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="75" spans="3:6">
-      <c r="F75" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="76" spans="3:6">
-      <c r="F76" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="77" spans="3:6">
-      <c r="D77" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="78" spans="3:6">
-      <c r="E78" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="79" spans="3:6">
-      <c r="E79" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="80" spans="3:6">
-      <c r="E80" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="81" spans="2:4">
-      <c r="B81" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="82" spans="2:4">
-      <c r="C82" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="83" spans="2:4">
-      <c r="C83" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="84" spans="2:4">
-      <c r="C84" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="85" spans="2:4">
-      <c r="C85" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="86" spans="2:4">
-      <c r="D86" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="87" spans="2:4">
-      <c r="D87" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="88" spans="2:4">
-      <c r="D88" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="89" spans="2:4">
-      <c r="D89" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="90" spans="2:4">
-      <c r="C90" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="91" spans="2:4">
-      <c r="D91" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="92" spans="2:4">
-      <c r="D92" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="93" spans="2:4">
-      <c r="D93" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="94" spans="2:4">
-      <c r="C94" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="95" spans="2:4">
-      <c r="D95" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="96" spans="2:4">
-      <c r="D96" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="97" spans="4:4">
-      <c r="D97" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="98" spans="4:4">
-      <c r="D98" s="1" t="s">
-        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/Note/测试.xlsx
+++ b/Note/测试.xlsx
@@ -49,172 +49,138 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
-  <si>
-    <t>如何认识关税战、贸易战### ###</t>
-  </si>
-  <si>
-    <t>一、基本论断：贸易战与保护主义的后果</t>
-  </si>
-  <si>
-    <t>总体定性</t>
-  </si>
-  <si>
-    <t>贸易战、关税战没有赢家</t>
-  </si>
-  <si>
-    <t>保护主义没有出路</t>
-  </si>
-  <si>
-    <t>二、对美国关税行为的指控</t>
-  </si>
-  <si>
-    <t>行为概述：美国以各种借口宣布对包括中国在内的所有贸易伙伴滥施关税</t>
-  </si>
-  <si>
-    <t>行为的四重“严重”危害</t>
-  </si>
-  <si>
-    <t>侵犯权益：严重侵犯各国正当权益</t>
-  </si>
-  <si>
-    <t>违反规则：严重违反世界贸易组织规则</t>
-  </si>
-  <si>
-    <t>损害体制：严重损害以规则为基础的多边贸易体制</t>
-  </si>
-  <si>
-    <t>冲击秩序：严重冲击全球经济秩序稳定</t>
-  </si>
-  <si>
-    <t>三、对美国行为本质的分析</t>
-  </si>
-  <si>
-    <t>违背基本规律与原则：美国有关做法违背基本经济规律和市场原则</t>
-  </si>
-  <si>
-    <t>三“无视”的行径特征</t>
-  </si>
-  <si>
-    <t>罔顾平衡：罔顾多边贸易谈判达成的利益平衡结果</t>
-  </si>
-  <si>
-    <t>无视事实：无视美国长期从国际贸易中大量获利的事实</t>
-  </si>
-  <si>
-    <t>滥用工具：将关税作为实施极限施压、谋取私利的武器</t>
-  </si>
-  <si>
-    <t>行为的根本定性：这是典型的单边主义、保护主义和经济霸凌行径</t>
-  </si>
-  <si>
-    <t>旗号与本质的矛盾</t>
-  </si>
-  <si>
-    <t>旗号：美国打着所谓追求“对等”“公平”的旗号</t>
-  </si>
-  <si>
-    <t>实质</t>
-  </si>
-  <si>
-    <t>搞零和博弈：搞零和博弈</t>
-  </si>
-  <si>
-    <t>追求“美国优先”：本质上是追求“美国优先”“美国特殊”</t>
-  </si>
-  <si>
-    <t>四、对全球化趋势的研判与展望</t>
-  </si>
-  <si>
-    <t>当今世界的现实：当今世界是经济全球化塑造的世界</t>
-  </si>
-  <si>
-    <t>共同的职责：维护健康的国际经贸秩序和全球产供链安全稳定，是各方共同的职责</t>
-  </si>
-  <si>
-    <t>保护主义的局限性：保护主义改变不了经济全球化大势</t>
-  </si>
-  <si>
-    <t>未来的必然趋势</t>
-  </si>
-  <si>
-    <t>必由之路：经济全球化始终是人类社会前进的必由之路</t>
-  </si>
-  <si>
-    <t>时代潮流：不可逆转的时代潮流</t>
-  </si>
-  <si>
-    <t>为什么要倡导普惠包容的经济全球化### ###</t>
-  </si>
-  <si>
-    <t>一、普惠的经济全球化</t>
-  </si>
-  <si>
-    <t>核心目标：处理好发展与分配
-：做大并分好经济发展的“蛋糕”</t>
-  </si>
-  <si>
-    <t>确保广泛参与与共享</t>
-  </si>
-  <si>
-    <t>参与主体：让不同国家、不同阶层、不同人群都能参与</t>
-  </si>
-  <si>
-    <t>享有成果：并享有经济社会发展的成果</t>
-  </si>
-  <si>
-    <t>解决关键问题：妥善解决国家间和各国内部发展失衡问题</t>
-  </si>
-  <si>
-    <t>最终愿景：实现共同发展、共同繁荣</t>
-  </si>
-  <si>
-    <t>二、包容的经济全球化</t>
-  </si>
-  <si>
-    <t>尊重发展道路多样性：支持各国走出符合自身国情的发展道路</t>
-  </si>
-  <si>
-    <t>反对单一与排他</t>
-  </si>
-  <si>
-    <t>反对模式单一：不搞发展模式的单一化</t>
-  </si>
-  <si>
-    <t>摒弃错误主义：摒弃损人利己的单边主义、保护主义</t>
-  </si>
-  <si>
-    <t>维护经济系统稳定与活力</t>
-  </si>
-  <si>
-    <t>稳定供应链：维护全球产业链供应链的稳定畅通</t>
-  </si>
-  <si>
-    <t>保持增长动力：保持世界经济增长活力与动力</t>
-  </si>
-  <si>
-    <t>三、普惠包容全球化的性质与中国角色</t>
-  </si>
-  <si>
-    <t>根本定位：普惠包容全球化是人心所向、人间正道</t>
-  </si>
-  <si>
-    <t>中国倡导的现实意义：具有针对性：中国倡导并推动此举，有着现实针对性和战略指导性</t>
-  </si>
-  <si>
-    <t>中国的引领与贡献</t>
-  </si>
-  <si>
-    <t>引领方向：将引领经济全球化正确方向</t>
-  </si>
-  <si>
-    <t>贡献智慧：为解决当今世界面临的一系列重大问题和挑战贡献中国智慧</t>
-  </si>
-  <si>
-    <t>提供依托：为构建人类命运共同体提供坚实依托</t>
-  </si>
-  <si>
-    <t>总体评价：普惠包容全球化具有重要深远意义</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+  <si>
+    <t>防沙治沙是恢复原貌### ###</t>
+  </si>
+  <si>
+    <t>一、总的核心原则</t>
+  </si>
+  <si>
+    <t>生态保护和修复既要尊重客观规律</t>
+  </si>
+  <si>
+    <t>也要充分发挥主观能动性</t>
+  </si>
+  <si>
+    <t>二、尊重客观规律是前提</t>
+  </si>
+  <si>
+    <t>基本定位：尊重客观规律是正确发挥主观能动性的前提</t>
+  </si>
+  <si>
+    <t>根本定义：规律是事物变化发展过程中内在的、本质的、必然的联系</t>
+  </si>
+  <si>
+    <t>正确行动的基础</t>
+  </si>
+  <si>
+    <t>认识世界的前提：人们只有在认识和掌握客观规律的基础上，才能正确地认识世界</t>
+  </si>
+  <si>
+    <t>改造世界的前提：才能有效地改造世界</t>
+  </si>
+  <si>
+    <t>三、必须充分发挥主观能动性</t>
+  </si>
+  <si>
+    <t>能动性的关键作用：只有充分发挥主观能动性，才能正确认识和利用客观规律</t>
+  </si>
+  <si>
+    <t>对规律客观性的正确态度</t>
+  </si>
+  <si>
+    <t>非消极无为：承认规律的客观性，并非说人在规律面前无能为力、无所作为</t>
+  </si>
+  <si>
+    <t>人的能动作用</t>
+  </si>
+  <si>
+    <t>能够认识规律：人能够通过自觉活动去认识规律</t>
+  </si>
+  <si>
+    <t>能够改造世界：并能按照客观规律去改造世界，以满足自身的需要</t>
+  </si>
+  <si>
+    <t>四、实例：自然生态系统的治理</t>
+  </si>
+  <si>
+    <t>生态系统的基本属性</t>
+  </si>
+  <si>
+    <t>有机生命躯体：自然生态系统是一个有机生命躯体</t>
+  </si>
+  <si>
+    <t>具有客观规律：有其自身发展演化的客观规律，要充分尊重和顺应自然</t>
+  </si>
+  <si>
+    <t>荒漠治理的辩证实践</t>
+  </si>
+  <si>
+    <t>认识到荒漠的价值：认识到天然的荒漠也是一种有价值的生态系统</t>
+  </si>
+  <si>
+    <t>治理实践中的平衡</t>
+  </si>
+  <si>
+    <t>主动治理：人们在发挥主观能动性治理荒漠化的同时</t>
+  </si>
+  <si>
+    <t>顺应与保留：也保留了地球上原有的沙漠和荒漠</t>
+  </si>
+  <si>
+    <t>人与自然的关系### ###</t>
+  </si>
+  <si>
+    <t>一、自然地理环境的基础性地位：作为生存与发展的根本条件</t>
+  </si>
+  <si>
+    <t>永恒且必要的条件：自然地理环境是人类社会生存和发展永恒的、必要的条件</t>
+  </si>
+  <si>
+    <t>生活与生产的自然基础：是人们生活和生产的自然基础</t>
+  </si>
+  <si>
+    <t>二、生态平衡与资源利用的重要性</t>
+  </si>
+  <si>
+    <t>生态平衡的社会作用：自然生态平衡对社会生活起着重要作用</t>
+  </si>
+  <si>
+    <t>合理利用与保护的必要性：合理地利用自然资源，保护生态平衡，是社会得以正常发展的必要条件</t>
+  </si>
+  <si>
+    <t>三、人类实践必须遵循自然规律</t>
+  </si>
+  <si>
+    <t>改造世界的双重性</t>
+  </si>
+  <si>
+    <t>按意愿改造：人类在实践活动中按照自己的意愿改造世界</t>
+  </si>
+  <si>
+    <t>必须遵循规律：的同时必须遵循自然规律</t>
+  </si>
+  <si>
+    <t>违背规律的后果：否则将会导致人与自然关系的失衡</t>
+  </si>
+  <si>
+    <t>四、马克思的观点及和谐共生的体现</t>
+  </si>
+  <si>
+    <t>马克思的核心主张</t>
+  </si>
+  <si>
+    <t>调节物质变换：应当合理地调节人与自然之间的物质变换</t>
+  </si>
+  <si>
+    <t>最适合的条件：在最无愧于和最适合人类本性的条件下进行这种物质变换</t>
+  </si>
+  <si>
+    <t>当代实践的例证</t>
+  </si>
+  <si>
+    <t>“在公园中留荒野”正是坚持人与自然和谐共生的体现</t>
   </si>
 </sst>
 </file>
@@ -831,10 +797,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1155,469 +1118,744 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr defaultColWidth="9.66666666666667" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="16384" width="9.66666666666667" style="1" customWidth="1"/>
+    <col min="1" max="16384" width="9.66666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:10">
-      <c r="A1" s="2">
+    <row r="1" customFormat="1" spans="1:12">
+      <c r="A1" s="1">
         <f>SUM(B1:AZ1)</f>
-        <v>13.65</v>
-      </c>
-      <c r="B1" s="2">
+        <v>11.1833333333333</v>
+      </c>
+      <c r="B1" s="1">
         <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2220)/COLUMN()</f>
         <v>1</v>
       </c>
-      <c r="C1" s="2">
+      <c r="C1" s="1">
         <f t="shared" si="0"/>
         <v>2.66666666666667</v>
       </c>
-      <c r="D1" s="2">
+      <c r="D1" s="1">
         <f t="shared" si="0"/>
-        <v>5.25</v>
-      </c>
-      <c r="E1" s="2">
+        <v>4.25</v>
+      </c>
+      <c r="E1" s="1">
         <f t="shared" si="0"/>
-        <v>4.4</v>
-      </c>
-      <c r="F1" s="2">
+        <v>2.6</v>
+      </c>
+      <c r="F1" s="1">
         <f t="shared" si="0"/>
-        <v>0.333333333333333</v>
-      </c>
-      <c r="G1" s="2">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="G1" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H1" s="2">
+      <c r="H1" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:10">
-      <c r="A2" s="3" t="str" cm="1">
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+    </row>
+    <row r="2" customFormat="1" spans="1:12">
+      <c r="A2" s="2" t="str" cm="1">
         <f ca="1" t="array" ref="A2">_wpsfn.SHEETSNAME(A1)</f>
         <v>待处理</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2"/>
-      <c r="D2"/>
-      <c r="E2"/>
-      <c r="F2"/>
-      <c r="G2"/>
-      <c r="H2"/>
-      <c r="I2"/>
-      <c r="J2"/>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:10">
-      <c r="A3" s="3"/>
-      <c r="B3"/>
-      <c r="C3" t="s">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+    </row>
+    <row r="3" customFormat="1" spans="1:12">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D3"/>
-      <c r="E3"/>
-      <c r="F3"/>
-      <c r="G3"/>
-      <c r="H3"/>
-      <c r="I3"/>
-      <c r="J3"/>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:10">
-      <c r="A4" s="3"/>
-      <c r="B4"/>
-      <c r="C4"/>
-      <c r="D4" t="s">
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+    </row>
+    <row r="4" customFormat="1" spans="1:12">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E4"/>
-      <c r="F4"/>
-      <c r="G4"/>
-      <c r="H4"/>
-      <c r="I4"/>
-      <c r="J4"/>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:10">
-      <c r="A5" s="3"/>
-      <c r="B5"/>
-      <c r="C5"/>
-      <c r="D5"/>
-      <c r="E5" t="s">
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+    </row>
+    <row r="5" customFormat="1" spans="1:12">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F5"/>
-      <c r="G5"/>
-      <c r="H5"/>
-      <c r="I5"/>
-      <c r="J5"/>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:10">
-      <c r="A6" s="3"/>
-      <c r="B6"/>
-      <c r="C6"/>
-      <c r="D6"/>
-      <c r="E6" t="s">
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+    </row>
+    <row r="6" customFormat="1" spans="1:12">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F6"/>
-      <c r="G6"/>
-      <c r="H6"/>
-      <c r="I6"/>
-      <c r="J6"/>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:10">
-      <c r="A7" s="3"/>
-      <c r="B7"/>
-      <c r="C7" t="s">
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+    </row>
+    <row r="7" customFormat="1" spans="1:12">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D7"/>
-      <c r="E7"/>
-      <c r="F7"/>
-      <c r="G7"/>
-      <c r="H7"/>
-      <c r="I7"/>
-      <c r="J7"/>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:10">
-      <c r="A8" s="3"/>
-      <c r="B8"/>
-      <c r="C8"/>
-      <c r="D8" t="s">
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" customFormat="1" spans="1:12">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E8"/>
-      <c r="F8"/>
-      <c r="G8"/>
-      <c r="H8"/>
-      <c r="I8"/>
-      <c r="J8"/>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:10">
-      <c r="A9" s="3"/>
-      <c r="B9"/>
-      <c r="C9"/>
-      <c r="D9" t="s">
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+    </row>
+    <row r="9" customFormat="1" spans="1:12">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E9"/>
-      <c r="F9"/>
-      <c r="G9"/>
-      <c r="H9"/>
-      <c r="I9"/>
-      <c r="J9"/>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:10">
-      <c r="A10" s="3"/>
-      <c r="B10"/>
-      <c r="C10"/>
-      <c r="D10"/>
-      <c r="E10" t="s">
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+    </row>
+    <row r="10" customFormat="1" spans="1:12">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F10"/>
-      <c r="G10"/>
-      <c r="H10"/>
-      <c r="I10"/>
-      <c r="J10"/>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:10">
-      <c r="A11" s="3"/>
-      <c r="B11"/>
-      <c r="C11"/>
-      <c r="D11"/>
-      <c r="E11" t="s">
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+    </row>
+    <row r="11" customFormat="1" spans="1:12">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F11"/>
-      <c r="G11"/>
-      <c r="H11"/>
-      <c r="I11"/>
-      <c r="J11"/>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:10">
-      <c r="A12" s="3"/>
-      <c r="B12"/>
-      <c r="C12"/>
-      <c r="D12"/>
-      <c r="E12" t="s">
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+    </row>
+    <row r="12" customFormat="1" spans="1:12">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F12"/>
-      <c r="G12"/>
-      <c r="H12"/>
-      <c r="I12"/>
-      <c r="J12"/>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:10">
-      <c r="A13" s="3"/>
-      <c r="B13"/>
-      <c r="C13"/>
-      <c r="D13"/>
-      <c r="E13" t="s">
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+    </row>
+    <row r="13" customFormat="1" spans="1:12">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F13"/>
-      <c r="G13"/>
-      <c r="H13"/>
-      <c r="I13"/>
-      <c r="J13"/>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:10">
-      <c r="A14" s="3"/>
-      <c r="B14"/>
-      <c r="C14" t="s">
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+    </row>
+    <row r="14" customFormat="1" spans="1:12">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D14"/>
-      <c r="E14"/>
-      <c r="F14"/>
-      <c r="G14"/>
-      <c r="H14"/>
-      <c r="I14"/>
-      <c r="J14"/>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:10">
-      <c r="A15" s="3"/>
-      <c r="B15"/>
-      <c r="C15"/>
-      <c r="D15" t="s">
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+    </row>
+    <row r="15" customFormat="1" spans="1:12">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E15"/>
-      <c r="F15"/>
-      <c r="G15"/>
-      <c r="H15"/>
-      <c r="I15"/>
-      <c r="J15"/>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="1:10">
-      <c r="A16" s="3"/>
-      <c r="B16"/>
-      <c r="C16"/>
-      <c r="D16" t="s">
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+    </row>
+    <row r="16" customFormat="1" spans="1:12">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E16"/>
-      <c r="F16"/>
-      <c r="G16"/>
-      <c r="H16"/>
-      <c r="I16"/>
-      <c r="J16"/>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:10">
-      <c r="A17" s="3"/>
-      <c r="B17"/>
-      <c r="C17"/>
-      <c r="D17"/>
-      <c r="E17" t="s">
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+    </row>
+    <row r="17" customFormat="1" spans="1:13">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F17"/>
-      <c r="G17"/>
-      <c r="H17"/>
-      <c r="I17"/>
-      <c r="J17"/>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="1:10">
-      <c r="E18" s="1" t="s">
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+    </row>
+    <row r="18" customFormat="1" spans="1:13">
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="1:10">
-      <c r="E19" s="1" t="s">
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+    </row>
+    <row r="19" customFormat="1" spans="1:13">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="1:10">
-      <c r="D20" s="1" t="s">
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+    </row>
+    <row r="20" customFormat="1" spans="1:13">
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="1:10">
-      <c r="D21" s="1" t="s">
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+    </row>
+    <row r="21" customFormat="1" spans="1:13">
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="1:10">
-      <c r="E22" s="1" t="s">
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+    </row>
+    <row r="22" customFormat="1" spans="1:13">
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="1:10">
-      <c r="E23" s="1" t="s">
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+    </row>
+    <row r="23" customFormat="1" spans="1:13">
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="1:10">
-      <c r="F24" s="1" t="s">
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+    </row>
+    <row r="24" customFormat="1" spans="1:13">
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="25" s="1" customFormat="1" spans="1:10">
-      <c r="F25" s="1" t="s">
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+    </row>
+    <row r="25" customFormat="1" spans="1:13">
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="26" s="1" customFormat="1" spans="1:10">
-      <c r="C26" s="1" t="s">
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+    </row>
+    <row r="26" customFormat="1" spans="1:13">
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="27" s="1" customFormat="1" spans="1:10">
-      <c r="D27" s="1" t="s">
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+    </row>
+    <row r="27" customFormat="1" spans="1:13">
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="28" s="1" customFormat="1" spans="1:10">
-      <c r="D28" s="1" t="s">
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+    </row>
+    <row r="28" customFormat="1" spans="1:13">
+      <c r="B28" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="29" s="1" customFormat="1" spans="1:10">
-      <c r="D29" s="1" t="s">
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+    </row>
+    <row r="29" customFormat="1" spans="1:13">
+      <c r="B29" s="2"/>
+      <c r="C29" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="30" s="1" customFormat="1" spans="1:10">
-      <c r="D30" s="1" t="s">
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+    </row>
+    <row r="30" customFormat="1" spans="1:13">
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="31" s="1" customFormat="1" spans="1:10">
-      <c r="E31" s="1" t="s">
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+    </row>
+    <row r="31" customFormat="1" spans="1:13">
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="32" s="1" customFormat="1" spans="1:10">
-      <c r="E32" s="1" t="s">
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+    </row>
+    <row r="32" customFormat="1" spans="1:13">
+      <c r="B32" s="2"/>
+      <c r="C32" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="33" s="1" customFormat="1" spans="2:5">
-      <c r="B33" s="1" t="s">
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+    </row>
+    <row r="33" customFormat="1" spans="2:13">
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" s="1" customFormat="1" spans="2:5">
-      <c r="C34" s="1" t="s">
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+    </row>
+    <row r="34" customFormat="1" spans="2:13">
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="35" s="1" customFormat="1" spans="2:5">
-      <c r="D35" s="1" t="s">
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+    </row>
+    <row r="35" customFormat="1" spans="2:13">
+      <c r="B35" s="2"/>
+      <c r="C35" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="36" s="1" customFormat="1" spans="2:5">
-      <c r="D36" s="1" t="s">
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+    </row>
+    <row r="36" customFormat="1" spans="2:13">
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="37" s="1" customFormat="1" spans="2:5">
-      <c r="E37" s="1" t="s">
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+    </row>
+    <row r="37" customFormat="1" spans="2:13">
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="38" s="1" customFormat="1" spans="2:5">
-      <c r="E38" s="1" t="s">
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+    </row>
+    <row r="38" customFormat="1" spans="2:13">
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="39" s="1" customFormat="1" spans="2:5">
-      <c r="D39" s="1" t="s">
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" customFormat="1" spans="2:13">
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="40" s="1" customFormat="1" spans="2:5">
-      <c r="D40" s="1" t="s">
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+    </row>
+    <row r="40" customFormat="1" spans="2:13">
+      <c r="B40" s="2"/>
+      <c r="C40" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="41" s="1" customFormat="1" spans="2:5">
-      <c r="C41" s="1" t="s">
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+    </row>
+    <row r="41" customFormat="1" spans="2:13">
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="42" s="1" customFormat="1" spans="2:5">
-      <c r="D42" s="1" t="s">
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+    </row>
+    <row r="42" customFormat="1" spans="2:13">
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="43" s="1" customFormat="1" spans="2:5">
-      <c r="D43" s="1" t="s">
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2"/>
+    </row>
+    <row r="43" customFormat="1" spans="2:13">
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="44" s="1" customFormat="1" spans="2:5">
-      <c r="E44" s="1" t="s">
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2"/>
+      <c r="M43" s="2"/>
+    </row>
+    <row r="44" customFormat="1" spans="2:13">
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="45" s="1" customFormat="1" spans="2:5">
-      <c r="E45" s="1" t="s">
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
+      <c r="M44" s="2"/>
+    </row>
+    <row r="45" customFormat="1" spans="2:13">
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="46" s="1" customFormat="1" spans="2:5">
-      <c r="D46" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="47" s="1" customFormat="1" spans="2:5">
-      <c r="E47" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="48" s="1" customFormat="1" spans="2:5">
-      <c r="E48" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="49" s="1" customFormat="1" spans="3:5">
-      <c r="C49" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="50" s="1" customFormat="1" spans="3:5">
-      <c r="D50" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="51" s="1" customFormat="1" spans="3:5">
-      <c r="D51" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="52" s="1" customFormat="1" spans="3:5">
-      <c r="D52" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="53" s="1" customFormat="1" spans="3:5">
-      <c r="E53" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="54" s="1" customFormat="1" spans="3:5">
-      <c r="E54" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="55" s="1" customFormat="1" spans="3:5">
-      <c r="E55" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="56" s="1" customFormat="1" spans="3:5">
-      <c r="C56" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2"/>
+      <c r="L45" s="2"/>
+      <c r="M45" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Note/测试.xlsx
+++ b/Note/测试.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="11520" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="待处理" sheetId="1" r:id="rId1"/>
@@ -49,138 +49,285 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
-  <si>
-    <t>防沙治沙是恢复原貌### ###</t>
-  </si>
-  <si>
-    <t>一、总的核心原则</t>
-  </si>
-  <si>
-    <t>生态保护和修复既要尊重客观规律</t>
-  </si>
-  <si>
-    <t>也要充分发挥主观能动性</t>
-  </si>
-  <si>
-    <t>二、尊重客观规律是前提</t>
-  </si>
-  <si>
-    <t>基本定位：尊重客观规律是正确发挥主观能动性的前提</t>
-  </si>
-  <si>
-    <t>根本定义：规律是事物变化发展过程中内在的、本质的、必然的联系</t>
-  </si>
-  <si>
-    <t>正确行动的基础</t>
-  </si>
-  <si>
-    <t>认识世界的前提：人们只有在认识和掌握客观规律的基础上，才能正确地认识世界</t>
-  </si>
-  <si>
-    <t>改造世界的前提：才能有效地改造世界</t>
-  </si>
-  <si>
-    <t>三、必须充分发挥主观能动性</t>
-  </si>
-  <si>
-    <t>能动性的关键作用：只有充分发挥主观能动性，才能正确认识和利用客观规律</t>
-  </si>
-  <si>
-    <t>对规律客观性的正确态度</t>
-  </si>
-  <si>
-    <t>非消极无为：承认规律的客观性，并非说人在规律面前无能为力、无所作为</t>
-  </si>
-  <si>
-    <t>人的能动作用</t>
-  </si>
-  <si>
-    <t>能够认识规律：人能够通过自觉活动去认识规律</t>
-  </si>
-  <si>
-    <t>能够改造世界：并能按照客观规律去改造世界，以满足自身的需要</t>
-  </si>
-  <si>
-    <t>四、实例：自然生态系统的治理</t>
-  </si>
-  <si>
-    <t>生态系统的基本属性</t>
-  </si>
-  <si>
-    <t>有机生命躯体：自然生态系统是一个有机生命躯体</t>
-  </si>
-  <si>
-    <t>具有客观规律：有其自身发展演化的客观规律，要充分尊重和顺应自然</t>
-  </si>
-  <si>
-    <t>荒漠治理的辩证实践</t>
-  </si>
-  <si>
-    <t>认识到荒漠的价值：认识到天然的荒漠也是一种有价值的生态系统</t>
-  </si>
-  <si>
-    <t>治理实践中的平衡</t>
-  </si>
-  <si>
-    <t>主动治理：人们在发挥主观能动性治理荒漠化的同时</t>
-  </si>
-  <si>
-    <t>顺应与保留：也保留了地球上原有的沙漠和荒漠</t>
-  </si>
-  <si>
-    <t>人与自然的关系### ###</t>
-  </si>
-  <si>
-    <t>一、自然地理环境的基础性地位：作为生存与发展的根本条件</t>
-  </si>
-  <si>
-    <t>永恒且必要的条件：自然地理环境是人类社会生存和发展永恒的、必要的条件</t>
-  </si>
-  <si>
-    <t>生活与生产的自然基础：是人们生活和生产的自然基础</t>
-  </si>
-  <si>
-    <t>二、生态平衡与资源利用的重要性</t>
-  </si>
-  <si>
-    <t>生态平衡的社会作用：自然生态平衡对社会生活起着重要作用</t>
-  </si>
-  <si>
-    <t>合理利用与保护的必要性：合理地利用自然资源，保护生态平衡，是社会得以正常发展的必要条件</t>
-  </si>
-  <si>
-    <t>三、人类实践必须遵循自然规律</t>
-  </si>
-  <si>
-    <t>改造世界的双重性</t>
-  </si>
-  <si>
-    <t>按意愿改造：人类在实践活动中按照自己的意愿改造世界</t>
-  </si>
-  <si>
-    <t>必须遵循规律：的同时必须遵循自然规律</t>
-  </si>
-  <si>
-    <t>违背规律的后果：否则将会导致人与自然关系的失衡</t>
-  </si>
-  <si>
-    <t>四、马克思的观点及和谐共生的体现</t>
-  </si>
-  <si>
-    <t>马克思的核心主张</t>
-  </si>
-  <si>
-    <t>调节物质变换：应当合理地调节人与自然之间的物质变换</t>
-  </si>
-  <si>
-    <t>最适合的条件：在最无愧于和最适合人类本性的条件下进行这种物质变换</t>
-  </si>
-  <si>
-    <t>当代实践的例证</t>
-  </si>
-  <si>
-    <t>“在公园中留荒野”正是坚持人与自然和谐共生的体现</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
+  <si>
+    <t>为什么要铸牢中华民族共同体意识### ###</t>
+  </si>
+  <si>
+    <t>一、主线定位：工作的核心</t>
+  </si>
+  <si>
+    <t>铸牢中华民族共同体意识是新时代党的民族工作的主线</t>
+  </si>
+  <si>
+    <t>是民族地区各项工作的主线</t>
+  </si>
+  <si>
+    <t>二、与共同体建设的关系：互为因果</t>
+  </si>
+  <si>
+    <t>建设的落脚点：推进中华民族共同体建设是铸牢中华民族共同体意识的落脚点</t>
+  </si>
+  <si>
+    <t>意识的核心性：铸牢中华民族共同体意识则是推进中华民族共同体建设的核心</t>
+  </si>
+  <si>
+    <t>三、历史与法理基础</t>
+  </si>
+  <si>
+    <t>国家的本质：中国是全国各族人民共同缔造的统一的多民族国家</t>
+  </si>
+  <si>
+    <t>形成的必然性：中华民族共同体的形成是中华民族历史发展的必然结果</t>
+  </si>
+  <si>
+    <t>四、铸牢意识的多重重要意义</t>
+  </si>
+  <si>
+    <t>首要意义：构筑思想长城</t>
+  </si>
+  <si>
+    <t>只有铸牢中华民族共同体意识</t>
+  </si>
+  <si>
+    <t>才能构建起维护国家统一和民族团结的坚固思想长城</t>
+  </si>
+  <si>
+    <t>第二意义：增进认同与夯实基础</t>
+  </si>
+  <si>
+    <t>增进自觉认同：才能增进各民族对中华民族的自觉认同</t>
+  </si>
+  <si>
+    <t>务实思想基础：务实我国民族关系发展的思想基础</t>
+  </si>
+  <si>
+    <t>第三意义：应对风险与提供保证</t>
+  </si>
+  <si>
+    <t>有效应对挑战：才能有效应对实现中华民族伟大复兴过程中民族领域可能发生的风险挑战</t>
+  </si>
+  <si>
+    <t>提供思想保证：为党和国家兴旺发达、长治久安提供重要思想保证</t>
+  </si>
+  <si>
+    <t>为什么要坚持和完善民族区域自治### ###</t>
+  </si>
+  <si>
+    <t>一、制度的根本定位与作用</t>
+  </si>
+  <si>
+    <t>基本政治制度：是我国的基本政治制度</t>
+  </si>
+  <si>
+    <t>解决民族问题的内容与保障</t>
+  </si>
+  <si>
+    <t>正确道路的核心内容：是中国特色解决民族问题的正确道路的重要内容</t>
+  </si>
+  <si>
+    <t>制度保障：是中国特色解决民族问题的正确道路的制度保障</t>
+  </si>
+  <si>
+    <t>二、实践成就与制度优越性</t>
+  </si>
+  <si>
+    <t>巨大成就的证明：民族区域自治地区几十年来取得的巨大成就说明该制度具有优越性</t>
+  </si>
+  <si>
+    <t>制度的核心原则</t>
+  </si>
+  <si>
+    <t>结合统一与自治：坚持统一和自治相结合</t>
+  </si>
+  <si>
+    <t>结合民族与区域因素：坚持民族因素和区域因素相结合</t>
+  </si>
+  <si>
+    <t>制度的多重积极效能：促进民族共同目标</t>
+  </si>
+  <si>
+    <t>促进团结奋斗：能够促进各民族共同团结奋斗</t>
+  </si>
+  <si>
+    <t>促进繁荣发展：能够促进各民族共同繁荣发展</t>
+  </si>
+  <si>
+    <t>巩固国家统一：有利于巩固国家统一</t>
+  </si>
+  <si>
+    <t>增强民族凝聚力：有利于增强中华民族凝聚力</t>
+  </si>
+  <si>
+    <t>推动共同繁荣：有利于各民族共同繁荣发展</t>
+  </si>
+  <si>
+    <t>三、对制度的总结与立场</t>
+  </si>
+  <si>
+    <t>显著优越性：该制度具有显著优越性</t>
+  </si>
+  <si>
+    <t>根本态度与要求：应当坚持和完善</t>
+  </si>
+  <si>
+    <t>辛亥革命是伟大而艰辛的探索### ###</t>
+  </si>
+  <si>
+    <t>一、鸦片战争后的社会性质与民族梦想</t>
+  </si>
+  <si>
+    <t>社会性质的转变</t>
+  </si>
+  <si>
+    <t>外部入侵与内部统治：1840年鸦片战争后，西方列强入侵，封建统治腐败</t>
+  </si>
+  <si>
+    <t>社会性质的质变：中国逐步成为半殖民地半封建社会</t>
+  </si>
+  <si>
+    <t>民族劫难与伟大梦想的诞生</t>
+  </si>
+  <si>
+    <t>空前劫难：中国人民和中华民族遭受了前所未有的劫难</t>
+  </si>
+  <si>
+    <t>梦想的起点：从那时起，实现中华民族伟大复兴就成为中华民族最伟大的梦想</t>
+  </si>
+  <si>
+    <t>二、辛亥革命：近代民族民主革命的序幕：革命的开端</t>
+  </si>
+  <si>
+    <t>标志性事件：1911年10月10日，武昌城头枪声一响</t>
+  </si>
+  <si>
+    <t>双重序幕的拉开</t>
+  </si>
+  <si>
+    <t>拉开了中国完全意义上的近代民族民主革命的序幕</t>
+  </si>
+  <si>
+    <t>近代以来中国发生的深刻社会变革也由此拉开了序幕</t>
+  </si>
+  <si>
+    <t>三、辛亥革命的多重历史意义</t>
+  </si>
+  <si>
+    <t>政治制度的终结</t>
+  </si>
+  <si>
+    <t>推翻了清朝政府</t>
+  </si>
+  <si>
+    <t>结束了在中国延续几千年的君主专制制度</t>
+  </si>
+  <si>
+    <t>思想的解放与统治根基的撼动</t>
+  </si>
+  <si>
+    <t>促进思想解放：极大促进了中华民族的思想解放</t>
+  </si>
+  <si>
+    <t>撼动统治秩序：撼动了反动统治秩序的根基</t>
+  </si>
+  <si>
+    <t>推动社会变革与探索复兴道路</t>
+  </si>
+  <si>
+    <t>变革的推动力：以巨大的震撼力和深刻的影响力推动了中国社会变革</t>
+  </si>
+  <si>
+    <t>道路的探索：为实现中华民族伟大复兴探索了道路</t>
+  </si>
+  <si>
+    <t>四、辛亥革命的局限性</t>
+  </si>
+  <si>
+    <t>未改变的社会性质与人民命运</t>
+  </si>
+  <si>
+    <t>但是，辛亥革命未能改变中国半殖民地半封建的社会性质</t>
+  </si>
+  <si>
+    <t>未能改变中国人民的悲惨命运</t>
+  </si>
+  <si>
+    <t>新的历史迫切需求</t>
+  </si>
+  <si>
+    <t>需要新思想：中国迫切需要新的思想引领救亡运动</t>
+  </si>
+  <si>
+    <t>需要新组织：迫切需要新的组织凝聚革命力量</t>
+  </si>
+  <si>
+    <t>中共是孙中山革命事业的支持者和继承者### ###</t>
+  </si>
+  <si>
+    <t>一、历史继承：完成孙中山的未竟事业</t>
+  </si>
+  <si>
+    <t>孙中山先生生前：坚定支持：中国共产党人坚定支持他的事业</t>
+  </si>
+  <si>
+    <t>孙中山先生身后</t>
+  </si>
+  <si>
+    <t>忠实继承遗志</t>
+  </si>
+  <si>
+    <t>付出牺牲：忠实继承孙中山先生的遗志，付出巨大牺牲</t>
+  </si>
+  <si>
+    <t>完成未竟事业：完成了孙中山先生的未竟事业</t>
+  </si>
+  <si>
+    <t>取得革命胜利</t>
+  </si>
+  <si>
+    <t>新民主主义革命：取得了新民主主义革命胜利</t>
+  </si>
+  <si>
+    <t>建立新中国：建立了人民当家作主的中华人民共和国</t>
+  </si>
+  <si>
+    <t>实现独立解放：实现了民族独立、人民解放</t>
+  </si>
+  <si>
+    <t>基础上的继续奋斗</t>
+  </si>
+  <si>
+    <t>完成社会主义革命：完成了社会主义革命</t>
+  </si>
+  <si>
+    <t>确立社会主义制度：确立了社会主义制度</t>
+  </si>
+  <si>
+    <t>二、当今发展：超越蓝图的现实成就</t>
+  </si>
+  <si>
+    <t>成就的创造主体与基础：党的领导与人民奋斗：在中国共产党领导下，在全国各族人民顽强奋斗下</t>
+  </si>
+  <si>
+    <t>对孙中山蓝图的实现与超越</t>
+  </si>
+  <si>
+    <t>蓝图早已实现：孙中山先生当年描绘的蓝图早已实现</t>
+  </si>
+  <si>
+    <t>成就远超设想：中国人民创造的许多成就远远超出了孙中山先生的设想</t>
+  </si>
+  <si>
+    <t>国家的现实状态：巍然屹立东方：孙中山先生致力于建设的独立、民主、富强的国家早已巍然屹立在世界东方</t>
+  </si>
+  <si>
+    <t>民族复兴的历史方位</t>
+  </si>
+  <si>
+    <t>更接近目标：我们比历史上任何时候都更接近中华民族伟大复兴的目标</t>
+  </si>
+  <si>
+    <t>更有信心能力：比历史上任何时期都更有信心、有能力实现这个目标</t>
   </si>
 </sst>
 </file>
@@ -801,10 +948,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1118,744 +1265,516 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M45"/>
-  <sheetFormatPr defaultColWidth="9.66666666666667" defaultRowHeight="14.4"/>
+  <dimension ref="A1:H94"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="16384" width="9.66666666666667" customWidth="1"/>
+    <col min="1" max="1" width="9.66666666666667" style="1"/>
+    <col min="2" max="16384" width="8.88888888888889" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:12">
-      <c r="A1" s="1">
+    <row r="1" s="1" customFormat="1" spans="1:8">
+      <c r="A1" s="2">
         <f>SUM(B1:AZ1)</f>
-        <v>11.1833333333333</v>
-      </c>
-      <c r="B1" s="1">
+        <v>22.9666666666667</v>
+      </c>
+      <c r="B1" s="2">
         <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2220)/COLUMN()</f>
-        <v>1</v>
-      </c>
-      <c r="C1" s="1">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2">
         <f t="shared" si="0"/>
-        <v>2.66666666666667</v>
-      </c>
-      <c r="D1" s="1">
+        <v>4.33333333333333</v>
+      </c>
+      <c r="D1" s="2">
         <f t="shared" si="0"/>
-        <v>4.25</v>
-      </c>
-      <c r="E1" s="1">
+        <v>8</v>
+      </c>
+      <c r="E1" s="2">
         <f t="shared" si="0"/>
-        <v>2.6</v>
-      </c>
-      <c r="F1" s="1">
+        <v>7.8</v>
+      </c>
+      <c r="F1" s="2">
         <f t="shared" si="0"/>
-        <v>0.666666666666667</v>
-      </c>
-      <c r="G1" s="1">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="G1" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H1" s="1">
+      <c r="H1" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-    </row>
-    <row r="2" customFormat="1" spans="1:12">
-      <c r="A2" s="2" t="str" cm="1">
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:8">
+      <c r="A2" s="1" t="str" cm="1">
         <f ca="1" t="array" ref="A2">_wpsfn.SHEETSNAME(A1)</f>
         <v>待处理</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-    </row>
-    <row r="3" customFormat="1" spans="1:12">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2" t="s">
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:8">
+      <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-    </row>
-    <row r="4" customFormat="1" spans="1:12">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="s">
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:8">
+      <c r="D4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-    </row>
-    <row r="5" customFormat="1" spans="1:12">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="s">
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:8">
+      <c r="D5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-    </row>
-    <row r="6" customFormat="1" spans="1:12">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2" t="s">
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:8">
+      <c r="C6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-    </row>
-    <row r="7" customFormat="1" spans="1:12">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="s">
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:8">
+      <c r="D7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" customFormat="1" spans="1:12">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="s">
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:8">
+      <c r="D8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-    </row>
-    <row r="9" customFormat="1" spans="1:12">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2" t="s">
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:8">
+      <c r="C9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-    </row>
-    <row r="10" customFormat="1" spans="1:12">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2" t="s">
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:8">
+      <c r="D10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-    </row>
-    <row r="11" customFormat="1" spans="1:12">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2" t="s">
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:8">
+      <c r="D11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-    </row>
-    <row r="12" customFormat="1" spans="1:12">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2" t="s">
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:8">
+      <c r="C12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-    </row>
-    <row r="13" customFormat="1" spans="1:12">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="s">
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:8">
+      <c r="D13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-    </row>
-    <row r="14" customFormat="1" spans="1:12">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="s">
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:8">
+      <c r="D14"/>
+      <c r="E14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-    </row>
-    <row r="15" customFormat="1" spans="1:12">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2" t="s">
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:8">
+      <c r="E15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-    </row>
-    <row r="16" customFormat="1" spans="1:12">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2" t="s">
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:8">
+      <c r="D16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-    </row>
-    <row r="17" customFormat="1" spans="1:13">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2" t="s">
+    </row>
+    <row r="17" s="1" customFormat="1" spans="2:5">
+      <c r="E17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-    </row>
-    <row r="18" customFormat="1" spans="1:13">
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2" t="s">
+    </row>
+    <row r="18" s="1" customFormat="1" spans="2:5">
+      <c r="E18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-    </row>
-    <row r="19" customFormat="1" spans="1:13">
-      <c r="B19" s="2"/>
-      <c r="C19" s="2" t="s">
+    </row>
+    <row r="19" s="1" customFormat="1" spans="2:5">
+      <c r="D19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-    </row>
-    <row r="20" customFormat="1" spans="1:13">
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2" t="s">
+    </row>
+    <row r="20" s="1" customFormat="1" spans="2:5">
+      <c r="E20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-    </row>
-    <row r="21" customFormat="1" spans="1:13">
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2" t="s">
+    </row>
+    <row r="21" s="1" customFormat="1" spans="2:5">
+      <c r="E21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-    </row>
-    <row r="22" customFormat="1" spans="1:13">
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2" t="s">
+    </row>
+    <row r="22" s="1" customFormat="1" spans="2:5">
+      <c r="B22" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-    </row>
-    <row r="23" customFormat="1" spans="1:13">
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2" t="s">
+    </row>
+    <row r="23" s="1" customFormat="1" spans="2:5">
+      <c r="C23" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-    </row>
-    <row r="24" customFormat="1" spans="1:13">
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2" t="s">
+    </row>
+    <row r="24" s="1" customFormat="1" spans="2:5">
+      <c r="D24" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-    </row>
-    <row r="25" customFormat="1" spans="1:13">
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2" t="s">
+    </row>
+    <row r="25" s="1" customFormat="1" spans="2:5">
+      <c r="D25" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-    </row>
-    <row r="26" customFormat="1" spans="1:13">
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2" t="s">
+    </row>
+    <row r="26" s="1" customFormat="1" spans="2:5">
+      <c r="E26" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
-    </row>
-    <row r="27" customFormat="1" spans="1:13">
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2" t="s">
+    </row>
+    <row r="27" s="1" customFormat="1" spans="2:5">
+      <c r="E27" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
-    </row>
-    <row r="28" customFormat="1" spans="1:13">
-      <c r="B28" s="2" t="s">
+    </row>
+    <row r="28" s="1" customFormat="1" spans="2:5">
+      <c r="C28" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
-      <c r="M28" s="2"/>
-    </row>
-    <row r="29" customFormat="1" spans="1:13">
-      <c r="B29" s="2"/>
-      <c r="C29" s="2" t="s">
+    </row>
+    <row r="29" s="1" customFormat="1" spans="2:5">
+      <c r="D29" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-      <c r="L29" s="2"/>
-      <c r="M29" s="2"/>
-    </row>
-    <row r="30" customFormat="1" spans="1:13">
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2" t="s">
+    </row>
+    <row r="30" s="1" customFormat="1" spans="2:5">
+      <c r="D30" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-      <c r="L30" s="2"/>
-      <c r="M30" s="2"/>
-    </row>
-    <row r="31" customFormat="1" spans="1:13">
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2" t="s">
+    </row>
+    <row r="31" s="1" customFormat="1" spans="2:5">
+      <c r="E31" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
-      <c r="L31" s="2"/>
-      <c r="M31" s="2"/>
-    </row>
-    <row r="32" customFormat="1" spans="1:13">
-      <c r="B32" s="2"/>
-      <c r="C32" s="2" t="s">
+    </row>
+    <row r="32" s="1" customFormat="1" spans="2:5">
+      <c r="E32" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-      <c r="L32" s="2"/>
-      <c r="M32" s="2"/>
-    </row>
-    <row r="33" customFormat="1" spans="2:13">
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2" t="s">
+    </row>
+    <row r="33" s="1" customFormat="1" spans="2:5">
+      <c r="D33" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
-      <c r="M33" s="2"/>
-    </row>
-    <row r="34" customFormat="1" spans="2:13">
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2" t="s">
+    </row>
+    <row r="34" s="1" customFormat="1" spans="2:5">
+      <c r="E34" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
-      <c r="L34" s="2"/>
-      <c r="M34" s="2"/>
-    </row>
-    <row r="35" customFormat="1" spans="2:13">
-      <c r="B35" s="2"/>
-      <c r="C35" s="2" t="s">
+    </row>
+    <row r="35" s="1" customFormat="1" spans="2:5">
+      <c r="E35" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
-      <c r="L35" s="2"/>
-      <c r="M35" s="2"/>
-    </row>
-    <row r="36" customFormat="1" spans="2:13">
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2" t="s">
+    </row>
+    <row r="36" s="1" customFormat="1" spans="2:5">
+      <c r="E36" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
-      <c r="L36" s="2"/>
-      <c r="M36" s="2"/>
-    </row>
-    <row r="37" customFormat="1" spans="2:13">
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2" t="s">
+    </row>
+    <row r="37" s="1" customFormat="1" spans="2:5">
+      <c r="E37" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="2"/>
-      <c r="L37" s="2"/>
-      <c r="M37" s="2"/>
-    </row>
-    <row r="38" customFormat="1" spans="2:13">
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2" t="s">
+    </row>
+    <row r="38" s="1" customFormat="1" spans="2:5">
+      <c r="E38" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
-      <c r="L38" s="2"/>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" customFormat="1" spans="2:13">
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2" t="s">
+    </row>
+    <row r="39" s="1" customFormat="1" spans="2:5">
+      <c r="C39" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="2"/>
-      <c r="L39" s="2"/>
-      <c r="M39" s="2"/>
-    </row>
-    <row r="40" customFormat="1" spans="2:13">
-      <c r="B40" s="2"/>
-      <c r="C40" s="2" t="s">
+    </row>
+    <row r="40" s="1" customFormat="1" spans="2:5">
+      <c r="D40" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
-      <c r="K40" s="2"/>
-      <c r="L40" s="2"/>
-      <c r="M40" s="2"/>
-    </row>
-    <row r="41" customFormat="1" spans="2:13">
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2" t="s">
+    </row>
+    <row r="41" s="1" customFormat="1" spans="2:5">
+      <c r="D41" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="2"/>
-      <c r="K41" s="2"/>
-      <c r="L41" s="2"/>
-      <c r="M41" s="2"/>
-    </row>
-    <row r="42" customFormat="1" spans="2:13">
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2" t="s">
+    </row>
+    <row r="42" s="1" customFormat="1" spans="2:5">
+      <c r="B42" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="2"/>
-      <c r="K42" s="2"/>
-      <c r="L42" s="2"/>
-      <c r="M42" s="2"/>
-    </row>
-    <row r="43" customFormat="1" spans="2:13">
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2" t="s">
+    </row>
+    <row r="43" s="1" customFormat="1" spans="2:5">
+      <c r="C43" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="2"/>
-      <c r="K43" s="2"/>
-      <c r="L43" s="2"/>
-      <c r="M43" s="2"/>
-    </row>
-    <row r="44" customFormat="1" spans="2:13">
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2" t="s">
+    </row>
+    <row r="44" s="1" customFormat="1" spans="2:5">
+      <c r="D44" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="2"/>
-      <c r="K44" s="2"/>
-      <c r="L44" s="2"/>
-      <c r="M44" s="2"/>
-    </row>
-    <row r="45" customFormat="1" spans="2:13">
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2" t="s">
+    </row>
+    <row r="45" s="1" customFormat="1" spans="2:5">
+      <c r="E45" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
-      <c r="L45" s="2"/>
-      <c r="M45" s="2"/>
+    </row>
+    <row r="46" s="1" customFormat="1" spans="2:5">
+      <c r="E46" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" s="1" customFormat="1" spans="2:5">
+      <c r="D47" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" s="1" customFormat="1" spans="2:5">
+      <c r="E48" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" s="1" customFormat="1" spans="3:5">
+      <c r="E49" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" s="1" customFormat="1" spans="3:5">
+      <c r="C50" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51" s="1" customFormat="1" spans="3:5">
+      <c r="D51" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" s="1" customFormat="1" spans="3:5">
+      <c r="D52" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" s="1" customFormat="1" spans="3:5">
+      <c r="E53" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54" s="1" customFormat="1" spans="3:5">
+      <c r="E54" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="55" s="1" customFormat="1" spans="3:5">
+      <c r="C55" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="56" s="1" customFormat="1" spans="3:5">
+      <c r="D56" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="57" s="1" customFormat="1" spans="3:5">
+      <c r="E57" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" s="1" customFormat="1" spans="3:5">
+      <c r="E58" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="59" s="1" customFormat="1" spans="3:5">
+      <c r="D59" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="60" s="1" customFormat="1" spans="3:5">
+      <c r="E60" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="61" s="1" customFormat="1" spans="3:5">
+      <c r="E61" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="62" s="1" customFormat="1" spans="3:5">
+      <c r="D62" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="63" s="1" customFormat="1" spans="3:5">
+      <c r="E63" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64" s="1" customFormat="1" spans="3:5">
+      <c r="E64" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="65" s="1" customFormat="1" spans="2:6">
+      <c r="C65" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="66" s="1" customFormat="1" spans="2:6">
+      <c r="D66" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="67" s="1" customFormat="1" spans="2:6">
+      <c r="E67" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="68" s="1" customFormat="1" spans="2:6">
+      <c r="E68" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="69" s="1" customFormat="1" spans="2:6">
+      <c r="D69" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="70" s="1" customFormat="1" spans="2:6">
+      <c r="E70" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="71" s="1" customFormat="1" spans="2:6">
+      <c r="E71" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="72" s="1" customFormat="1" spans="2:6">
+      <c r="B72" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="73" s="1" customFormat="1" spans="2:6">
+      <c r="C73" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="74" s="1" customFormat="1" spans="2:6">
+      <c r="D74" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="75" s="1" customFormat="1" spans="2:6">
+      <c r="D75" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="76" s="1" customFormat="1" spans="2:6">
+      <c r="E76" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="77" s="1" customFormat="1" spans="2:6">
+      <c r="F77" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="78" s="1" customFormat="1" spans="2:6">
+      <c r="F78" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="79" s="1" customFormat="1" spans="2:6">
+      <c r="E79" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="80" s="1" customFormat="1" spans="2:6">
+      <c r="F80" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="81" s="1" customFormat="1" spans="3:6">
+      <c r="F81" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="82" s="1" customFormat="1" spans="3:6">
+      <c r="F82" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="83" s="1" customFormat="1" spans="3:6">
+      <c r="D83" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="84" s="1" customFormat="1" spans="3:6">
+      <c r="E84" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="85" s="1" customFormat="1" spans="3:6">
+      <c r="E85" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="86" s="1" customFormat="1" spans="3:6">
+      <c r="C86" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="87" s="1" customFormat="1" spans="3:6">
+      <c r="D87" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="88" s="1" customFormat="1" spans="3:6">
+      <c r="D88" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="89" s="1" customFormat="1" spans="3:6">
+      <c r="E89" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="90" s="1" customFormat="1" spans="3:6">
+      <c r="E90" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="91" s="1" customFormat="1" spans="3:6">
+      <c r="D91" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="92" s="1" customFormat="1" spans="3:6">
+      <c r="D92" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="93" s="1" customFormat="1" spans="3:6">
+      <c r="E93" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="94" s="1" customFormat="1" spans="3:6">
+      <c r="E94" s="1" t="s">
+        <v>92</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Note/测试.xlsx
+++ b/Note/测试.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11520" windowHeight="9180"/>
+    <workbookView windowWidth="23040" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="待处理" sheetId="1" r:id="rId1"/>
@@ -49,285 +49,261 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
-  <si>
-    <t>为什么要铸牢中华民族共同体意识### ###</t>
-  </si>
-  <si>
-    <t>一、主线定位：工作的核心</t>
-  </si>
-  <si>
-    <t>铸牢中华民族共同体意识是新时代党的民族工作的主线</t>
-  </si>
-  <si>
-    <t>是民族地区各项工作的主线</t>
-  </si>
-  <si>
-    <t>二、与共同体建设的关系：互为因果</t>
-  </si>
-  <si>
-    <t>建设的落脚点：推进中华民族共同体建设是铸牢中华民族共同体意识的落脚点</t>
-  </si>
-  <si>
-    <t>意识的核心性：铸牢中华民族共同体意识则是推进中华民族共同体建设的核心</t>
-  </si>
-  <si>
-    <t>三、历史与法理基础</t>
-  </si>
-  <si>
-    <t>国家的本质：中国是全国各族人民共同缔造的统一的多民族国家</t>
-  </si>
-  <si>
-    <t>形成的必然性：中华民族共同体的形成是中华民族历史发展的必然结果</t>
-  </si>
-  <si>
-    <t>四、铸牢意识的多重重要意义</t>
-  </si>
-  <si>
-    <t>首要意义：构筑思想长城</t>
-  </si>
-  <si>
-    <t>只有铸牢中华民族共同体意识</t>
-  </si>
-  <si>
-    <t>才能构建起维护国家统一和民族团结的坚固思想长城</t>
-  </si>
-  <si>
-    <t>第二意义：增进认同与夯实基础</t>
-  </si>
-  <si>
-    <t>增进自觉认同：才能增进各民族对中华民族的自觉认同</t>
-  </si>
-  <si>
-    <t>务实思想基础：务实我国民族关系发展的思想基础</t>
-  </si>
-  <si>
-    <t>第三意义：应对风险与提供保证</t>
-  </si>
-  <si>
-    <t>有效应对挑战：才能有效应对实现中华民族伟大复兴过程中民族领域可能发生的风险挑战</t>
-  </si>
-  <si>
-    <t>提供思想保证：为党和国家兴旺发达、长治久安提供重要思想保证</t>
-  </si>
-  <si>
-    <t>为什么要坚持和完善民族区域自治### ###</t>
-  </si>
-  <si>
-    <t>一、制度的根本定位与作用</t>
-  </si>
-  <si>
-    <t>基本政治制度：是我国的基本政治制度</t>
-  </si>
-  <si>
-    <t>解决民族问题的内容与保障</t>
-  </si>
-  <si>
-    <t>正确道路的核心内容：是中国特色解决民族问题的正确道路的重要内容</t>
-  </si>
-  <si>
-    <t>制度保障：是中国特色解决民族问题的正确道路的制度保障</t>
-  </si>
-  <si>
-    <t>二、实践成就与制度优越性</t>
-  </si>
-  <si>
-    <t>巨大成就的证明：民族区域自治地区几十年来取得的巨大成就说明该制度具有优越性</t>
-  </si>
-  <si>
-    <t>制度的核心原则</t>
-  </si>
-  <si>
-    <t>结合统一与自治：坚持统一和自治相结合</t>
-  </si>
-  <si>
-    <t>结合民族与区域因素：坚持民族因素和区域因素相结合</t>
-  </si>
-  <si>
-    <t>制度的多重积极效能：促进民族共同目标</t>
-  </si>
-  <si>
-    <t>促进团结奋斗：能够促进各民族共同团结奋斗</t>
-  </si>
-  <si>
-    <t>促进繁荣发展：能够促进各民族共同繁荣发展</t>
-  </si>
-  <si>
-    <t>巩固国家统一：有利于巩固国家统一</t>
-  </si>
-  <si>
-    <t>增强民族凝聚力：有利于增强中华民族凝聚力</t>
-  </si>
-  <si>
-    <t>推动共同繁荣：有利于各民族共同繁荣发展</t>
-  </si>
-  <si>
-    <t>三、对制度的总结与立场</t>
-  </si>
-  <si>
-    <t>显著优越性：该制度具有显著优越性</t>
-  </si>
-  <si>
-    <t>根本态度与要求：应当坚持和完善</t>
-  </si>
-  <si>
-    <t>辛亥革命是伟大而艰辛的探索### ###</t>
-  </si>
-  <si>
-    <t>一、鸦片战争后的社会性质与民族梦想</t>
-  </si>
-  <si>
-    <t>社会性质的转变</t>
-  </si>
-  <si>
-    <t>外部入侵与内部统治：1840年鸦片战争后，西方列强入侵，封建统治腐败</t>
-  </si>
-  <si>
-    <t>社会性质的质变：中国逐步成为半殖民地半封建社会</t>
-  </si>
-  <si>
-    <t>民族劫难与伟大梦想的诞生</t>
-  </si>
-  <si>
-    <t>空前劫难：中国人民和中华民族遭受了前所未有的劫难</t>
-  </si>
-  <si>
-    <t>梦想的起点：从那时起，实现中华民族伟大复兴就成为中华民族最伟大的梦想</t>
-  </si>
-  <si>
-    <t>二、辛亥革命：近代民族民主革命的序幕：革命的开端</t>
-  </si>
-  <si>
-    <t>标志性事件：1911年10月10日，武昌城头枪声一响</t>
-  </si>
-  <si>
-    <t>双重序幕的拉开</t>
-  </si>
-  <si>
-    <t>拉开了中国完全意义上的近代民族民主革命的序幕</t>
-  </si>
-  <si>
-    <t>近代以来中国发生的深刻社会变革也由此拉开了序幕</t>
-  </si>
-  <si>
-    <t>三、辛亥革命的多重历史意义</t>
-  </si>
-  <si>
-    <t>政治制度的终结</t>
-  </si>
-  <si>
-    <t>推翻了清朝政府</t>
-  </si>
-  <si>
-    <t>结束了在中国延续几千年的君主专制制度</t>
-  </si>
-  <si>
-    <t>思想的解放与统治根基的撼动</t>
-  </si>
-  <si>
-    <t>促进思想解放：极大促进了中华民族的思想解放</t>
-  </si>
-  <si>
-    <t>撼动统治秩序：撼动了反动统治秩序的根基</t>
-  </si>
-  <si>
-    <t>推动社会变革与探索复兴道路</t>
-  </si>
-  <si>
-    <t>变革的推动力：以巨大的震撼力和深刻的影响力推动了中国社会变革</t>
-  </si>
-  <si>
-    <t>道路的探索：为实现中华民族伟大复兴探索了道路</t>
-  </si>
-  <si>
-    <t>四、辛亥革命的局限性</t>
-  </si>
-  <si>
-    <t>未改变的社会性质与人民命运</t>
-  </si>
-  <si>
-    <t>但是，辛亥革命未能改变中国半殖民地半封建的社会性质</t>
-  </si>
-  <si>
-    <t>未能改变中国人民的悲惨命运</t>
-  </si>
-  <si>
-    <t>新的历史迫切需求</t>
-  </si>
-  <si>
-    <t>需要新思想：中国迫切需要新的思想引领救亡运动</t>
-  </si>
-  <si>
-    <t>需要新组织：迫切需要新的组织凝聚革命力量</t>
-  </si>
-  <si>
-    <t>中共是孙中山革命事业的支持者和继承者### ###</t>
-  </si>
-  <si>
-    <t>一、历史继承：完成孙中山的未竟事业</t>
-  </si>
-  <si>
-    <t>孙中山先生生前：坚定支持：中国共产党人坚定支持他的事业</t>
-  </si>
-  <si>
-    <t>孙中山先生身后</t>
-  </si>
-  <si>
-    <t>忠实继承遗志</t>
-  </si>
-  <si>
-    <t>付出牺牲：忠实继承孙中山先生的遗志，付出巨大牺牲</t>
-  </si>
-  <si>
-    <t>完成未竟事业：完成了孙中山先生的未竟事业</t>
-  </si>
-  <si>
-    <t>取得革命胜利</t>
-  </si>
-  <si>
-    <t>新民主主义革命：取得了新民主主义革命胜利</t>
-  </si>
-  <si>
-    <t>建立新中国：建立了人民当家作主的中华人民共和国</t>
-  </si>
-  <si>
-    <t>实现独立解放：实现了民族独立、人民解放</t>
-  </si>
-  <si>
-    <t>基础上的继续奋斗</t>
-  </si>
-  <si>
-    <t>完成社会主义革命：完成了社会主义革命</t>
-  </si>
-  <si>
-    <t>确立社会主义制度：确立了社会主义制度</t>
-  </si>
-  <si>
-    <t>二、当今发展：超越蓝图的现实成就</t>
-  </si>
-  <si>
-    <t>成就的创造主体与基础：党的领导与人民奋斗：在中国共产党领导下，在全国各族人民顽强奋斗下</t>
-  </si>
-  <si>
-    <t>对孙中山蓝图的实现与超越</t>
-  </si>
-  <si>
-    <t>蓝图早已实现：孙中山先生当年描绘的蓝图早已实现</t>
-  </si>
-  <si>
-    <t>成就远超设想：中国人民创造的许多成就远远超出了孙中山先生的设想</t>
-  </si>
-  <si>
-    <t>国家的现实状态：巍然屹立东方：孙中山先生致力于建设的独立、民主、富强的国家早已巍然屹立在世界东方</t>
-  </si>
-  <si>
-    <t>民族复兴的历史方位</t>
-  </si>
-  <si>
-    <t>更接近目标：我们比历史上任何时候都更接近中华民族伟大复兴的目标</t>
-  </si>
-  <si>
-    <t>更有信心能力：比历史上任何时期都更有信心、有能力实现这个目标</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
+  <si>
+    <t>平凡岗位与实现社会价值### ###</t>
+  </si>
+  <si>
+    <t>一、根本尺度的客观标准：核心依据：是否符合社会规律、促进历史进步</t>
+  </si>
+  <si>
+    <t>实践活动的检验标准：看一个人的实践活动是否符合社会发展的客观规律</t>
+  </si>
+  <si>
+    <t>历史作用的检验标准：看一个人的实践活动是否促进了历史的进步</t>
+  </si>
+  <si>
+    <t>二、当今社会的具体衡量标准：核心标准：为国家社会奉献，为人民服务</t>
+  </si>
+  <si>
+    <t>奉献才智：看一个人是否用自己的劳动和聪明才智为国家和社会真诚奉献</t>
+  </si>
+  <si>
+    <t>尽心服务：看一个人是否为人民群众尽心尽力服务</t>
+  </si>
+  <si>
+    <t>三、对奉献与平凡价值的阐释</t>
+  </si>
+  <si>
+    <t>核心观点：奉献即成功，平凡孕伟大</t>
+  </si>
+  <si>
+    <t>成功的本质：成功在于奉献</t>
+  </si>
+  <si>
+    <t>伟大的源泉：平凡孕育伟大</t>
+  </si>
+  <si>
+    <t>对普通劳动者的激励与肯定</t>
+  </si>
+  <si>
+    <t>实现价值的前提：只要有志气、有闯劲</t>
+  </si>
+  <si>
+    <t>实现价值的场域：普通劳动者都可以在宽广舞台上实现自己的人生价值</t>
+  </si>
+  <si>
+    <t>实现价值的方式：在平凡岗位上干出不平凡的业绩</t>
+  </si>
+  <si>
+    <t>弘扬志愿精神### ###</t>
+  </si>
+  <si>
+    <t>一、志愿服务的精神内涵</t>
+  </si>
+  <si>
+    <t>核心定义：志愿服务的精神是奉献、友爱、互助、进步</t>
+  </si>
+  <si>
+    <t>精神精髓：核心是奉献：其中，奉献精神是精髓</t>
+  </si>
+  <si>
+    <t>二、志愿服务活动的双重作用</t>
+  </si>
+  <si>
+    <t>对社会的作用</t>
+  </si>
+  <si>
+    <t>直接帮助：帮助了他人</t>
+  </si>
+  <si>
+    <t>服务社会：服务了社会</t>
+  </si>
+  <si>
+    <t>道德提升：推动了社会道德水平的提高</t>
+  </si>
+  <si>
+    <t>对个人的作用</t>
+  </si>
+  <si>
+    <t>视为义务与职责：把为社会和他人的服务看作自己应尽的义务和光荣的职责</t>
+  </si>
+  <si>
+    <t>获得内在回报</t>
+  </si>
+  <si>
+    <t>得到成就感：从服务社会和帮助他人中获得成就感</t>
+  </si>
+  <si>
+    <t>得到幸福感：获得幸福感</t>
+  </si>
+  <si>
+    <t>三、对新时代青年的核心要求</t>
+  </si>
+  <si>
+    <t>结合自身提供服务</t>
+  </si>
+  <si>
+    <t>匹配能力特长：应结合自身的能力、专业、特长</t>
+  </si>
+  <si>
+    <t>提供优质服务：在最需要的地方提供优质高效的服务</t>
+  </si>
+  <si>
+    <t>关爱特定群体：为最需要关爱的群体送温暖、献爱心</t>
+  </si>
+  <si>
+    <t>实现自我成长：增长知识与才干</t>
+  </si>
+  <si>
+    <t>在志愿服务中长知识</t>
+  </si>
+  <si>
+    <t>强本领</t>
+  </si>
+  <si>
+    <t>增才干</t>
+  </si>
+  <si>
+    <t>为什么要推进平等有序的世界多极化### ###</t>
+  </si>
+  <si>
+    <t>一、世界多极化的基本定位：当代趋势与历史方向</t>
+  </si>
+  <si>
+    <t>多极化是当今世界的基本趋势</t>
+  </si>
+  <si>
+    <t>也是历史进步的方向</t>
+  </si>
+  <si>
+    <t>二、平等的世界多极化</t>
+  </si>
+  <si>
+    <t>核心原则：国家不分大小强弱，均应在多极化进程中平等参与、享受权利、发挥作用</t>
+  </si>
+  <si>
+    <t>具体目标与实践方向</t>
+  </si>
+  <si>
+    <t>推进国际关系民主化：切实推进国际关系民主化</t>
+  </si>
+  <si>
+    <t>增强发展中国家话语权：增强广大发展中国家的代表性和发言权</t>
+  </si>
+  <si>
+    <t>反对霸权与强权：反对霸权主义和强权政治</t>
+  </si>
+  <si>
+    <t>三、有序的世界多极化</t>
+  </si>
+  <si>
+    <t>维护的三大核心支柱</t>
+  </si>
+  <si>
+    <t>以联合国为核心：坚定维护以联合国为核心的国际体系</t>
+  </si>
+  <si>
+    <t>以国际法为基础：维护以国际法为基础的国际秩序</t>
+  </si>
+  <si>
+    <t>以宪章宗旨原则为基础：维护以联合国宪章宗旨和原则为基础的国际关系基本准则</t>
+  </si>
+  <si>
+    <t>秉持的理念与反对的倾向</t>
+  </si>
+  <si>
+    <t>秉持真正多边主义</t>
+  </si>
+  <si>
+    <t>反对错误倾向</t>
+  </si>
+  <si>
+    <t>反对阵营化</t>
+  </si>
+  <si>
+    <t>反对碎片化</t>
+  </si>
+  <si>
+    <t>反对无序化</t>
+  </si>
+  <si>
+    <t>四、平等有序世界多极化的意义</t>
+  </si>
+  <si>
+    <t>契合普遍诉求：契合了大多数国家和各国民众的普遍诉求</t>
+  </si>
+  <si>
+    <t>指明未来方向：走向长治久安：为国际社会从变乱交织走向长治久安指明了方向</t>
+  </si>
+  <si>
+    <t>提供重要路径</t>
+  </si>
+  <si>
+    <t>推动构建全球治理体系：为推动构建公正合理的全球治理体系提供了重要路径</t>
+  </si>
+  <si>
+    <t>推动构建人类命运共同体：为推动构建人类命运共同体提供了重要路径</t>
+  </si>
+  <si>
+    <t>为什么要坚守多边主义### ###</t>
+  </si>
+  <si>
+    <t>一、历史所昭示的核心论断：多边主义的根本定位</t>
+  </si>
+  <si>
+    <t>是人心所向：多边主义是人心所向</t>
+  </si>
+  <si>
+    <t>是大势所趋</t>
+  </si>
+  <si>
+    <t>关键依靠：对和平与发展的意义：是世界和平与发展的重要依靠</t>
+  </si>
+  <si>
+    <t>二、当前世界面临的突出问题</t>
+  </si>
+  <si>
+    <t>三大失衡失序</t>
+  </si>
+  <si>
+    <t>安全失序</t>
+  </si>
+  <si>
+    <t>发展失衡</t>
+  </si>
+  <si>
+    <t>治理失效</t>
+  </si>
+  <si>
+    <t>具体矛盾冲突频发</t>
+  </si>
+  <si>
+    <t>热点冲突</t>
+  </si>
+  <si>
+    <t>大国对抗</t>
+  </si>
+  <si>
+    <t>地缘矛盾</t>
+  </si>
+  <si>
+    <t>引发的普遍忧虑：对未来的担忧：人们对这个星球的未来更为忧虑</t>
+  </si>
+  <si>
+    <t>三、应对变局的必然选择</t>
+  </si>
+  <si>
+    <t>总体形势判断：国际形势变乱交织</t>
+  </si>
+  <si>
+    <t>应对挑战的根本路径</t>
+  </si>
+  <si>
+    <t>针对当下：应对当前全球性挑战，多边主义是必然选择</t>
+  </si>
+  <si>
+    <t>面向未来：共创人类美好明天，多边主义是必然选择</t>
   </si>
 </sst>
 </file>
@@ -1265,7 +1241,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H94"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="9.66666666666667" style="1"/>
@@ -1275,7 +1251,7 @@
     <row r="1" s="1" customFormat="1" spans="1:8">
       <c r="A1" s="2">
         <f>SUM(B1:AZ1)</f>
-        <v>22.9666666666667</v>
+        <v>21.2666666666667</v>
       </c>
       <c r="B1" s="2">
         <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2220)/COLUMN()</f>
@@ -1287,11 +1263,11 @@
       </c>
       <c r="D1" s="2">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="E1" s="2">
         <f t="shared" si="0"/>
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="F1" s="2">
         <f t="shared" si="0"/>
@@ -1356,12 +1332,12 @@
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:8">
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:8">
-      <c r="C12" s="1" t="s">
+      <c r="E12" s="1" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1371,7 +1347,6 @@
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:8">
-      <c r="D14"/>
       <c r="E14" s="1" t="s">
         <v>12</v>
       </c>
@@ -1382,92 +1357,92 @@
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:8">
-      <c r="D16" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" spans="2:5">
-      <c r="E17" s="1" t="s">
+    <row r="17" s="1" customFormat="1" spans="2:6">
+      <c r="B17" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" spans="2:5">
-      <c r="E18" s="1" t="s">
+    <row r="18" s="1" customFormat="1" spans="2:6">
+      <c r="C18" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" spans="2:5">
+    <row r="19" s="1" customFormat="1" spans="2:6">
       <c r="D19" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" spans="2:5">
-      <c r="E20" s="1" t="s">
+    <row r="20" s="1" customFormat="1" spans="2:6">
+      <c r="D20" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" spans="2:5">
-      <c r="E21" s="1" t="s">
+    <row r="21" s="1" customFormat="1" spans="2:6">
+      <c r="C21" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" spans="2:5">
-      <c r="B22" s="1" t="s">
+    <row r="22" s="1" customFormat="1" spans="2:6">
+      <c r="D22" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" spans="2:5">
-      <c r="C23" s="1" t="s">
+    <row r="23" s="1" customFormat="1" spans="2:6">
+      <c r="E23" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" spans="2:5">
-      <c r="D24" s="1" t="s">
+    <row r="24" s="1" customFormat="1" spans="2:6">
+      <c r="E24" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" spans="2:5">
-      <c r="D25" s="1" t="s">
+    <row r="25" s="1" customFormat="1" spans="2:6">
+      <c r="E25" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" spans="2:5">
-      <c r="E26" s="1" t="s">
+    <row r="26" s="1" customFormat="1" spans="2:6">
+      <c r="D26" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" spans="2:5">
+    <row r="27" s="1" customFormat="1" spans="2:6">
       <c r="E27" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" spans="2:5">
-      <c r="C28" s="1" t="s">
+    <row r="28" s="1" customFormat="1" spans="2:6">
+      <c r="E28" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" spans="2:5">
-      <c r="D29" s="1" t="s">
+    <row r="29" s="1" customFormat="1" spans="2:6">
+      <c r="F29" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" spans="2:5">
-      <c r="D30" s="1" t="s">
+    <row r="30" s="1" customFormat="1" spans="2:6">
+      <c r="F30" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" spans="2:5">
-      <c r="E31" s="1" t="s">
+    <row r="31" s="1" customFormat="1" spans="2:6">
+      <c r="C31" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="32" s="1" customFormat="1" spans="2:5">
-      <c r="E32" s="1" t="s">
+    <row r="32" s="1" customFormat="1" spans="2:6">
+      <c r="D32" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" spans="2:5">
-      <c r="D33" s="1" t="s">
+      <c r="E33" s="1" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1477,12 +1452,12 @@
       </c>
     </row>
     <row r="35" s="1" customFormat="1" spans="2:5">
-      <c r="E35" s="1" t="s">
+      <c r="D35" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" spans="2:5">
-      <c r="E36" s="1" t="s">
+      <c r="D36" s="1" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1497,47 +1472,47 @@
       </c>
     </row>
     <row r="39" s="1" customFormat="1" spans="2:5">
-      <c r="C39" s="1" t="s">
+      <c r="E39" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" spans="2:5">
-      <c r="D40" s="1" t="s">
+      <c r="B40" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" spans="2:5">
-      <c r="D41" s="1" t="s">
+      <c r="C41" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" spans="2:5">
-      <c r="B42" s="1" t="s">
+      <c r="D42" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" spans="2:5">
-      <c r="C43" s="1" t="s">
+      <c r="D43" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" spans="2:5">
-      <c r="D44" s="1" t="s">
+      <c r="C44" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" spans="2:5">
-      <c r="E45" s="1" t="s">
+      <c r="D45" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" spans="2:5">
-      <c r="E46" s="1" t="s">
+      <c r="D46" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" spans="2:5">
-      <c r="D47" s="1" t="s">
+      <c r="E47" s="1" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1546,234 +1521,196 @@
         <v>46</v>
       </c>
     </row>
-    <row r="49" s="1" customFormat="1" spans="3:5">
+    <row r="49" s="1" customFormat="1" spans="3:6">
       <c r="E49" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="50" s="1" customFormat="1" spans="3:5">
+    <row r="50" s="1" customFormat="1" spans="3:6">
       <c r="C50" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="51" s="1" customFormat="1" spans="3:5">
+    <row r="51" s="1" customFormat="1" spans="3:6">
       <c r="D51" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="52" s="1" customFormat="1" spans="3:5">
-      <c r="D52" s="1" t="s">
+    <row r="52" s="1" customFormat="1" spans="3:6">
+      <c r="E52" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="53" s="1" customFormat="1" spans="3:5">
+    <row r="53" s="1" customFormat="1" spans="3:6">
       <c r="E53" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="54" s="1" customFormat="1" spans="3:5">
+    <row r="54" s="1" customFormat="1" spans="3:6">
       <c r="E54" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="55" s="1" customFormat="1" spans="3:5">
-      <c r="C55" s="1" t="s">
+    <row r="55" s="1" customFormat="1" spans="3:6">
+      <c r="D55" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="56" s="1" customFormat="1" spans="3:5">
-      <c r="D56" s="1" t="s">
+    <row r="56" s="1" customFormat="1" spans="3:6">
+      <c r="E56" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="57" s="1" customFormat="1" spans="3:5">
+    <row r="57" s="1" customFormat="1" spans="3:6">
       <c r="E57" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="58" s="1" customFormat="1" spans="3:5">
-      <c r="E58" s="1" t="s">
+    <row r="58" s="1" customFormat="1" spans="3:6">
+      <c r="D58"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="59" s="1" customFormat="1" spans="3:5">
-      <c r="D59" s="1" t="s">
+    <row r="59" s="1" customFormat="1" spans="3:6">
+      <c r="F59" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="60" s="1" customFormat="1" spans="3:5">
-      <c r="E60" s="1" t="s">
+    <row r="60" s="1" customFormat="1" spans="3:6">
+      <c r="F60" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="61" s="1" customFormat="1" spans="3:5">
-      <c r="E61" s="1" t="s">
+    <row r="61" s="1" customFormat="1" spans="3:6">
+      <c r="C61" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="62" s="1" customFormat="1" spans="3:5">
+    <row r="62" s="1" customFormat="1" spans="3:6">
       <c r="D62" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="63" s="1" customFormat="1" spans="3:5">
-      <c r="E63" s="1" t="s">
+    <row r="63" s="1" customFormat="1" spans="3:6">
+      <c r="D63" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="64" s="1" customFormat="1" spans="3:5">
-      <c r="E64" s="1" t="s">
+    <row r="64" s="1" customFormat="1" spans="3:6">
+      <c r="D64" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="65" s="1" customFormat="1" spans="2:6">
-      <c r="C65" s="1" t="s">
+    <row r="65" s="1" customFormat="1" spans="2:5">
+      <c r="E65" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="66" s="1" customFormat="1" spans="2:6">
-      <c r="D66" s="1" t="s">
+    <row r="66" s="1" customFormat="1" spans="2:5">
+      <c r="E66" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="67" s="1" customFormat="1" spans="2:6">
-      <c r="E67" s="1" t="s">
+    <row r="67" s="1" customFormat="1" spans="2:5">
+      <c r="B67" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="68" s="1" customFormat="1" spans="2:6">
-      <c r="E68" s="1" t="s">
+    <row r="68" s="1" customFormat="1" spans="2:5">
+      <c r="C68" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="69" s="1" customFormat="1" spans="2:6">
+    <row r="69" s="1" customFormat="1" spans="2:5">
       <c r="D69" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="70" s="1" customFormat="1" spans="2:6">
-      <c r="E70" s="1" t="s">
+    <row r="70" s="1" customFormat="1" spans="2:5">
+      <c r="D70" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="71" s="1" customFormat="1" spans="2:6">
-      <c r="E71" s="1" t="s">
+    <row r="71" s="1" customFormat="1" spans="2:5">
+      <c r="D71" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="72" s="1" customFormat="1" spans="2:6">
-      <c r="B72" s="1" t="s">
+    <row r="72" s="1" customFormat="1" spans="2:5">
+      <c r="C72" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="73" s="1" customFormat="1" spans="2:6">
-      <c r="C73" s="1" t="s">
+    <row r="73" s="1" customFormat="1" spans="2:5">
+      <c r="D73" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="74" s="1" customFormat="1" spans="2:6">
-      <c r="D74" s="1" t="s">
+    <row r="74" s="1" customFormat="1" spans="2:5">
+      <c r="E74" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="75" s="1" customFormat="1" spans="2:6">
-      <c r="D75" s="1" t="s">
+    <row r="75" s="1" customFormat="1" spans="2:5">
+      <c r="E75" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="76" s="1" customFormat="1" spans="2:6">
+    <row r="76" s="1" customFormat="1" spans="2:5">
       <c r="E76" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="77" s="1" customFormat="1" spans="2:6">
-      <c r="F77" s="1" t="s">
+    <row r="77" s="1" customFormat="1" spans="2:5">
+      <c r="D77" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="78" s="1" customFormat="1" spans="2:6">
-      <c r="F78" s="1" t="s">
+    <row r="78" s="1" customFormat="1" spans="2:5">
+      <c r="E78" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="79" s="1" customFormat="1" spans="2:6">
+    <row r="79" s="1" customFormat="1" spans="2:5">
       <c r="E79" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="80" s="1" customFormat="1" spans="2:6">
-      <c r="F80" s="1" t="s">
+    <row r="80" s="1" customFormat="1" spans="2:5">
+      <c r="E80" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="81" s="1" customFormat="1" spans="3:6">
-      <c r="F81" s="1" t="s">
+    <row r="81" s="1" customFormat="1" spans="3:5">
+      <c r="D81" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="82" s="1" customFormat="1" spans="3:6">
-      <c r="F82" s="1" t="s">
+    <row r="82" s="1" customFormat="1" spans="3:5">
+      <c r="C82" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="83" s="1" customFormat="1" spans="3:6">
+    <row r="83" s="1" customFormat="1" spans="3:5">
       <c r="D83" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="84" s="1" customFormat="1" spans="3:6">
-      <c r="E84" s="1" t="s">
+    <row r="84" s="1" customFormat="1" spans="3:5">
+      <c r="D84" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="85" s="1" customFormat="1" spans="3:6">
+    <row r="85" s="1" customFormat="1" spans="3:5">
       <c r="E85" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="86" s="1" customFormat="1" spans="3:6">
-      <c r="C86" s="1" t="s">
+    <row r="86" s="1" customFormat="1" spans="3:5">
+      <c r="E86" s="1" t="s">
         <v>84</v>
-      </c>
-    </row>
-    <row r="87" s="1" customFormat="1" spans="3:6">
-      <c r="D87" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="88" s="1" customFormat="1" spans="3:6">
-      <c r="D88" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="89" s="1" customFormat="1" spans="3:6">
-      <c r="E89" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="90" s="1" customFormat="1" spans="3:6">
-      <c r="E90" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="91" s="1" customFormat="1" spans="3:6">
-      <c r="D91" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="92" s="1" customFormat="1" spans="3:6">
-      <c r="D92" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="93" s="1" customFormat="1" spans="3:6">
-      <c r="E93" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="94" s="1" customFormat="1" spans="3:6">
-      <c r="E94" s="1" t="s">
-        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/Note/测试.xlsx
+++ b/Note/测试.xlsx
@@ -49,261 +49,231 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
-  <si>
-    <t>平凡岗位与实现社会价值### ###</t>
-  </si>
-  <si>
-    <t>一、根本尺度的客观标准：核心依据：是否符合社会规律、促进历史进步</t>
-  </si>
-  <si>
-    <t>实践活动的检验标准：看一个人的实践活动是否符合社会发展的客观规律</t>
-  </si>
-  <si>
-    <t>历史作用的检验标准：看一个人的实践活动是否促进了历史的进步</t>
-  </si>
-  <si>
-    <t>二、当今社会的具体衡量标准：核心标准：为国家社会奉献，为人民服务</t>
-  </si>
-  <si>
-    <t>奉献才智：看一个人是否用自己的劳动和聪明才智为国家和社会真诚奉献</t>
-  </si>
-  <si>
-    <t>尽心服务：看一个人是否为人民群众尽心尽力服务</t>
-  </si>
-  <si>
-    <t>三、对奉献与平凡价值的阐释</t>
-  </si>
-  <si>
-    <t>核心观点：奉献即成功，平凡孕伟大</t>
-  </si>
-  <si>
-    <t>成功的本质：成功在于奉献</t>
-  </si>
-  <si>
-    <t>伟大的源泉：平凡孕育伟大</t>
-  </si>
-  <si>
-    <t>对普通劳动者的激励与肯定</t>
-  </si>
-  <si>
-    <t>实现价值的前提：只要有志气、有闯劲</t>
-  </si>
-  <si>
-    <t>实现价值的场域：普通劳动者都可以在宽广舞台上实现自己的人生价值</t>
-  </si>
-  <si>
-    <t>实现价值的方式：在平凡岗位上干出不平凡的业绩</t>
-  </si>
-  <si>
-    <t>弘扬志愿精神### ###</t>
-  </si>
-  <si>
-    <t>一、志愿服务的精神内涵</t>
-  </si>
-  <si>
-    <t>核心定义：志愿服务的精神是奉献、友爱、互助、进步</t>
-  </si>
-  <si>
-    <t>精神精髓：核心是奉献：其中，奉献精神是精髓</t>
-  </si>
-  <si>
-    <t>二、志愿服务活动的双重作用</t>
-  </si>
-  <si>
-    <t>对社会的作用</t>
-  </si>
-  <si>
-    <t>直接帮助：帮助了他人</t>
-  </si>
-  <si>
-    <t>服务社会：服务了社会</t>
-  </si>
-  <si>
-    <t>道德提升：推动了社会道德水平的提高</t>
-  </si>
-  <si>
-    <t>对个人的作用</t>
-  </si>
-  <si>
-    <t>视为义务与职责：把为社会和他人的服务看作自己应尽的义务和光荣的职责</t>
-  </si>
-  <si>
-    <t>获得内在回报</t>
-  </si>
-  <si>
-    <t>得到成就感：从服务社会和帮助他人中获得成就感</t>
-  </si>
-  <si>
-    <t>得到幸福感：获得幸福感</t>
-  </si>
-  <si>
-    <t>三、对新时代青年的核心要求</t>
-  </si>
-  <si>
-    <t>结合自身提供服务</t>
-  </si>
-  <si>
-    <t>匹配能力特长：应结合自身的能力、专业、特长</t>
-  </si>
-  <si>
-    <t>提供优质服务：在最需要的地方提供优质高效的服务</t>
-  </si>
-  <si>
-    <t>关爱特定群体：为最需要关爱的群体送温暖、献爱心</t>
-  </si>
-  <si>
-    <t>实现自我成长：增长知识与才干</t>
-  </si>
-  <si>
-    <t>在志愿服务中长知识</t>
-  </si>
-  <si>
-    <t>强本领</t>
-  </si>
-  <si>
-    <t>增才干</t>
-  </si>
-  <si>
-    <t>为什么要推进平等有序的世界多极化### ###</t>
-  </si>
-  <si>
-    <t>一、世界多极化的基本定位：当代趋势与历史方向</t>
-  </si>
-  <si>
-    <t>多极化是当今世界的基本趋势</t>
-  </si>
-  <si>
-    <t>也是历史进步的方向</t>
-  </si>
-  <si>
-    <t>二、平等的世界多极化</t>
-  </si>
-  <si>
-    <t>核心原则：国家不分大小强弱，均应在多极化进程中平等参与、享受权利、发挥作用</t>
-  </si>
-  <si>
-    <t>具体目标与实践方向</t>
-  </si>
-  <si>
-    <t>推进国际关系民主化：切实推进国际关系民主化</t>
-  </si>
-  <si>
-    <t>增强发展中国家话语权：增强广大发展中国家的代表性和发言权</t>
-  </si>
-  <si>
-    <t>反对霸权与强权：反对霸权主义和强权政治</t>
-  </si>
-  <si>
-    <t>三、有序的世界多极化</t>
-  </si>
-  <si>
-    <t>维护的三大核心支柱</t>
-  </si>
-  <si>
-    <t>以联合国为核心：坚定维护以联合国为核心的国际体系</t>
-  </si>
-  <si>
-    <t>以国际法为基础：维护以国际法为基础的国际秩序</t>
-  </si>
-  <si>
-    <t>以宪章宗旨原则为基础：维护以联合国宪章宗旨和原则为基础的国际关系基本准则</t>
-  </si>
-  <si>
-    <t>秉持的理念与反对的倾向</t>
-  </si>
-  <si>
-    <t>秉持真正多边主义</t>
-  </si>
-  <si>
-    <t>反对错误倾向</t>
-  </si>
-  <si>
-    <t>反对阵营化</t>
-  </si>
-  <si>
-    <t>反对碎片化</t>
-  </si>
-  <si>
-    <t>反对无序化</t>
-  </si>
-  <si>
-    <t>四、平等有序世界多极化的意义</t>
-  </si>
-  <si>
-    <t>契合普遍诉求：契合了大多数国家和各国民众的普遍诉求</t>
-  </si>
-  <si>
-    <t>指明未来方向：走向长治久安：为国际社会从变乱交织走向长治久安指明了方向</t>
-  </si>
-  <si>
-    <t>提供重要路径</t>
-  </si>
-  <si>
-    <t>推动构建全球治理体系：为推动构建公正合理的全球治理体系提供了重要路径</t>
-  </si>
-  <si>
-    <t>推动构建人类命运共同体：为推动构建人类命运共同体提供了重要路径</t>
-  </si>
-  <si>
-    <t>为什么要坚守多边主义### ###</t>
-  </si>
-  <si>
-    <t>一、历史所昭示的核心论断：多边主义的根本定位</t>
-  </si>
-  <si>
-    <t>是人心所向：多边主义是人心所向</t>
-  </si>
-  <si>
-    <t>是大势所趋</t>
-  </si>
-  <si>
-    <t>关键依靠：对和平与发展的意义：是世界和平与发展的重要依靠</t>
-  </si>
-  <si>
-    <t>二、当前世界面临的突出问题</t>
-  </si>
-  <si>
-    <t>三大失衡失序</t>
-  </si>
-  <si>
-    <t>安全失序</t>
-  </si>
-  <si>
-    <t>发展失衡</t>
-  </si>
-  <si>
-    <t>治理失效</t>
-  </si>
-  <si>
-    <t>具体矛盾冲突频发</t>
-  </si>
-  <si>
-    <t>热点冲突</t>
-  </si>
-  <si>
-    <t>大国对抗</t>
-  </si>
-  <si>
-    <t>地缘矛盾</t>
-  </si>
-  <si>
-    <t>引发的普遍忧虑：对未来的担忧：人们对这个星球的未来更为忧虑</t>
-  </si>
-  <si>
-    <t>三、应对变局的必然选择</t>
-  </si>
-  <si>
-    <t>总体形势判断：国际形势变乱交织</t>
-  </si>
-  <si>
-    <t>应对挑战的根本路径</t>
-  </si>
-  <si>
-    <t>针对当下：应对当前全球性挑战，多边主义是必然选择</t>
-  </si>
-  <si>
-    <t>面向未来：共创人类美好明天，多边主义是必然选择</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
+  <si>
+    <t>KMP（nextval及补充笔记）### ###</t>
+  </si>
+  <si>
+    <t>用目前的算法，指针跳转是不需要变的</t>
+  </si>
+  <si>
+    <t>但如果题目本身问next和nextval，全部数值还要加1</t>
+  </si>
+  <si>
+    <t>nextval计算</t>
+  </si>
+  <si>
+    <t>nextval[0]固定是-1</t>
+  </si>
+  <si>
+    <t>到了nextval[i]，初始化temp=i</t>
+  </si>
+  <si>
+    <t>看pattern[temp]和pattern[next[temp]]是否相等</t>
+  </si>
+  <si>
+    <t>如果不相同，nextval[i]=next[temp]</t>
+  </si>
+  <si>
+    <t>如果相同，设定temp=next[temp]，然后继续判断</t>
+  </si>
+  <si>
+    <t>直到pattern[temp]和pattern[next[temp]]不相同</t>
+  </si>
+  <si>
+    <t>某点极限存在可以推出存在一个处处有定义的去心邻域### ###</t>
+  </si>
+  <si>
+    <t>党生存发展第一位的问题是方向问题### ###</t>
+  </si>
+  <si>
+    <t>坚持正确政治方向</t>
+  </si>
+  <si>
+    <t>旗帜鲜明讲政治</t>
+  </si>
+  <si>
+    <t>保证党的团结和集中统一</t>
+  </si>
+  <si>
+    <t>党思想、政治、组织路线的确立### ###</t>
+  </si>
+  <si>
+    <t>首次确立：整风运动（1941-1945）奠定基础，七大（1945）正式确立</t>
+  </si>
+  <si>
+    <t>思想路线：实事求是的马克思主义</t>
+  </si>
+  <si>
+    <t>政治路线：放手发动群众、壮大人民力量</t>
+  </si>
+  <si>
+    <t>组织路线：以毛泽东为核心的党的第一代中央领导集体</t>
+  </si>
+  <si>
+    <t>重新确立：十一届三中全会（1978）</t>
+  </si>
+  <si>
+    <t>思想路线：解放思想、实事求是的马克思主义</t>
+  </si>
+  <si>
+    <t>政治路线：结束以阶级斗争为纲，工作重心到经济建设</t>
+  </si>
+  <si>
+    <t>组织路线：以邓小平为核心的党的第二代中央领导集体</t>
+  </si>
+  <si>
+    <t>作风建设的三个关乎### ###</t>
+  </si>
+  <si>
+    <t>关乎党的性质</t>
+  </si>
+  <si>
+    <t>关乎人心向背</t>
+  </si>
+  <si>
+    <t>关乎事业成败</t>
+  </si>
+  <si>
+    <t>新时代我国民主政治领域具有重大创新意义的标志性成果是全过程民主### ###</t>
+  </si>
+  <si>
+    <t>十八大提出的新概念</t>
+  </si>
+  <si>
+    <t>民主形态：片段化到全链条（选举、协商、决策、管理、监督）</t>
+  </si>
+  <si>
+    <t>民主覆盖：从局部到全方位（覆盖经济、政治、文化等）</t>
+  </si>
+  <si>
+    <t>民主效能：从形式到实质（四个统一）</t>
+  </si>
+  <si>
+    <t>过程与成果统一</t>
+  </si>
+  <si>
+    <t>程序与实质统一</t>
+  </si>
+  <si>
+    <t>直接与间接统一</t>
+  </si>
+  <si>
+    <t>人民民主与国家意志统一</t>
+  </si>
+  <si>
+    <t>制度保障：松散到系统（系统化、制度化、写入宪法修正案）</t>
+  </si>
+  <si>
+    <t>作风问题的核心是党同人民群众的关系问题### ###</t>
+  </si>
+  <si>
+    <t>作风建设的关键是保持党同人民群众的血肉联系### ###</t>
+  </si>
+  <si>
+    <t>建设文化强国，事关### ###</t>
+  </si>
+  <si>
+    <t>中国式现代化建设全局</t>
+  </si>
+  <si>
+    <t>中华民族复兴大业</t>
+  </si>
+  <si>
+    <t>提升国际竞争力</t>
+  </si>
+  <si>
+    <t>文化### ###</t>
+  </si>
+  <si>
+    <t>生命力、本质特征在于创新创造</t>
+  </si>
+  <si>
+    <t>创造核心在人</t>
+  </si>
+  <si>
+    <t>文化企业应该做到### ###</t>
+  </si>
+  <si>
+    <t>坚持把社会效益放在首位</t>
+  </si>
+  <si>
+    <t>实现社会效益和经济效益的相统一</t>
+  </si>
+  <si>
+    <t>文化遗产保护的原则### ###</t>
+  </si>
+  <si>
+    <t>保护第一</t>
+  </si>
+  <si>
+    <t>合理利用</t>
+  </si>
+  <si>
+    <t>最小干预</t>
+  </si>
+  <si>
+    <t>国家综合创新能力排名还没达到世界第一### ###</t>
+  </si>
+  <si>
+    <t>三大国际科创中心：北京、上海、粤港澳大湾区### ###</t>
+  </si>
+  <si>
+    <t>区域创新新格局是### ###</t>
+  </si>
+  <si>
+    <t>高地引领</t>
+  </si>
+  <si>
+    <t>梯次联动</t>
+  </si>
+  <si>
+    <t>优势互补</t>
+  </si>
+  <si>
+    <t>工人阶级是我们社会主义国家的领导阶级### ###</t>
+  </si>
+  <si>
+    <t>我们和拉美及加勒比国家的共同追求是公平正义### ###</t>
+  </si>
+  <si>
+    <t>中拉五大工程### ###</t>
+  </si>
+  <si>
+    <t>（首位）团结工程</t>
+  </si>
+  <si>
+    <t>发展工程</t>
+  </si>
+  <si>
+    <t>文明工程</t>
+  </si>
+  <si>
+    <t>和平工程</t>
+  </si>
+  <si>
+    <t>民心工程</t>
+  </si>
+  <si>
+    <t>中俄关系稳定发展的根本保障是元首引领### ###</t>
+  </si>
+  <si>
+    <t>鲜明特征是长期睦邻友好、互利合作共赢</t>
+  </si>
+  <si>
+    <t>主席强调中俄要</t>
+  </si>
+  <si>
+    <t>坚持世代友好（苏联老大哥）</t>
+  </si>
+  <si>
+    <t>坚持互利共赢（你的能源，我的技术）</t>
+  </si>
+  <si>
+    <t>坚持公平正义（反法西斯）</t>
+  </si>
+  <si>
+    <t>坚持和衷共济（对抗美帝）</t>
   </si>
 </sst>
 </file>
@@ -1241,7 +1211,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H86"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="9.66666666666667" style="1"/>
@@ -1251,31 +1221,31 @@
     <row r="1" s="1" customFormat="1" spans="1:8">
       <c r="A1" s="2">
         <f>SUM(B1:AZ1)</f>
-        <v>21.2666666666667</v>
+        <v>26.1761904761905</v>
       </c>
       <c r="B1" s="2">
-        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2220)/COLUMN()</f>
-        <v>2</v>
+        <f t="shared" ref="B1:H1" si="0">COUNTA(B2:B2193)/COLUMN()</f>
+        <v>9.5</v>
       </c>
       <c r="C1" s="2">
         <f t="shared" si="0"/>
-        <v>4.33333333333333</v>
+        <v>12</v>
       </c>
       <c r="D1" s="2">
         <f t="shared" si="0"/>
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="E1" s="2">
         <f t="shared" si="0"/>
-        <v>6.6</v>
+        <v>0.2</v>
       </c>
       <c r="F1" s="2">
         <f t="shared" si="0"/>
-        <v>0.833333333333333</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="G1" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.142857142857143</v>
       </c>
       <c r="H1" s="2">
         <f t="shared" si="0"/>
@@ -1297,17 +1267,17 @@
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:8">
-      <c r="D4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:8">
-      <c r="D5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:8">
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1317,400 +1287,348 @@
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:8">
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:8">
-      <c r="C9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:8">
-      <c r="D10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:8">
-      <c r="E11" s="1" t="s">
+      <c r="G11" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:8">
-      <c r="E12" s="1" t="s">
+      <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:8">
-      <c r="D13" s="1" t="s">
+      <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:8">
-      <c r="E14" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:8">
-      <c r="E15" s="1" t="s">
+      <c r="C15" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:8">
-      <c r="E16" s="1" t="s">
+      <c r="C16" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" spans="2:6">
+    <row r="17" s="1" customFormat="1" spans="2:4">
       <c r="B17" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" spans="2:6">
+    <row r="18" s="1" customFormat="1" spans="2:4">
       <c r="C18" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" spans="2:6">
+    <row r="19" s="1" customFormat="1" spans="2:4">
       <c r="D19" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" spans="2:6">
+    <row r="20" s="1" customFormat="1" spans="2:4">
       <c r="D20" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" spans="2:6">
-      <c r="C21" s="1" t="s">
+    <row r="21" s="1" customFormat="1" spans="2:4">
+      <c r="D21" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" spans="2:6">
-      <c r="D22" s="1" t="s">
+    <row r="22" s="1" customFormat="1" spans="2:4">
+      <c r="C22" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" spans="2:6">
-      <c r="E23" s="1" t="s">
+    <row r="23" s="1" customFormat="1" spans="2:4">
+      <c r="D23" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" spans="2:6">
-      <c r="E24" s="1" t="s">
+    <row r="24" s="1" customFormat="1" spans="2:4">
+      <c r="D24" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" spans="2:6">
-      <c r="E25" s="1" t="s">
+    <row r="25" s="1" customFormat="1" spans="2:4">
+      <c r="D25" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" spans="2:6">
-      <c r="D26" s="1" t="s">
+    <row r="26" s="1" customFormat="1" spans="2:4">
+      <c r="B26" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" spans="2:6">
-      <c r="E27" s="1" t="s">
+    <row r="27" s="1" customFormat="1" spans="2:4">
+      <c r="C27" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" spans="2:6">
-      <c r="E28" s="1" t="s">
+    <row r="28" s="1" customFormat="1" spans="2:4">
+      <c r="C28" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" spans="2:6">
-      <c r="F29" s="1" t="s">
+    <row r="29" s="1" customFormat="1" spans="2:4">
+      <c r="C29" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" spans="2:6">
-      <c r="F30" s="1" t="s">
+    <row r="30" s="1" customFormat="1" spans="2:4">
+      <c r="B30" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" spans="2:6">
+    <row r="31" s="1" customFormat="1" spans="2:4">
       <c r="C31" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="32" s="1" customFormat="1" spans="2:6">
-      <c r="D32" s="1" t="s">
+    <row r="32" s="1" customFormat="1" spans="2:4">
+      <c r="C32" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="33" s="1" customFormat="1" spans="2:5">
-      <c r="E33" s="1" t="s">
+    <row r="33" s="1" customFormat="1" spans="2:4">
+      <c r="C33" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" spans="2:5">
-      <c r="E34" s="1" t="s">
+    <row r="34" s="1" customFormat="1" spans="2:4">
+      <c r="C34" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" spans="2:5">
+    <row r="35" s="1" customFormat="1" spans="2:4">
       <c r="D35" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="36" s="1" customFormat="1" spans="2:5">
+    <row r="36" s="1" customFormat="1" spans="2:4">
       <c r="D36" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="37" s="1" customFormat="1" spans="2:5">
-      <c r="E37" s="1" t="s">
+    <row r="37" s="1" customFormat="1" spans="2:4">
+      <c r="D37" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1" spans="2:5">
-      <c r="E38" s="1" t="s">
+    <row r="38" s="1" customFormat="1" spans="2:4">
+      <c r="D38" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="39" s="1" customFormat="1" spans="2:5">
-      <c r="E39" s="1" t="s">
+    <row r="39" s="1" customFormat="1" spans="2:4">
+      <c r="C39" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="40" s="1" customFormat="1" spans="2:5">
+    <row r="40" s="1" customFormat="1" spans="2:4">
       <c r="B40" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="41" s="1" customFormat="1" spans="2:5">
-      <c r="C41" s="1" t="s">
+    <row r="41" s="1" customFormat="1" spans="2:4">
+      <c r="B41" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="42" s="1" customFormat="1" spans="2:5">
-      <c r="D42" s="1" t="s">
+    <row r="42" s="1" customFormat="1" spans="2:4">
+      <c r="B42" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="43" s="1" customFormat="1" spans="2:5">
-      <c r="D43" s="1" t="s">
+    <row r="43" s="1" customFormat="1" spans="2:4">
+      <c r="C43" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="44" s="1" customFormat="1" spans="2:5">
+    <row r="44" s="1" customFormat="1" spans="2:4">
       <c r="C44" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="45" s="1" customFormat="1" spans="2:5">
-      <c r="D45" s="1" t="s">
+    <row r="45" s="1" customFormat="1" spans="2:4">
+      <c r="C45" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="46" s="1" customFormat="1" spans="2:5">
-      <c r="D46" s="1" t="s">
+    <row r="46" s="1" customFormat="1" spans="2:4">
+      <c r="B46" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="47" s="1" customFormat="1" spans="2:5">
-      <c r="E47" s="1" t="s">
+    <row r="47" s="1" customFormat="1" spans="2:4">
+      <c r="C47" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="48" s="1" customFormat="1" spans="2:5">
-      <c r="E48" s="1" t="s">
+    <row r="48" s="1" customFormat="1" spans="2:4">
+      <c r="C48" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="49" s="1" customFormat="1" spans="3:6">
-      <c r="E49" s="1" t="s">
+    <row r="49" s="1" customFormat="1" spans="2:3">
+      <c r="B49" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="50" s="1" customFormat="1" spans="3:6">
+    <row r="50" s="1" customFormat="1" spans="2:3">
       <c r="C50" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="51" s="1" customFormat="1" spans="3:6">
-      <c r="D51" s="1" t="s">
+    <row r="51" s="1" customFormat="1" spans="2:3">
+      <c r="C51" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="52" s="1" customFormat="1" spans="3:6">
-      <c r="E52" s="1" t="s">
+    <row r="52" s="1" customFormat="1" spans="2:3">
+      <c r="B52" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="53" s="1" customFormat="1" spans="3:6">
-      <c r="E53" s="1" t="s">
+    <row r="53" s="1" customFormat="1" spans="2:3">
+      <c r="C53" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="54" s="1" customFormat="1" spans="3:6">
-      <c r="E54" s="1" t="s">
+    <row r="54" s="1" customFormat="1" spans="2:3">
+      <c r="C54" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="55" s="1" customFormat="1" spans="3:6">
-      <c r="D55" s="1" t="s">
+    <row r="55" s="1" customFormat="1" spans="2:3">
+      <c r="C55" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="56" s="1" customFormat="1" spans="3:6">
-      <c r="E56" s="1" t="s">
+    <row r="56" s="1" customFormat="1" spans="2:3">
+      <c r="B56" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="57" s="1" customFormat="1" spans="3:6">
-      <c r="E57" s="1" t="s">
+    <row r="57" s="1" customFormat="1" spans="2:3">
+      <c r="B57" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="58" s="1" customFormat="1" spans="3:6">
-      <c r="D58"/>
-      <c r="E58" s="1"/>
-      <c r="F58" s="1" t="s">
+    <row r="58" s="1" customFormat="1" spans="2:3">
+      <c r="B58" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="59" s="1" customFormat="1" spans="3:6">
-      <c r="F59" s="1" t="s">
+    <row r="59" s="1" customFormat="1" spans="2:3">
+      <c r="C59" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="60" s="1" customFormat="1" spans="3:6">
-      <c r="F60" s="1" t="s">
+    <row r="60" s="1" customFormat="1" spans="2:3">
+      <c r="C60" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="61" s="1" customFormat="1" spans="3:6">
+    <row r="61" s="1" customFormat="1" spans="2:3">
       <c r="C61" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="62" s="1" customFormat="1" spans="3:6">
-      <c r="D62" s="1" t="s">
+    <row r="62" s="1" customFormat="1" spans="2:3">
+      <c r="B62" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="63" s="1" customFormat="1" spans="3:6">
-      <c r="D63" s="1" t="s">
+    <row r="63" s="1" customFormat="1" spans="2:3">
+      <c r="B63" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="64" s="1" customFormat="1" spans="3:6">
-      <c r="D64" s="1" t="s">
+    <row r="64" s="1" customFormat="1" spans="2:3">
+      <c r="B64" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="65" s="1" customFormat="1" spans="2:5">
-      <c r="E65" s="1" t="s">
+    <row r="65" s="1" customFormat="1" spans="2:4">
+      <c r="C65" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="66" s="1" customFormat="1" spans="2:5">
-      <c r="E66" s="1" t="s">
+    <row r="66" s="1" customFormat="1" spans="2:4">
+      <c r="C66" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="67" s="1" customFormat="1" spans="2:5">
-      <c r="B67" s="1" t="s">
+    <row r="67" s="1" customFormat="1" spans="2:4">
+      <c r="C67" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="68" s="1" customFormat="1" spans="2:5">
+    <row r="68" s="1" customFormat="1" spans="2:4">
       <c r="C68" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="69" s="1" customFormat="1" spans="2:5">
-      <c r="D69" s="1" t="s">
+    <row r="69" s="1" customFormat="1" spans="2:4">
+      <c r="C69" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="70" s="1" customFormat="1" spans="2:5">
-      <c r="D70" s="1" t="s">
+    <row r="70" s="1" customFormat="1" spans="2:4">
+      <c r="B70" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="71" s="1" customFormat="1" spans="2:5">
-      <c r="D71" s="1" t="s">
+    <row r="71" s="1" customFormat="1" spans="2:4">
+      <c r="C71" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="72" s="1" customFormat="1" spans="2:5">
+    <row r="72" s="1" customFormat="1" spans="2:4">
       <c r="C72" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="73" s="1" customFormat="1" spans="2:5">
+    <row r="73" s="1" customFormat="1" spans="2:4">
       <c r="D73" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="74" s="1" customFormat="1" spans="2:5">
-      <c r="E74" s="1" t="s">
+    <row r="74" s="1" customFormat="1" spans="2:4">
+      <c r="D74" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="75" s="1" customFormat="1" spans="2:5">
-      <c r="E75" s="1" t="s">
+    <row r="75" s="1" customFormat="1" spans="2:4">
+      <c r="D75" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="76" s="1" customFormat="1" spans="2:5">
-      <c r="E76" s="1" t="s">
+    <row r="76" s="1" customFormat="1" spans="2:4">
+      <c r="D76" s="1" t="s">
         <v>74</v>
-      </c>
-    </row>
-    <row r="77" s="1" customFormat="1" spans="2:5">
-      <c r="D77" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="78" s="1" customFormat="1" spans="2:5">
-      <c r="E78" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="79" s="1" customFormat="1" spans="2:5">
-      <c r="E79" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="80" s="1" customFormat="1" spans="2:5">
-      <c r="E80" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="81" s="1" customFormat="1" spans="3:5">
-      <c r="D81" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="82" s="1" customFormat="1" spans="3:5">
-      <c r="C82" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="83" s="1" customFormat="1" spans="3:5">
-      <c r="D83" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="84" s="1" customFormat="1" spans="3:5">
-      <c r="D84" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="85" s="1" customFormat="1" spans="3:5">
-      <c r="E85" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="86" s="1" customFormat="1" spans="3:5">
-      <c r="E86" s="1" t="s">
-        <v>84</v>
       </c>
     </row>
   </sheetData>
